--- a/ЦНСВ БД.xlsx
+++ b/ЦНСВ БД.xlsx
@@ -630,7 +630,7 @@
       </c>
       <c r="D3" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Портной с умением кроить </t>
+          <t>Швея с умением кроить</t>
         </is>
       </c>
       <c r="E3" s="4" t="inlineStr">
@@ -662,7 +662,7 @@
       </c>
       <c r="D4" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Портной с умением кроить </t>
+          <t>Швея с умением кроить</t>
         </is>
       </c>
       <c r="E4" s="4" t="inlineStr">
@@ -694,7 +694,7 @@
       </c>
       <c r="D5" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Портной с умением кроить </t>
+          <t>Швея с умением кроить</t>
         </is>
       </c>
       <c r="E5" s="4" t="inlineStr">
@@ -726,7 +726,7 @@
       </c>
       <c r="D6" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Портной с умением кроить </t>
+          <t>Швея с умением кроить</t>
         </is>
       </c>
       <c r="E6" s="4" t="inlineStr">
@@ -758,7 +758,7 @@
       </c>
       <c r="D7" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Портной с умением кроить </t>
+          <t>Швея с умением кроить</t>
         </is>
       </c>
       <c r="E7" s="4" t="inlineStr">
@@ -790,7 +790,7 @@
       </c>
       <c r="D8" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Портной с умением кроить </t>
+          <t>Швея с умением кроить</t>
         </is>
       </c>
       <c r="E8" s="4" t="inlineStr">
@@ -1334,7 +1334,7 @@
       </c>
       <c r="D25" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Портной с умением кроить </t>
+          <t>Швея с умением кроить</t>
         </is>
       </c>
       <c r="E25" s="4" t="inlineStr">
@@ -1366,7 +1366,7 @@
       </c>
       <c r="D26" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Портной с умением кроить </t>
+          <t>Швея с умением кроить</t>
         </is>
       </c>
       <c r="E26" s="4" t="inlineStr">
@@ -1398,7 +1398,7 @@
       </c>
       <c r="D27" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Портной с умением кроить </t>
+          <t>Швея с умением кроить</t>
         </is>
       </c>
       <c r="E27" s="4" t="inlineStr">
@@ -1430,7 +1430,7 @@
       </c>
       <c r="D28" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Портной с умением кроить </t>
+          <t>Швея с умением кроить</t>
         </is>
       </c>
       <c r="E28" s="4" t="inlineStr">
@@ -1462,7 +1462,7 @@
       </c>
       <c r="D29" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Портной с умением кроить </t>
+          <t>Швея с умением кроить</t>
         </is>
       </c>
       <c r="E29" s="4" t="inlineStr">
@@ -1494,7 +1494,7 @@
       </c>
       <c r="D30" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Портной с умением кроить </t>
+          <t>Швея с умением кроить</t>
         </is>
       </c>
       <c r="E30" s="4" t="inlineStr">
@@ -1526,7 +1526,7 @@
       </c>
       <c r="D31" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Портной с умением кроить </t>
+          <t>Швея с умением кроить</t>
         </is>
       </c>
       <c r="E31" s="4" t="inlineStr">
@@ -1558,7 +1558,7 @@
       </c>
       <c r="D32" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Портной с умением кроить </t>
+          <t>Швея с умением кроить</t>
         </is>
       </c>
       <c r="E32" s="4" t="inlineStr">
@@ -1590,7 +1590,7 @@
       </c>
       <c r="D33" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Портной с умением кроить </t>
+          <t>Швея с умением кроить</t>
         </is>
       </c>
       <c r="E33" s="4" t="inlineStr">
@@ -1622,7 +1622,7 @@
       </c>
       <c r="D34" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Портной с умением кроить </t>
+          <t>Швея с умением кроить</t>
         </is>
       </c>
       <c r="E34" s="4" t="inlineStr">
@@ -1654,7 +1654,7 @@
       </c>
       <c r="D35" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Портной с умением кроить </t>
+          <t>Швея с умением кроить</t>
         </is>
       </c>
       <c r="E35" s="4" t="inlineStr">
@@ -1686,7 +1686,7 @@
       </c>
       <c r="D36" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Портной с умением кроить </t>
+          <t>Швея с умением кроить</t>
         </is>
       </c>
       <c r="E36" s="4" t="inlineStr">
@@ -1718,7 +1718,7 @@
       </c>
       <c r="D37" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Портной с умением кроить </t>
+          <t>Швея с умением кроить</t>
         </is>
       </c>
       <c r="E37" s="4" t="inlineStr">
@@ -1750,7 +1750,7 @@
       </c>
       <c r="D38" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Портной с умением кроить </t>
+          <t>Швея с умением кроить</t>
         </is>
       </c>
       <c r="E38" s="4" t="inlineStr">
@@ -1782,7 +1782,7 @@
       </c>
       <c r="D39" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Портной с умением кроить </t>
+          <t>Швея с умением кроить</t>
         </is>
       </c>
       <c r="E39" s="4" t="inlineStr">
@@ -4566,7 +4566,7 @@
       </c>
       <c r="D126" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">"Швея" и портной с умением кроить" </t>
+          <t>Швея с умением кроить</t>
         </is>
       </c>
       <c r="E126" s="4" t="inlineStr">
@@ -4598,7 +4598,7 @@
       </c>
       <c r="D127" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">"Швея" и портной с умением кроить" </t>
+          <t>Швея с умением кроить</t>
         </is>
       </c>
       <c r="E127" s="4" t="inlineStr">
@@ -4630,7 +4630,7 @@
       </c>
       <c r="D128" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">"Швея" и портной с умением кроить" </t>
+          <t>Швея с умением кроить</t>
         </is>
       </c>
       <c r="E128" s="4" t="inlineStr">
@@ -4662,7 +4662,7 @@
       </c>
       <c r="D129" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">"Швея" и портной с умением кроить" </t>
+          <t>Швея с умением кроить</t>
         </is>
       </c>
       <c r="E129" s="4" t="inlineStr">
@@ -7638,7 +7638,7 @@
       </c>
       <c r="D222" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">"Портной с умением кроить" 3-4 разряда </t>
+          <t>Швея с умением кроить 3-4 разряда</t>
         </is>
       </c>
       <c r="E222" s="4" t="inlineStr">
@@ -7670,7 +7670,7 @@
       </c>
       <c r="D223" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">"Портной с умением кроить" 3-4 разряда </t>
+          <t>Швея с умением кроить 3-4 разряда</t>
         </is>
       </c>
       <c r="E223" s="4" t="inlineStr">
@@ -7702,7 +7702,7 @@
       </c>
       <c r="D224" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">"Портной с умением кроить" 3-4 разряда </t>
+          <t>Швея с умением кроить 3-4 разряда</t>
         </is>
       </c>
       <c r="E224" s="4" t="inlineStr">
@@ -7734,7 +7734,7 @@
       </c>
       <c r="D225" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">"Портной с умением кроить" 3-4 разряда </t>
+          <t>Швея с умением кроить 3-4 разряда</t>
         </is>
       </c>
       <c r="E225" s="4" t="inlineStr">
@@ -7766,7 +7766,7 @@
       </c>
       <c r="D226" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">"Портной с умением кроить" 3-4 разряда </t>
+          <t>Швея с умением кроить 3-4 разряда</t>
         </is>
       </c>
       <c r="E226" s="4" t="inlineStr">
@@ -7798,7 +7798,7 @@
       </c>
       <c r="D227" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">"Портной с умением кроить" 3-4 разряда </t>
+          <t>Швея с умением кроить 3-4 разряда</t>
         </is>
       </c>
       <c r="E227" s="4" t="inlineStr">
@@ -7830,7 +7830,7 @@
       </c>
       <c r="D228" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">"Портной с умением кроить" 3-4 разряда </t>
+          <t>Швея с умением кроить 3-4 разряда</t>
         </is>
       </c>
       <c r="E228" s="4" t="inlineStr">
@@ -7862,7 +7862,7 @@
       </c>
       <c r="D229" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">"Портной с умением кроить" 3-4 разряда </t>
+          <t>Швея с умением кроить 3-4 разряда</t>
         </is>
       </c>
       <c r="E229" s="4" t="inlineStr">
@@ -7894,7 +7894,7 @@
       </c>
       <c r="D230" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">"Портной с умением кроить" 3-4 разряда </t>
+          <t>Швея с умением кроить 3-4 разряда</t>
         </is>
       </c>
       <c r="E230" s="4" t="inlineStr">
@@ -7926,7 +7926,7 @@
       </c>
       <c r="D231" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">"Портной с умением кроить" 3-4 разряда </t>
+          <t>Швея с умением кроить 3-4 разряда</t>
         </is>
       </c>
       <c r="E231" s="4" t="inlineStr">
@@ -7958,7 +7958,7 @@
       </c>
       <c r="D232" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">"Портной с умением кроить" 3-4 разряда </t>
+          <t>Швея с умением кроить 3-4 разряда</t>
         </is>
       </c>
       <c r="E232" s="4" t="inlineStr">
@@ -7990,7 +7990,7 @@
       </c>
       <c r="D233" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">"Портной с умением кроить" 3-4 разряда </t>
+          <t>Швея с умением кроить 3-4 разряда</t>
         </is>
       </c>
       <c r="E233" s="4" t="inlineStr">
@@ -8022,7 +8022,7 @@
       </c>
       <c r="D234" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">"Портной с умением кроить" 3-4 разряда </t>
+          <t>Швея с умением кроить 3-4 разряда</t>
         </is>
       </c>
       <c r="E234" s="4" t="inlineStr">
@@ -8054,7 +8054,7 @@
       </c>
       <c r="D235" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">"Портной с умением кроить" 3-4 разряда </t>
+          <t>Швея с умением кроить 3-4 разряда</t>
         </is>
       </c>
       <c r="E235" s="4" t="inlineStr">
@@ -8086,7 +8086,7 @@
       </c>
       <c r="D236" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">"Портной с умением кроить" 3-4 разряда </t>
+          <t>Швея с умением кроить 3-4 разряда</t>
         </is>
       </c>
       <c r="E236" s="4" t="inlineStr">
@@ -8118,7 +8118,7 @@
       </c>
       <c r="D237" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">"Портной с умением кроить" 3-4 разряда </t>
+          <t>Швея с умением кроить 3-4 разряда</t>
         </is>
       </c>
       <c r="E237" s="4" t="inlineStr">
@@ -8150,7 +8150,7 @@
       </c>
       <c r="D238" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">"Портной с умением кроить" 3-4 разряда </t>
+          <t>Швея с умением кроить 3-4 разряда</t>
         </is>
       </c>
       <c r="E238" s="4" t="inlineStr">
@@ -8182,7 +8182,7 @@
       </c>
       <c r="D239" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">"Портной с умением кроить" 3-4 разряда </t>
+          <t>Швея с умением кроить 3-4 разряда</t>
         </is>
       </c>
       <c r="E239" s="4" t="inlineStr">
@@ -8214,7 +8214,7 @@
       </c>
       <c r="D240" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">"Портной с умением кроить" 3-4 разряда </t>
+          <t>Швея с умением кроить 3-4 разряда</t>
         </is>
       </c>
       <c r="E240" s="4" t="inlineStr">
@@ -8246,7 +8246,7 @@
       </c>
       <c r="D241" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">"Портной с умением кроить" 3-4 разряда </t>
+          <t>Швея с умением кроить 3-4 разряда</t>
         </is>
       </c>
       <c r="E241" s="4" t="inlineStr">
@@ -8278,7 +8278,7 @@
       </c>
       <c r="D242" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">"Портной с умением кроить" 3-4 разряда </t>
+          <t>Швея с умением кроить 3-4 разряда</t>
         </is>
       </c>
       <c r="E242" s="4" t="inlineStr">
@@ -8310,7 +8310,7 @@
       </c>
       <c r="D243" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">"Портной с умением кроить" 3-4 разряда </t>
+          <t>Швея с умением кроить 3-4 разряда</t>
         </is>
       </c>
       <c r="E243" s="4" t="inlineStr">
@@ -8342,7 +8342,7 @@
       </c>
       <c r="D244" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">"Портной с умением кроить" 3-4 разряда </t>
+          <t>Швея с умением кроить 3-4 разряда</t>
         </is>
       </c>
       <c r="E244" s="4" t="inlineStr">
@@ -8374,7 +8374,7 @@
       </c>
       <c r="D245" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">"Портной с умением кроить" 3-4 разряда </t>
+          <t>Швея с умением кроить 3-4 разряда</t>
         </is>
       </c>
       <c r="E245" s="4" t="inlineStr">
@@ -8406,7 +8406,7 @@
       </c>
       <c r="D246" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">"Портной с умением кроить" 3-4 разряда </t>
+          <t>Швея с умением кроить 3-4 разряда</t>
         </is>
       </c>
       <c r="E246" s="4" t="inlineStr">
@@ -8438,7 +8438,7 @@
       </c>
       <c r="D247" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">"Портной с умением кроить" 3-4 разряда </t>
+          <t>Швея с умением кроить 3-4 разряда</t>
         </is>
       </c>
       <c r="E247" s="4" t="inlineStr">
@@ -8470,7 +8470,7 @@
       </c>
       <c r="D248" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">"Портной с умением кроить" 3-4 разряда </t>
+          <t>Швея с умением кроить 3-4 разряда</t>
         </is>
       </c>
       <c r="E248" s="4" t="inlineStr">
@@ -8502,7 +8502,7 @@
       </c>
       <c r="D249" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">"Портной с умением кроить" 3-4 разряда </t>
+          <t>Швея с умением кроить 3-4 разряда</t>
         </is>
       </c>
       <c r="E249" s="4" t="inlineStr">
@@ -8534,7 +8534,7 @@
       </c>
       <c r="D250" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">"Портной с умением кроить" 3-4 разряда </t>
+          <t>Швея с умением кроить 3-4 разряда</t>
         </is>
       </c>
       <c r="E250" s="4" t="inlineStr">
@@ -8566,7 +8566,7 @@
       </c>
       <c r="D251" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">"Портной с умением кроить" 3-4 разряда </t>
+          <t>Швея с умением кроить 3-4 разряда</t>
         </is>
       </c>
       <c r="E251" s="4" t="inlineStr">
@@ -8598,7 +8598,7 @@
       </c>
       <c r="D252" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">"Портной с умением кроить" 3-4 разряда </t>
+          <t>Швея с умением кроить 3-4 разряда</t>
         </is>
       </c>
       <c r="E252" s="4" t="inlineStr">
@@ -8630,7 +8630,7 @@
       </c>
       <c r="D253" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">"Портной с умением кроить" 3-4 разряда </t>
+          <t>Швея с умением кроить 3-4 разряда</t>
         </is>
       </c>
       <c r="E253" s="4" t="inlineStr">
@@ -8662,7 +8662,7 @@
       </c>
       <c r="D254" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">"Портной с умением кроить" 3-4 разряда </t>
+          <t>Швея с умением кроить 3-4 разряда</t>
         </is>
       </c>
       <c r="E254" s="4" t="inlineStr">
@@ -8694,7 +8694,7 @@
       </c>
       <c r="D255" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">"Портной с умением кроить" 3-4 разряда </t>
+          <t>Швея с умением кроить 3-4 разряда</t>
         </is>
       </c>
       <c r="E255" s="4" t="inlineStr">
@@ -8726,7 +8726,7 @@
       </c>
       <c r="D256" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">"Портной с умением кроить" 3-4 разряда </t>
+          <t>Швея с умением кроить 3-4 разряда</t>
         </is>
       </c>
       <c r="E256" s="4" t="inlineStr">
@@ -8758,7 +8758,7 @@
       </c>
       <c r="D257" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">"Портной с умением кроить" 3-4 разряда </t>
+          <t>Швея с умением кроить 3-4 разряда</t>
         </is>
       </c>
       <c r="E257" s="4" t="inlineStr">
@@ -8790,7 +8790,7 @@
       </c>
       <c r="D258" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">"Портной с умением кроить" 3-4 разряда </t>
+          <t>Швея с умением кроить 3-4 разряда</t>
         </is>
       </c>
       <c r="E258" s="4" t="inlineStr">
@@ -8822,7 +8822,7 @@
       </c>
       <c r="D259" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">"Портной с умением кроить" 3-4 разряда </t>
+          <t>Швея с умением кроить 3-4 разряда</t>
         </is>
       </c>
       <c r="E259" s="4" t="inlineStr">
@@ -8854,7 +8854,7 @@
       </c>
       <c r="D260" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">"Портной с умением кроить" 3-4 разряда </t>
+          <t>Швея с умением кроить 3-4 разряда</t>
         </is>
       </c>
       <c r="E260" s="4" t="inlineStr">
@@ -13046,7 +13046,7 @@
       </c>
       <c r="D391" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">"Швея" "Портной с умением кроить" </t>
+          <t>Швея с умением кроить</t>
         </is>
       </c>
       <c r="E391" s="4" t="inlineStr">
@@ -13078,7 +13078,7 @@
       </c>
       <c r="D392" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">"Швея" "Портной с умением кроить" </t>
+          <t>Швея с умением кроить</t>
         </is>
       </c>
       <c r="E392" s="4" t="inlineStr">
@@ -13110,7 +13110,7 @@
       </c>
       <c r="D393" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">"Швея" "Портной с умением кроить" </t>
+          <t>Швея с умением кроить</t>
         </is>
       </c>
       <c r="E393" s="4" t="inlineStr">
@@ -13142,7 +13142,7 @@
       </c>
       <c r="D394" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">"Швея" "Портной с умением кроить" </t>
+          <t>Швея с умением кроить</t>
         </is>
       </c>
       <c r="E394" s="4" t="inlineStr">
@@ -13174,7 +13174,7 @@
       </c>
       <c r="D395" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">"Швея" "Портной с умением кроить" </t>
+          <t>Швея с умением кроить</t>
         </is>
       </c>
       <c r="E395" s="4" t="inlineStr">
@@ -13206,7 +13206,7 @@
       </c>
       <c r="D396" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">"Швея" "Портной с умением кроить" </t>
+          <t>Швея с умением кроить</t>
         </is>
       </c>
       <c r="E396" s="4" t="inlineStr">
@@ -13238,7 +13238,7 @@
       </c>
       <c r="D397" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">"Швея" "Портной с умением кроить" </t>
+          <t>Швея с умением кроить</t>
         </is>
       </c>
       <c r="E397" s="4" t="inlineStr">
@@ -13270,7 +13270,7 @@
       </c>
       <c r="D398" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">"Швея" "Портной с умением кроить" </t>
+          <t>Швея с умением кроить</t>
         </is>
       </c>
       <c r="E398" s="4" t="inlineStr">
@@ -13302,7 +13302,7 @@
       </c>
       <c r="D399" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">"Швея" "Портной с умением кроить" </t>
+          <t>Швея с умением кроить</t>
         </is>
       </c>
       <c r="E399" s="4" t="inlineStr">
@@ -13334,7 +13334,7 @@
       </c>
       <c r="D400" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">"Швея" "Портной с умением кроить" </t>
+          <t>Швея с умением кроить</t>
         </is>
       </c>
       <c r="E400" s="4" t="inlineStr">
@@ -13366,7 +13366,7 @@
       </c>
       <c r="D401" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">"Швея" "Портной с умением кроить" </t>
+          <t>Швея с умением кроить</t>
         </is>
       </c>
       <c r="E401" s="4" t="inlineStr">
@@ -13398,7 +13398,7 @@
       </c>
       <c r="D402" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">"Швея" "Портной с умением кроить" </t>
+          <t>Швея с умением кроить</t>
         </is>
       </c>
       <c r="E402" s="4" t="inlineStr">
@@ -17846,7 +17846,7 @@
       </c>
       <c r="D541" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">"Слесарь по ремонту автотранспортных средств" </t>
+          <t>"Слесарь по ремонту автотранспортных средств"</t>
         </is>
       </c>
       <c r="E541" s="4" t="inlineStr">
@@ -18838,7 +18838,7 @@
       </c>
       <c r="D572" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">портной,мастер народных промыслов </t>
+          <t>Швея, мастер народных промыслов</t>
         </is>
       </c>
       <c r="E572" s="4" t="inlineStr">
@@ -18870,7 +18870,7 @@
       </c>
       <c r="D573" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Слесарь по ремонту автотранспортных средств </t>
+          <t>Слесарь по ремонту автотранспортных средств</t>
         </is>
       </c>
       <c r="E573" s="4" t="inlineStr">
@@ -18902,7 +18902,7 @@
       </c>
       <c r="D574" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Слесарь по ремонту автотранспортных средств </t>
+          <t>Слесарь по ремонту автотранспортных средств</t>
         </is>
       </c>
       <c r="E574" s="4" t="inlineStr">
@@ -18934,7 +18934,7 @@
       </c>
       <c r="D575" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Слесарь по ремонту автотранспортных средств </t>
+          <t>Слесарь по ремонту автотранспортных средств</t>
         </is>
       </c>
       <c r="E575" s="4" t="inlineStr">
@@ -18966,7 +18966,7 @@
       </c>
       <c r="D576" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Слесарь по ремонту автотранспортных средств </t>
+          <t>Слесарь по ремонту автотранспортных средств</t>
         </is>
       </c>
       <c r="E576" s="4" t="inlineStr">
@@ -18998,7 +18998,7 @@
       </c>
       <c r="D577" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Слесарь по ремонту автотранспортных средств </t>
+          <t>Слесарь по ремонту автотранспортных средств</t>
         </is>
       </c>
       <c r="E577" s="4" t="inlineStr">
@@ -19346,7 +19346,7 @@
       </c>
       <c r="D588" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Портной с умением кроить </t>
+          <t>Швея с умением кроить</t>
         </is>
       </c>
       <c r="E588" s="4" t="inlineStr">
@@ -20466,7 +20466,7 @@
       </c>
       <c r="D623" s="4" t="inlineStr">
         <is>
-          <t>Портной</t>
+          <t>Швея</t>
         </is>
       </c>
       <c r="E623" s="4" t="inlineStr">
@@ -20498,7 +20498,7 @@
       </c>
       <c r="D624" s="4" t="inlineStr">
         <is>
-          <t>портной</t>
+          <t>Швея</t>
         </is>
       </c>
       <c r="E624" s="4" t="inlineStr">
@@ -20530,7 +20530,7 @@
       </c>
       <c r="D625" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">портной </t>
+          <t>Швея</t>
         </is>
       </c>
       <c r="E625" s="4" t="inlineStr">
@@ -20562,7 +20562,7 @@
       </c>
       <c r="D626" s="4" t="inlineStr">
         <is>
-          <t>портной</t>
+          <t>Швея</t>
         </is>
       </c>
       <c r="E626" s="4" t="inlineStr">
@@ -20594,7 +20594,7 @@
       </c>
       <c r="D627" s="4" t="inlineStr">
         <is>
-          <t>портной</t>
+          <t>Швея</t>
         </is>
       </c>
       <c r="E627" s="4" t="inlineStr">
@@ -20658,7 +20658,7 @@
       </c>
       <c r="D629" s="4" t="inlineStr">
         <is>
-          <t>портной</t>
+          <t>Швея</t>
         </is>
       </c>
       <c r="E629" s="4" t="inlineStr">
@@ -20690,7 +20690,7 @@
       </c>
       <c r="D630" s="4" t="inlineStr">
         <is>
-          <t>портной</t>
+          <t>Швея</t>
         </is>
       </c>
       <c r="E630" s="4" t="inlineStr">
@@ -20722,7 +20722,7 @@
       </c>
       <c r="D631" s="4" t="inlineStr">
         <is>
-          <t>портной</t>
+          <t>Швея</t>
         </is>
       </c>
       <c r="E631" s="4" t="inlineStr">
@@ -21554,7 +21554,7 @@
       </c>
       <c r="D657" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Слесерь по ремонту автотранспортных средств </t>
+          <t>Слесерь по ремонту автотранспортных средств</t>
         </is>
       </c>
       <c r="E657" s="4" t="inlineStr">
@@ -22356,7 +22356,7 @@
       </c>
       <c r="D682" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Портной </t>
+          <t>Швея</t>
         </is>
       </c>
       <c r="E682" s="4" t="inlineStr">
@@ -22388,7 +22388,7 @@
       </c>
       <c r="D683" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Портной </t>
+          <t>Швея</t>
         </is>
       </c>
       <c r="E683" s="4" t="inlineStr">
@@ -22422,7 +22422,7 @@
       </c>
       <c r="D684" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Портной </t>
+          <t>Швея</t>
         </is>
       </c>
       <c r="E684" s="4" t="inlineStr">
@@ -22774,7 +22774,7 @@
       </c>
       <c r="D695" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Слесарь по ремонту автотранспортных средств </t>
+          <t>Слесарь по ремонту автотранспортных средств</t>
         </is>
       </c>
       <c r="E695" s="4" t="inlineStr">
@@ -23318,7 +23318,7 @@
       </c>
       <c r="D712" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Контролер технического состояния автомототранспортных средств </t>
+          <t>Контролер технического состояния автомототранспортных средств</t>
         </is>
       </c>
       <c r="E712" s="4" t="inlineStr">
@@ -24758,7 +24758,7 @@
       </c>
       <c r="D757" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Портной с умением кроить 5 разряда </t>
+          <t>Швея с умением кроить 5 разряда</t>
         </is>
       </c>
       <c r="E757" s="4" t="inlineStr">
@@ -24790,7 +24790,7 @@
       </c>
       <c r="D758" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Портной с умением кроить 5 разряда </t>
+          <t>Швея с умением кроить 5 разряда</t>
         </is>
       </c>
       <c r="E758" s="4" t="inlineStr">
@@ -25398,7 +25398,7 @@
       </c>
       <c r="D777" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Портной с умением кроить 3 разряда </t>
+          <t>Швея с умением кроить 3 разряда</t>
         </is>
       </c>
       <c r="E777" s="4" t="inlineStr">

--- a/ЦНСВ БД.xlsx
+++ b/ЦНСВ БД.xlsx
@@ -17,7 +17,9 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
+  <numFmts count="1">
+    <numFmt numFmtId="164" formatCode="yyyy-mm-dd"/>
+  </numFmts>
   <fonts count="7">
     <font>
       <name val="Calibri"/>
@@ -135,7 +137,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="22">
+  <cellXfs count="23">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment wrapText="1"/>
@@ -184,6 +186,7 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Обычный" xfId="0" builtinId="0"/>
@@ -191,93 +194,6 @@
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <colors/>
 </styleSheet>
-</file>
-
-<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
-<wsDr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
-  <twoCellAnchor editAs="oneCell">
-    <from>
-      <col>6</col>
-      <colOff>130175</colOff>
-      <row>0</row>
-      <rowOff>28575</rowOff>
-    </from>
-    <to>
-      <col>6</col>
-      <colOff>1184275</colOff>
-      <row>0</row>
-      <rowOff>819150</rowOff>
-    </to>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="3" name="Рисунок 2"/>
-        <cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </cNvPicPr>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId1"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:xfrm>
-          <a:off x="8131175" y="28575"/>
-          <a:ext cx="1054100" cy="790575"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <avLst/>
-        </a:prstGeom>
-        <a:ln>
-          <a:prstDash val="solid"/>
-        </a:ln>
-      </spPr>
-    </pic>
-    <clientData/>
-  </twoCellAnchor>
-  <twoCellAnchor editAs="oneCell">
-    <from>
-      <col>2</col>
-      <colOff>1247775</colOff>
-      <row>0</row>
-      <rowOff>95250</rowOff>
-    </from>
-    <to>
-      <col>2</col>
-      <colOff>1905001</colOff>
-      <row>0</row>
-      <rowOff>752476</rowOff>
-    </to>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="5" name="Рисунок 4"/>
-        <cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </cNvPicPr>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId2"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:xfrm>
-          <a:off x="1971675" y="95250"/>
-          <a:ext cx="657226" cy="657226"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <avLst/>
-        </a:prstGeom>
-        <a:ln>
-          <a:prstDash val="solid"/>
-        </a:ln>
-      </spPr>
-    </pic>
-    <clientData/>
-  </twoCellAnchor>
-</wsDr>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -547,7 +463,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:H2563"/>
+  <dimension ref="A1:H2562"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="14.4"/>
   <cols>
     <col width="5.33203125" customWidth="1" min="1" max="1"/>
@@ -625,12 +541,12 @@
       </c>
       <c r="C3" s="4" t="inlineStr">
         <is>
-          <t>Абдилова Свветлана</t>
+          <t xml:space="preserve">Абдилова Свветлана </t>
         </is>
       </c>
       <c r="D3" s="4" t="inlineStr">
         <is>
-          <t>Швея с умением кроить</t>
+          <t xml:space="preserve">Портной с умением кроить </t>
         </is>
       </c>
       <c r="E3" s="4" t="inlineStr">
@@ -657,12 +573,12 @@
       </c>
       <c r="C4" s="4" t="inlineStr">
         <is>
-          <t>Артыкова Барно</t>
+          <t xml:space="preserve">Артыкова Барно </t>
         </is>
       </c>
       <c r="D4" s="4" t="inlineStr">
         <is>
-          <t>Швея с умением кроить</t>
+          <t xml:space="preserve">Портной с умением кроить </t>
         </is>
       </c>
       <c r="E4" s="4" t="inlineStr">
@@ -689,12 +605,12 @@
       </c>
       <c r="C5" s="4" t="inlineStr">
         <is>
-          <t>Каныбекова Анара</t>
+          <t xml:space="preserve">Каныбекова Анара </t>
         </is>
       </c>
       <c r="D5" s="4" t="inlineStr">
         <is>
-          <t>Швея с умением кроить</t>
+          <t xml:space="preserve">Портной с умением кроить </t>
         </is>
       </c>
       <c r="E5" s="4" t="inlineStr">
@@ -721,12 +637,12 @@
       </c>
       <c r="C6" s="4" t="inlineStr">
         <is>
-          <t>Касымова Айжаркын</t>
+          <t xml:space="preserve">Касымова Айжаркын </t>
         </is>
       </c>
       <c r="D6" s="4" t="inlineStr">
         <is>
-          <t>Швея с умением кроить</t>
+          <t xml:space="preserve">Портной с умением кроить </t>
         </is>
       </c>
       <c r="E6" s="4" t="inlineStr">
@@ -753,12 +669,12 @@
       </c>
       <c r="C7" s="4" t="inlineStr">
         <is>
-          <t>Мамытова Санжыра</t>
+          <t xml:space="preserve">Мамытова Санжыра </t>
         </is>
       </c>
       <c r="D7" s="4" t="inlineStr">
         <is>
-          <t>Швея с умением кроить</t>
+          <t xml:space="preserve">Портной с умением кроить </t>
         </is>
       </c>
       <c r="E7" s="4" t="inlineStr">
@@ -785,12 +701,12 @@
       </c>
       <c r="C8" s="4" t="inlineStr">
         <is>
-          <t>Сатыбалдиева Каныкей</t>
+          <t xml:space="preserve">Сатыбалдиева Каныкей </t>
         </is>
       </c>
       <c r="D8" s="4" t="inlineStr">
         <is>
-          <t>Швея с умением кроить</t>
+          <t xml:space="preserve">Портной с умением кроить </t>
         </is>
       </c>
       <c r="E8" s="4" t="inlineStr">
@@ -817,7 +733,7 @@
       </c>
       <c r="C9" s="4" t="inlineStr">
         <is>
-          <t>Анаркадый уулу Адилет</t>
+          <t xml:space="preserve">Анаркадый уулу Адилет </t>
         </is>
       </c>
       <c r="D9" s="4" t="inlineStr">
@@ -849,7 +765,7 @@
       </c>
       <c r="C10" s="4" t="inlineStr">
         <is>
-          <t>Хафизов Кутпидин</t>
+          <t xml:space="preserve">Хафизов Кутпидин </t>
         </is>
       </c>
       <c r="D10" s="4" t="inlineStr">
@@ -881,7 +797,7 @@
       </c>
       <c r="C11" s="4" t="inlineStr">
         <is>
-          <t>Жамангулов Миргелбек</t>
+          <t xml:space="preserve">Жамангулов Миргелбек </t>
         </is>
       </c>
       <c r="D11" s="4" t="inlineStr">
@@ -945,7 +861,7 @@
       </c>
       <c r="C13" s="4" t="inlineStr">
         <is>
-          <t>Шергазы уулу Тилктеш</t>
+          <t xml:space="preserve">Шергазы уулу Тилктеш </t>
         </is>
       </c>
       <c r="D13" s="4" t="inlineStr">
@@ -977,7 +893,7 @@
       </c>
       <c r="C14" s="4" t="inlineStr">
         <is>
-          <t>Низомов Махмадамин</t>
+          <t xml:space="preserve">Низомов Махмадамин </t>
         </is>
       </c>
       <c r="D14" s="4" t="inlineStr">
@@ -1009,7 +925,7 @@
       </c>
       <c r="C15" s="4" t="inlineStr">
         <is>
-          <t>Жодатбек уулу Нур</t>
+          <t xml:space="preserve">Жодатбек уулу Нур </t>
         </is>
       </c>
       <c r="D15" s="4" t="inlineStr">
@@ -1041,7 +957,7 @@
       </c>
       <c r="C16" s="4" t="inlineStr">
         <is>
-          <t>Доктурбеков Мирлан</t>
+          <t xml:space="preserve">Доктурбеков Мирлан </t>
         </is>
       </c>
       <c r="D16" s="4" t="inlineStr">
@@ -1073,7 +989,7 @@
       </c>
       <c r="C17" s="4" t="inlineStr">
         <is>
-          <t>Женишбек уулу Азамат</t>
+          <t xml:space="preserve">Женишбек уулу Азамат </t>
         </is>
       </c>
       <c r="D17" s="4" t="inlineStr">
@@ -1105,7 +1021,7 @@
       </c>
       <c r="C18" s="4" t="inlineStr">
         <is>
-          <t>Файзидинов Фарух</t>
+          <t xml:space="preserve">Файзидинов Фарух </t>
         </is>
       </c>
       <c r="D18" s="4" t="inlineStr">
@@ -1137,7 +1053,7 @@
       </c>
       <c r="C19" s="4" t="inlineStr">
         <is>
-          <t>Мусаев Акмалидин</t>
+          <t xml:space="preserve">Мусаев Акмалидин </t>
         </is>
       </c>
       <c r="D19" s="4" t="inlineStr">
@@ -1169,7 +1085,7 @@
       </c>
       <c r="C20" s="4" t="inlineStr">
         <is>
-          <t>Закиров Мулоджон</t>
+          <t xml:space="preserve">Закиров Мулоджон </t>
         </is>
       </c>
       <c r="D20" s="4" t="inlineStr">
@@ -1233,7 +1149,7 @@
       </c>
       <c r="C22" s="4" t="inlineStr">
         <is>
-          <t>Фазылов Данияр</t>
+          <t xml:space="preserve">Фазылов Данияр </t>
         </is>
       </c>
       <c r="D22" s="4" t="inlineStr">
@@ -1265,7 +1181,7 @@
       </c>
       <c r="C23" s="4" t="inlineStr">
         <is>
-          <t>Чыналиев Каныбек</t>
+          <t xml:space="preserve">Чыналиев Каныбек </t>
         </is>
       </c>
       <c r="D23" s="4" t="inlineStr">
@@ -1297,7 +1213,7 @@
       </c>
       <c r="C24" s="4" t="inlineStr">
         <is>
-          <t>Аалиев Анарбек</t>
+          <t xml:space="preserve">Аалиев Анарбек </t>
         </is>
       </c>
       <c r="D24" s="4" t="inlineStr">
@@ -1329,12 +1245,12 @@
       </c>
       <c r="C25" s="4" t="inlineStr">
         <is>
-          <t>Абдыгапыр кызы Фарида</t>
+          <t xml:space="preserve">Абдыгапыр кызы Фарида </t>
         </is>
       </c>
       <c r="D25" s="4" t="inlineStr">
         <is>
-          <t>Швея с умением кроить</t>
+          <t xml:space="preserve">Портной с умением кроить </t>
         </is>
       </c>
       <c r="E25" s="4" t="inlineStr">
@@ -1361,12 +1277,12 @@
       </c>
       <c r="C26" s="4" t="inlineStr">
         <is>
-          <t>Арапбай кызы Аида</t>
+          <t xml:space="preserve">Арапбай кызы Аида </t>
         </is>
       </c>
       <c r="D26" s="4" t="inlineStr">
         <is>
-          <t>Швея с умением кроить</t>
+          <t xml:space="preserve">Портной с умением кроить </t>
         </is>
       </c>
       <c r="E26" s="4" t="inlineStr">
@@ -1393,12 +1309,12 @@
       </c>
       <c r="C27" s="4" t="inlineStr">
         <is>
-          <t>Азим кызы Нуржамал</t>
+          <t xml:space="preserve">Азим кызы Нуржамал </t>
         </is>
       </c>
       <c r="D27" s="4" t="inlineStr">
         <is>
-          <t>Швея с умением кроить</t>
+          <t xml:space="preserve">Портной с умением кроить </t>
         </is>
       </c>
       <c r="E27" s="4" t="inlineStr">
@@ -1425,12 +1341,12 @@
       </c>
       <c r="C28" s="4" t="inlineStr">
         <is>
-          <t>Балтабаева Жанаргул</t>
+          <t xml:space="preserve">Балтабаева Жанаргул </t>
         </is>
       </c>
       <c r="D28" s="4" t="inlineStr">
         <is>
-          <t>Швея с умением кроить</t>
+          <t xml:space="preserve">Портной с умением кроить </t>
         </is>
       </c>
       <c r="E28" s="4" t="inlineStr">
@@ -1457,12 +1373,12 @@
       </c>
       <c r="C29" s="4" t="inlineStr">
         <is>
-          <t>Бактыбек кызы Бурулай</t>
+          <t xml:space="preserve">Бактыбек кызы Бурулай </t>
         </is>
       </c>
       <c r="D29" s="4" t="inlineStr">
         <is>
-          <t>Швея с умением кроить</t>
+          <t xml:space="preserve">Портной с умением кроить </t>
         </is>
       </c>
       <c r="E29" s="4" t="inlineStr">
@@ -1489,12 +1405,12 @@
       </c>
       <c r="C30" s="4" t="inlineStr">
         <is>
-          <t>Боронова Нуркан</t>
+          <t xml:space="preserve">Боронова Нуркан </t>
         </is>
       </c>
       <c r="D30" s="4" t="inlineStr">
         <is>
-          <t>Швея с умением кроить</t>
+          <t xml:space="preserve">Портной с умением кроить </t>
         </is>
       </c>
       <c r="E30" s="4" t="inlineStr">
@@ -1521,12 +1437,12 @@
       </c>
       <c r="C31" s="4" t="inlineStr">
         <is>
-          <t>Вайдуллаева Дилором</t>
+          <t xml:space="preserve">Вайдуллаева Дилором </t>
         </is>
       </c>
       <c r="D31" s="4" t="inlineStr">
         <is>
-          <t>Швея с умением кроить</t>
+          <t xml:space="preserve">Портной с умением кроить </t>
         </is>
       </c>
       <c r="E31" s="4" t="inlineStr">
@@ -1553,12 +1469,12 @@
       </c>
       <c r="C32" s="4" t="inlineStr">
         <is>
-          <t>Жолдошова Уулара</t>
+          <t xml:space="preserve">Жолдошова Уулара </t>
         </is>
       </c>
       <c r="D32" s="4" t="inlineStr">
         <is>
-          <t>Швея с умением кроить</t>
+          <t xml:space="preserve">Портной с умением кроить </t>
         </is>
       </c>
       <c r="E32" s="4" t="inlineStr">
@@ -1585,12 +1501,12 @@
       </c>
       <c r="C33" s="4" t="inlineStr">
         <is>
-          <t>Зулпиева Элиза</t>
+          <t xml:space="preserve">Зулпиева Элиза </t>
         </is>
       </c>
       <c r="D33" s="4" t="inlineStr">
         <is>
-          <t>Швея с умением кроить</t>
+          <t xml:space="preserve">Портной с умением кроить </t>
         </is>
       </c>
       <c r="E33" s="4" t="inlineStr">
@@ -1617,12 +1533,12 @@
       </c>
       <c r="C34" s="4" t="inlineStr">
         <is>
-          <t>Кубанычбек кызы Элиза</t>
+          <t xml:space="preserve">Кубанычбек кызы Элиза </t>
         </is>
       </c>
       <c r="D34" s="4" t="inlineStr">
         <is>
-          <t>Швея с умением кроить</t>
+          <t xml:space="preserve">Портной с умением кроить </t>
         </is>
       </c>
       <c r="E34" s="4" t="inlineStr">
@@ -1649,12 +1565,12 @@
       </c>
       <c r="C35" s="4" t="inlineStr">
         <is>
-          <t>Мурзакарим кызы Нуржан</t>
+          <t xml:space="preserve">Мурзакарим кызы Нуржан </t>
         </is>
       </c>
       <c r="D35" s="4" t="inlineStr">
         <is>
-          <t>Швея с умением кроить</t>
+          <t xml:space="preserve">Портной с умением кроить </t>
         </is>
       </c>
       <c r="E35" s="4" t="inlineStr">
@@ -1681,12 +1597,12 @@
       </c>
       <c r="C36" s="4" t="inlineStr">
         <is>
-          <t>Мамашарипова Гүлмира</t>
+          <t xml:space="preserve">Мамашарипова Гульмира </t>
         </is>
       </c>
       <c r="D36" s="4" t="inlineStr">
         <is>
-          <t>Швея с умением кроить</t>
+          <t xml:space="preserve">Портной с умением кроить </t>
         </is>
       </c>
       <c r="E36" s="4" t="inlineStr">
@@ -1713,12 +1629,12 @@
       </c>
       <c r="C37" s="4" t="inlineStr">
         <is>
-          <t>Мадумарова Роза</t>
+          <t xml:space="preserve">Мадумарова Роза </t>
         </is>
       </c>
       <c r="D37" s="4" t="inlineStr">
         <is>
-          <t>Швея с умением кроить</t>
+          <t xml:space="preserve">Портной с умением кроить </t>
         </is>
       </c>
       <c r="E37" s="4" t="inlineStr">
@@ -1745,12 +1661,12 @@
       </c>
       <c r="C38" s="4" t="inlineStr">
         <is>
-          <t>Равшанова Хайтжан</t>
+          <t xml:space="preserve">Равшанова Хайтжан </t>
         </is>
       </c>
       <c r="D38" s="4" t="inlineStr">
         <is>
-          <t>Швея с умением кроить</t>
+          <t xml:space="preserve">Портной с умением кроить </t>
         </is>
       </c>
       <c r="E38" s="4" t="inlineStr">
@@ -1777,12 +1693,12 @@
       </c>
       <c r="C39" s="4" t="inlineStr">
         <is>
-          <t>Худоярова Зарифахан</t>
+          <t xml:space="preserve">Худоярова Зарифахан </t>
         </is>
       </c>
       <c r="D39" s="4" t="inlineStr">
         <is>
-          <t>Швея с умением кроить</t>
+          <t xml:space="preserve">Портной с умением кроить </t>
         </is>
       </c>
       <c r="E39" s="4" t="inlineStr">
@@ -1809,7 +1725,7 @@
       </c>
       <c r="C40" s="4" t="inlineStr">
         <is>
-          <t>Банеков Василий</t>
+          <t xml:space="preserve">Банеков Василий </t>
         </is>
       </c>
       <c r="D40" s="4" t="inlineStr">
@@ -1841,7 +1757,7 @@
       </c>
       <c r="C41" s="4" t="inlineStr">
         <is>
-          <t>Касымбаев Мырзабай</t>
+          <t xml:space="preserve">Касымбаев Мырзабай </t>
         </is>
       </c>
       <c r="D41" s="4" t="inlineStr">
@@ -1873,7 +1789,7 @@
       </c>
       <c r="C42" s="4" t="inlineStr">
         <is>
-          <t>Михайилов Никита</t>
+          <t xml:space="preserve">Михайилов Никита </t>
         </is>
       </c>
       <c r="D42" s="4" t="inlineStr">
@@ -1905,7 +1821,7 @@
       </c>
       <c r="C43" s="4" t="inlineStr">
         <is>
-          <t>Маслов Святослав</t>
+          <t xml:space="preserve">Маслов Святослав </t>
         </is>
       </c>
       <c r="D43" s="4" t="inlineStr">
@@ -1969,7 +1885,7 @@
       </c>
       <c r="C45" s="4" t="inlineStr">
         <is>
-          <t>Молчанов Евгений</t>
+          <t xml:space="preserve">Молчанов Евгений </t>
         </is>
       </c>
       <c r="D45" s="4" t="inlineStr">
@@ -2033,7 +1949,7 @@
       </c>
       <c r="C47" s="4" t="inlineStr">
         <is>
-          <t>Пулеха Антон</t>
+          <t xml:space="preserve">Пулеха Антон </t>
         </is>
       </c>
       <c r="D47" s="4" t="inlineStr">
@@ -2065,7 +1981,7 @@
       </c>
       <c r="C48" s="4" t="inlineStr">
         <is>
-          <t>Соколов Дмитрий</t>
+          <t xml:space="preserve">Соколов Дмитрий </t>
         </is>
       </c>
       <c r="D48" s="4" t="inlineStr">
@@ -2097,7 +2013,7 @@
       </c>
       <c r="C49" s="4" t="inlineStr">
         <is>
-          <t>Хаджимуратов Хамид</t>
+          <t xml:space="preserve">Хаджимуратов Хамид </t>
         </is>
       </c>
       <c r="D49" s="4" t="inlineStr">
@@ -2129,7 +2045,7 @@
       </c>
       <c r="C50" s="4" t="inlineStr">
         <is>
-          <t>Илперц Данил</t>
+          <t xml:space="preserve">Илперц Данил </t>
         </is>
       </c>
       <c r="D50" s="4" t="inlineStr">
@@ -2161,7 +2077,7 @@
       </c>
       <c r="C51" s="4" t="inlineStr">
         <is>
-          <t>Абдуллаев Уткирбек</t>
+          <t xml:space="preserve">Абдуллаев Уткирбек </t>
         </is>
       </c>
       <c r="D51" s="4" t="inlineStr">
@@ -2193,7 +2109,7 @@
       </c>
       <c r="C52" s="4" t="inlineStr">
         <is>
-          <t>Алижанов Максатбеке</t>
+          <t xml:space="preserve">Алижанов Максатбеке </t>
         </is>
       </c>
       <c r="D52" s="4" t="inlineStr">
@@ -2225,7 +2141,7 @@
       </c>
       <c r="C53" s="4" t="inlineStr">
         <is>
-          <t>Ажиматов Канат</t>
+          <t xml:space="preserve">Ажиматов Канат </t>
         </is>
       </c>
       <c r="D53" s="4" t="inlineStr">
@@ -2257,7 +2173,7 @@
       </c>
       <c r="C54" s="4" t="inlineStr">
         <is>
-          <t>Акмедов Насимидин</t>
+          <t xml:space="preserve">Акмедов Насимидин </t>
         </is>
       </c>
       <c r="D54" s="4" t="inlineStr">
@@ -2289,7 +2205,7 @@
       </c>
       <c r="C55" s="4" t="inlineStr">
         <is>
-          <t>Абдумалик уулу Абдуллажан</t>
+          <t xml:space="preserve">Абдумалик уулу Абдуллажан </t>
         </is>
       </c>
       <c r="D55" s="4" t="inlineStr">
@@ -2321,7 +2237,7 @@
       </c>
       <c r="C56" s="4" t="inlineStr">
         <is>
-          <t>Акмедов Рустамжан</t>
+          <t xml:space="preserve">Акмедов Рустамжан </t>
         </is>
       </c>
       <c r="D56" s="4" t="inlineStr">
@@ -2353,7 +2269,7 @@
       </c>
       <c r="C57" s="4" t="inlineStr">
         <is>
-          <t>Байматов Чолпонбай</t>
+          <t xml:space="preserve">Байматов Чолпонбай </t>
         </is>
       </c>
       <c r="D57" s="4" t="inlineStr">
@@ -2385,7 +2301,7 @@
       </c>
       <c r="C58" s="4" t="inlineStr">
         <is>
-          <t>Галиаскаров Ринат</t>
+          <t xml:space="preserve">Галиаскаров Ринат </t>
         </is>
       </c>
       <c r="D58" s="4" t="inlineStr">
@@ -2417,7 +2333,7 @@
       </c>
       <c r="C59" s="4" t="inlineStr">
         <is>
-          <t>Ибрагимов Асланбек</t>
+          <t xml:space="preserve">Ибрагимов Асланбек </t>
         </is>
       </c>
       <c r="D59" s="4" t="inlineStr">
@@ -2449,7 +2365,7 @@
       </c>
       <c r="C60" s="4" t="inlineStr">
         <is>
-          <t>Калмырзаев Жумабек</t>
+          <t xml:space="preserve">Калмырзаев Жумабек </t>
         </is>
       </c>
       <c r="D60" s="4" t="inlineStr">
@@ -2481,7 +2397,7 @@
       </c>
       <c r="C61" s="4" t="inlineStr">
         <is>
-          <t>Кабыл уулу Айтмамат</t>
+          <t xml:space="preserve">Кабыл уулу Айтмамат </t>
         </is>
       </c>
       <c r="D61" s="4" t="inlineStr">
@@ -2513,7 +2429,7 @@
       </c>
       <c r="C62" s="4" t="inlineStr">
         <is>
-          <t>Мамасидиков Махмуджан</t>
+          <t xml:space="preserve">Мамасидиков Махмуджан </t>
         </is>
       </c>
       <c r="D62" s="4" t="inlineStr">
@@ -2545,7 +2461,7 @@
       </c>
       <c r="C63" s="4" t="inlineStr">
         <is>
-          <t>Нарматов Доктурбек</t>
+          <t xml:space="preserve">Нарматов Доктурбек </t>
         </is>
       </c>
       <c r="D63" s="4" t="inlineStr">
@@ -2577,7 +2493,7 @@
       </c>
       <c r="C64" s="4" t="inlineStr">
         <is>
-          <t>Реджапай уулу Абубакир</t>
+          <t xml:space="preserve">Реджапай уулу Абубакир </t>
         </is>
       </c>
       <c r="D64" s="4" t="inlineStr">
@@ -2609,7 +2525,7 @@
       </c>
       <c r="C65" s="4" t="inlineStr">
         <is>
-          <t>Рысбаев Мирланбек</t>
+          <t xml:space="preserve">Рысбаев Мирланбек </t>
         </is>
       </c>
       <c r="D65" s="4" t="inlineStr">
@@ -2641,7 +2557,7 @@
       </c>
       <c r="C66" s="4" t="inlineStr">
         <is>
-          <t>Таштанов Кубанычбек</t>
+          <t xml:space="preserve">Таштанов Кубанычбек </t>
         </is>
       </c>
       <c r="D66" s="4" t="inlineStr">
@@ -2673,7 +2589,7 @@
       </c>
       <c r="C67" s="4" t="inlineStr">
         <is>
-          <t>Танатаров Радил</t>
+          <t xml:space="preserve">Танатаров Радил </t>
         </is>
       </c>
       <c r="D67" s="4" t="inlineStr">
@@ -2737,7 +2653,7 @@
       </c>
       <c r="C69" s="4" t="inlineStr">
         <is>
-          <t>Токтоматов Кенжебай</t>
+          <t xml:space="preserve">Токтоматов Кенжебай </t>
         </is>
       </c>
       <c r="D69" s="4" t="inlineStr">
@@ -2769,7 +2685,7 @@
       </c>
       <c r="C70" s="13" t="inlineStr">
         <is>
-          <t>Артюхов Александр</t>
+          <t xml:space="preserve">Артюхов Александр </t>
         </is>
       </c>
       <c r="D70" s="13" t="inlineStr">
@@ -2801,7 +2717,7 @@
       </c>
       <c r="C71" s="13" t="inlineStr">
         <is>
-          <t>Базарбек уулу Азамат</t>
+          <t xml:space="preserve">Базарбек уулу Азамат </t>
         </is>
       </c>
       <c r="D71" s="13" t="inlineStr">
@@ -2833,7 +2749,7 @@
       </c>
       <c r="C72" s="13" t="inlineStr">
         <is>
-          <t>Байбосунов Максат</t>
+          <t xml:space="preserve">Байбосунов Максат </t>
         </is>
       </c>
       <c r="D72" s="13" t="inlineStr">
@@ -2865,7 +2781,7 @@
       </c>
       <c r="C73" s="13" t="inlineStr">
         <is>
-          <t>Бекталиев Чынгыз</t>
+          <t xml:space="preserve">Бекталиев Чынгыз </t>
         </is>
       </c>
       <c r="D73" s="13" t="inlineStr">
@@ -2897,7 +2813,7 @@
       </c>
       <c r="C74" s="13" t="inlineStr">
         <is>
-          <t>Максатбеков Адилет</t>
+          <t xml:space="preserve">Максатбеков Адилет </t>
         </is>
       </c>
       <c r="D74" s="13" t="inlineStr">
@@ -2929,7 +2845,7 @@
       </c>
       <c r="C75" s="13" t="inlineStr">
         <is>
-          <t>Меджитов Алексей</t>
+          <t xml:space="preserve">Меджитов Алексей </t>
         </is>
       </c>
       <c r="D75" s="13" t="inlineStr">
@@ -2961,7 +2877,7 @@
       </c>
       <c r="C76" s="13" t="inlineStr">
         <is>
-          <t>Надиров Камель</t>
+          <t xml:space="preserve">Надиров Камель </t>
         </is>
       </c>
       <c r="D76" s="13" t="inlineStr">
@@ -2993,7 +2909,7 @@
       </c>
       <c r="C77" s="13" t="inlineStr">
         <is>
-          <t>Өмүров Марс</t>
+          <t xml:space="preserve">Омуров Марс </t>
         </is>
       </c>
       <c r="D77" s="13" t="inlineStr">
@@ -3025,7 +2941,7 @@
       </c>
       <c r="C78" s="13" t="inlineStr">
         <is>
-          <t>Шатемиров Медер</t>
+          <t xml:space="preserve">Шатемиров Медер </t>
         </is>
       </c>
       <c r="D78" s="13" t="inlineStr">
@@ -3057,7 +2973,7 @@
       </c>
       <c r="C79" s="13" t="inlineStr">
         <is>
-          <t>Эрматов Зарылбек</t>
+          <t xml:space="preserve">Эрматов Зарылбек </t>
         </is>
       </c>
       <c r="D79" s="13" t="inlineStr">
@@ -3089,7 +3005,7 @@
       </c>
       <c r="C80" s="13" t="inlineStr">
         <is>
-          <t>Эрматов Марат</t>
+          <t xml:space="preserve">Эрматов Марат </t>
         </is>
       </c>
       <c r="D80" s="13" t="inlineStr">
@@ -3121,7 +3037,7 @@
       </c>
       <c r="C81" s="13" t="inlineStr">
         <is>
-          <t>Якубов Жолдош</t>
+          <t xml:space="preserve">Якубов Жолдош </t>
         </is>
       </c>
       <c r="D81" s="13" t="inlineStr">
@@ -3153,7 +3069,7 @@
       </c>
       <c r="C82" s="13" t="inlineStr">
         <is>
-          <t>Акматов Нурбек</t>
+          <t xml:space="preserve">Акматов Нурбек </t>
         </is>
       </c>
       <c r="D82" s="15" t="inlineStr">
@@ -3185,7 +3101,7 @@
       </c>
       <c r="C83" s="13" t="inlineStr">
         <is>
-          <t>Алманкулов Акжолтой</t>
+          <t xml:space="preserve">Алманкулов Акжолтой </t>
         </is>
       </c>
       <c r="D83" s="15" t="inlineStr">
@@ -3217,7 +3133,7 @@
       </c>
       <c r="C84" s="13" t="inlineStr">
         <is>
-          <t>Бактыбаев Улан</t>
+          <t xml:space="preserve">Бактыбаев Улан </t>
         </is>
       </c>
       <c r="D84" s="15" t="inlineStr">
@@ -3249,7 +3165,7 @@
       </c>
       <c r="C85" s="13" t="inlineStr">
         <is>
-          <t>Бапиев Алтынбек</t>
+          <t xml:space="preserve">Бапиев Алтынбек </t>
         </is>
       </c>
       <c r="D85" s="15" t="inlineStr">
@@ -3281,7 +3197,7 @@
       </c>
       <c r="C86" s="13" t="inlineStr">
         <is>
-          <t>Бапиев Уланбек</t>
+          <t xml:space="preserve">Бапиев Уланбек </t>
         </is>
       </c>
       <c r="D86" s="15" t="inlineStr">
@@ -3313,7 +3229,7 @@
       </c>
       <c r="C87" s="13" t="inlineStr">
         <is>
-          <t>Жайлообек уулу Болотбек</t>
+          <t xml:space="preserve">Жайлообек уулу Болотбек </t>
         </is>
       </c>
       <c r="D87" s="15" t="inlineStr">
@@ -3345,7 +3261,7 @@
       </c>
       <c r="C88" s="13" t="inlineStr">
         <is>
-          <t>Жангарач уулу Исабек</t>
+          <t xml:space="preserve">Жангарач уулу Исабек </t>
         </is>
       </c>
       <c r="D88" s="15" t="inlineStr">
@@ -3377,7 +3293,7 @@
       </c>
       <c r="C89" s="13" t="inlineStr">
         <is>
-          <t>Жапаров Азамат</t>
+          <t xml:space="preserve">Жапаров Азамат </t>
         </is>
       </c>
       <c r="D89" s="15" t="inlineStr">
@@ -3409,7 +3325,7 @@
       </c>
       <c r="C90" s="13" t="inlineStr">
         <is>
-          <t>Жунусалиев Адилет</t>
+          <t xml:space="preserve">Жунусалиев Адилет </t>
         </is>
       </c>
       <c r="D90" s="15" t="inlineStr">
@@ -3441,7 +3357,7 @@
       </c>
       <c r="C91" s="13" t="inlineStr">
         <is>
-          <t>Исаков Аманбек</t>
+          <t xml:space="preserve">Исаков Аманбек </t>
         </is>
       </c>
       <c r="D91" s="15" t="inlineStr">
@@ -3473,7 +3389,7 @@
       </c>
       <c r="C92" s="13" t="inlineStr">
         <is>
-          <t>Карагулов Адилет</t>
+          <t xml:space="preserve">Карагулов Адилет </t>
         </is>
       </c>
       <c r="D92" s="15" t="inlineStr">
@@ -3505,7 +3421,7 @@
       </c>
       <c r="C93" s="13" t="inlineStr">
         <is>
-          <t>Мамбеталиев Бекжан</t>
+          <t xml:space="preserve">Мамбеталиев Бекжан </t>
         </is>
       </c>
       <c r="D93" s="15" t="inlineStr">
@@ -3537,7 +3453,7 @@
       </c>
       <c r="C94" s="13" t="inlineStr">
         <is>
-          <t>Садыбаказов Өмүрзак</t>
+          <t xml:space="preserve">Садыбаказов Омурзак </t>
         </is>
       </c>
       <c r="D94" s="15" t="inlineStr">
@@ -3569,7 +3485,7 @@
       </c>
       <c r="C95" s="13" t="inlineStr">
         <is>
-          <t>Ыдырысов Ырысбек</t>
+          <t xml:space="preserve">Ыдырысов Ырысбек </t>
         </is>
       </c>
       <c r="D95" s="15" t="inlineStr">
@@ -3601,7 +3517,7 @@
       </c>
       <c r="C96" s="13" t="inlineStr">
         <is>
-          <t>Эркинбек уулу Кубатбек</t>
+          <t xml:space="preserve">Эркинбек уулу Кубатбек </t>
         </is>
       </c>
       <c r="D96" s="15" t="inlineStr">
@@ -3633,7 +3549,7 @@
       </c>
       <c r="C97" s="13" t="inlineStr">
         <is>
-          <t>Зарлыкова Бегайым</t>
+          <t xml:space="preserve">Зарлыкова Бегайым </t>
         </is>
       </c>
       <c r="D97" s="13" t="inlineStr">
@@ -3665,7 +3581,7 @@
       </c>
       <c r="C98" s="13" t="inlineStr">
         <is>
-          <t>Тилекова Айдай</t>
+          <t xml:space="preserve">Тилекова Айдай </t>
         </is>
       </c>
       <c r="D98" s="13" t="inlineStr">
@@ -3697,7 +3613,7 @@
       </c>
       <c r="C99" s="13" t="inlineStr">
         <is>
-          <t>Идирисова Райкан</t>
+          <t xml:space="preserve">Идирисова Райкан </t>
         </is>
       </c>
       <c r="D99" s="13" t="inlineStr">
@@ -3729,7 +3645,7 @@
       </c>
       <c r="C100" s="13" t="inlineStr">
         <is>
-          <t>Айбекова Сагида</t>
+          <t xml:space="preserve">Айбекова Сагида </t>
         </is>
       </c>
       <c r="D100" s="13" t="inlineStr">
@@ -3761,7 +3677,7 @@
       </c>
       <c r="C101" s="13" t="inlineStr">
         <is>
-          <t>Сапарбекова Бегайым</t>
+          <t xml:space="preserve">Сапарбекова Бегайым </t>
         </is>
       </c>
       <c r="D101" s="13" t="inlineStr">
@@ -3793,7 +3709,7 @@
       </c>
       <c r="C102" s="13" t="inlineStr">
         <is>
-          <t>Муканбетова Гүлбайра</t>
+          <t xml:space="preserve">Муканбетова Гулбайра </t>
         </is>
       </c>
       <c r="D102" s="13" t="inlineStr">
@@ -3825,7 +3741,7 @@
       </c>
       <c r="C103" s="13" t="inlineStr">
         <is>
-          <t>Есентаева Бегимай</t>
+          <t xml:space="preserve">Есентаева Бегимай </t>
         </is>
       </c>
       <c r="D103" s="13" t="inlineStr">
@@ -3857,7 +3773,7 @@
       </c>
       <c r="C104" s="13" t="inlineStr">
         <is>
-          <t>Джакыпова Эльмира</t>
+          <t xml:space="preserve">Джакыпова Эльмира </t>
         </is>
       </c>
       <c r="D104" s="13" t="inlineStr">
@@ -3889,7 +3805,7 @@
       </c>
       <c r="C105" s="13" t="inlineStr">
         <is>
-          <t>Жолдошева Турсунай</t>
+          <t xml:space="preserve">Жолдошева Турсунай </t>
         </is>
       </c>
       <c r="D105" s="13" t="inlineStr">
@@ -3921,7 +3837,7 @@
       </c>
       <c r="C106" s="13" t="inlineStr">
         <is>
-          <t>Джаамбаева Нурсель</t>
+          <t xml:space="preserve">Джаамбаева Нурсель </t>
         </is>
       </c>
       <c r="D106" s="13" t="inlineStr">
@@ -3953,7 +3869,7 @@
       </c>
       <c r="C107" s="4" t="inlineStr">
         <is>
-          <t>Абдыбек кызы Адина</t>
+          <t xml:space="preserve">Абдыбек кызы Адина </t>
         </is>
       </c>
       <c r="D107" s="4" t="inlineStr">
@@ -3985,7 +3901,7 @@
       </c>
       <c r="C108" s="4" t="inlineStr">
         <is>
-          <t>Алиева Жылдыз</t>
+          <t xml:space="preserve">Алиева Жылдыз </t>
         </is>
       </c>
       <c r="D108" s="4" t="inlineStr">
@@ -4017,7 +3933,7 @@
       </c>
       <c r="C109" s="4" t="inlineStr">
         <is>
-          <t>Бектурсун кызы Жазгүл</t>
+          <t xml:space="preserve">Бектурсун кызы Жазгул </t>
         </is>
       </c>
       <c r="D109" s="4" t="inlineStr">
@@ -4049,7 +3965,7 @@
       </c>
       <c r="C110" s="4" t="inlineStr">
         <is>
-          <t>Додогелдиева Махабат</t>
+          <t xml:space="preserve">Додогелдиева Махабат </t>
         </is>
       </c>
       <c r="D110" s="4" t="inlineStr">
@@ -4081,7 +3997,7 @@
       </c>
       <c r="C111" s="4" t="inlineStr">
         <is>
-          <t>Жапаркулова Атыркул</t>
+          <t xml:space="preserve">Жапаркулова Атыркул </t>
         </is>
       </c>
       <c r="D111" s="4" t="inlineStr">
@@ -4113,7 +4029,7 @@
       </c>
       <c r="C112" s="4" t="inlineStr">
         <is>
-          <t>Журсунбек кызы Динара</t>
+          <t xml:space="preserve">Журсунбек кызы Динара </t>
         </is>
       </c>
       <c r="D112" s="4" t="inlineStr">
@@ -4145,7 +4061,7 @@
       </c>
       <c r="C113" s="4" t="inlineStr">
         <is>
-          <t>Кадырова Жанаркул</t>
+          <t xml:space="preserve">Кадырова Жанаркул </t>
         </is>
       </c>
       <c r="D113" s="4" t="inlineStr">
@@ -4177,7 +4093,7 @@
       </c>
       <c r="C114" s="4" t="inlineStr">
         <is>
-          <t>Канбаева Каныгүл</t>
+          <t xml:space="preserve">Канбаева Каныгул </t>
         </is>
       </c>
       <c r="D114" s="4" t="inlineStr">
@@ -4209,7 +4125,7 @@
       </c>
       <c r="C115" s="4" t="inlineStr">
         <is>
-          <t>Касыммакунова Жамиля</t>
+          <t xml:space="preserve">Касыммакунова Жамиля </t>
         </is>
       </c>
       <c r="D115" s="4" t="inlineStr">
@@ -4241,7 +4157,7 @@
       </c>
       <c r="C116" s="4" t="inlineStr">
         <is>
-          <t>Кенжетаева Зарифа</t>
+          <t xml:space="preserve">Кенжетаева Зарифа </t>
         </is>
       </c>
       <c r="D116" s="4" t="inlineStr">
@@ -4273,7 +4189,7 @@
       </c>
       <c r="C117" s="4" t="inlineStr">
         <is>
-          <t>Кубанычбекова Гүлүм</t>
+          <t xml:space="preserve">Кубанычбекова Гулум </t>
         </is>
       </c>
       <c r="D117" s="4" t="inlineStr">
@@ -4305,7 +4221,7 @@
       </c>
       <c r="C118" s="4" t="inlineStr">
         <is>
-          <t>Кулматова Жылдыз</t>
+          <t xml:space="preserve">Кулматова Жылдыз </t>
         </is>
       </c>
       <c r="D118" s="4" t="inlineStr">
@@ -4337,7 +4253,7 @@
       </c>
       <c r="C119" s="4" t="inlineStr">
         <is>
-          <t>Мамбеткадырова Венера</t>
+          <t xml:space="preserve">Мамбеткадырова Венера </t>
         </is>
       </c>
       <c r="D119" s="4" t="inlineStr">
@@ -4369,7 +4285,7 @@
       </c>
       <c r="C120" s="4" t="inlineStr">
         <is>
-          <t>Озокеева Нуриса</t>
+          <t xml:space="preserve">Озокеева Нуриса </t>
         </is>
       </c>
       <c r="D120" s="4" t="inlineStr">
@@ -4401,7 +4317,7 @@
       </c>
       <c r="C121" s="16" t="inlineStr">
         <is>
-          <t>Өмүрбекова Нурзаада</t>
+          <t xml:space="preserve">Өмүрбекова Нурзаада </t>
         </is>
       </c>
       <c r="D121" s="4" t="inlineStr">
@@ -4433,7 +4349,7 @@
       </c>
       <c r="C122" s="4" t="inlineStr">
         <is>
-          <t>Сариева Чынара</t>
+          <t xml:space="preserve">Сариева Чынара </t>
         </is>
       </c>
       <c r="D122" s="4" t="inlineStr">
@@ -4465,7 +4381,7 @@
       </c>
       <c r="C123" s="4" t="inlineStr">
         <is>
-          <t>Шадыбаева Мадина</t>
+          <t xml:space="preserve">Шадыбаева Мадина </t>
         </is>
       </c>
       <c r="D123" s="4" t="inlineStr">
@@ -4497,7 +4413,7 @@
       </c>
       <c r="C124" s="4" t="inlineStr">
         <is>
-          <t>Эдисова Кулиша</t>
+          <t xml:space="preserve">Эдисова Кулиша </t>
         </is>
       </c>
       <c r="D124" s="4" t="inlineStr">
@@ -4529,7 +4445,7 @@
       </c>
       <c r="C125" s="4" t="inlineStr">
         <is>
-          <t>Эликбаева Назира</t>
+          <t xml:space="preserve">Эликбаева Назира </t>
         </is>
       </c>
       <c r="D125" s="4" t="inlineStr">
@@ -4561,12 +4477,12 @@
       </c>
       <c r="C126" s="4" t="inlineStr">
         <is>
-          <t>Абылжан кызы Айгүл</t>
+          <t xml:space="preserve">Абылжан кызы Айгул </t>
         </is>
       </c>
       <c r="D126" s="4" t="inlineStr">
         <is>
-          <t>Швея с умением кроить</t>
+          <t xml:space="preserve">"Швея" и портной с умением кроить" </t>
         </is>
       </c>
       <c r="E126" s="4" t="inlineStr">
@@ -4593,12 +4509,12 @@
       </c>
       <c r="C127" s="4" t="inlineStr">
         <is>
-          <t>Ашымов Мелис</t>
+          <t xml:space="preserve">Ашымов Мелис </t>
         </is>
       </c>
       <c r="D127" s="4" t="inlineStr">
         <is>
-          <t>Швея с умением кроить</t>
+          <t xml:space="preserve">"Швея" и портной с умением кроить" </t>
         </is>
       </c>
       <c r="E127" s="4" t="inlineStr">
@@ -4625,12 +4541,12 @@
       </c>
       <c r="C128" s="4" t="inlineStr">
         <is>
-          <t>Усенбаева Чынара</t>
+          <t xml:space="preserve">Усенбаева Чынара </t>
         </is>
       </c>
       <c r="D128" s="4" t="inlineStr">
         <is>
-          <t>Швея с умением кроить</t>
+          <t xml:space="preserve">"Швея" и портной с умением кроить" </t>
         </is>
       </c>
       <c r="E128" s="4" t="inlineStr">
@@ -4657,12 +4573,12 @@
       </c>
       <c r="C129" s="4" t="inlineStr">
         <is>
-          <t>Буйневич Кира</t>
+          <t xml:space="preserve">Буйневич Кира </t>
         </is>
       </c>
       <c r="D129" s="4" t="inlineStr">
         <is>
-          <t>Швея с умением кроить</t>
+          <t xml:space="preserve">"Швея" и портной с умением кроить" </t>
         </is>
       </c>
       <c r="E129" s="4" t="inlineStr">
@@ -4689,7 +4605,7 @@
       </c>
       <c r="C130" s="4" t="inlineStr">
         <is>
-          <t>Акматова Нуржан</t>
+          <t xml:space="preserve">Акматова Нуржан </t>
         </is>
       </c>
       <c r="D130" s="4" t="inlineStr">
@@ -4721,7 +4637,7 @@
       </c>
       <c r="C131" s="4" t="inlineStr">
         <is>
-          <t>Айталиева Айжан</t>
+          <t xml:space="preserve">Айталиева Айжан </t>
         </is>
       </c>
       <c r="D131" s="4" t="inlineStr">
@@ -4753,7 +4669,7 @@
       </c>
       <c r="C132" s="4" t="inlineStr">
         <is>
-          <t>Джамалова Роза</t>
+          <t xml:space="preserve">Джамалова Роза </t>
         </is>
       </c>
       <c r="D132" s="4" t="inlineStr">
@@ -4785,7 +4701,7 @@
       </c>
       <c r="C133" s="4" t="inlineStr">
         <is>
-          <t>Джеенбекова Толкун</t>
+          <t xml:space="preserve">Джеенбекова Толкун </t>
         </is>
       </c>
       <c r="D133" s="4" t="inlineStr">
@@ -4817,7 +4733,7 @@
       </c>
       <c r="C134" s="4" t="inlineStr">
         <is>
-          <t>Джеенбекова Лира</t>
+          <t xml:space="preserve">Джеенбекова Лира </t>
         </is>
       </c>
       <c r="D134" s="4" t="inlineStr">
@@ -4849,7 +4765,7 @@
       </c>
       <c r="C135" s="4" t="inlineStr">
         <is>
-          <t>Жумадил кызы Чынаркул</t>
+          <t xml:space="preserve">Жумадил кызы Чынаркул </t>
         </is>
       </c>
       <c r="D135" s="4" t="inlineStr">
@@ -4881,7 +4797,7 @@
       </c>
       <c r="C136" s="4" t="inlineStr">
         <is>
-          <t>Маталиева Эркайым</t>
+          <t xml:space="preserve">Маталиева Эркайым </t>
         </is>
       </c>
       <c r="D136" s="4" t="inlineStr">
@@ -4913,7 +4829,7 @@
       </c>
       <c r="C137" s="4" t="inlineStr">
         <is>
-          <t>Толебаев Алмаз</t>
+          <t xml:space="preserve">Толебаев Алмаз </t>
         </is>
       </c>
       <c r="D137" s="4" t="inlineStr">
@@ -4945,7 +4861,7 @@
       </c>
       <c r="C138" s="4" t="inlineStr">
         <is>
-          <t>Калманбетов Толегон</t>
+          <t xml:space="preserve">Калманбетов Толегон </t>
         </is>
       </c>
       <c r="D138" s="4" t="inlineStr">
@@ -4977,7 +4893,7 @@
       </c>
       <c r="C139" s="4" t="inlineStr">
         <is>
-          <t>Сапарбек уулу Эрназар</t>
+          <t xml:space="preserve">Сапарбек уулу Эрназар </t>
         </is>
       </c>
       <c r="D139" s="4" t="inlineStr">
@@ -5009,7 +4925,7 @@
       </c>
       <c r="C140" s="4" t="inlineStr">
         <is>
-          <t>Кармиаев Алексей</t>
+          <t xml:space="preserve">Кармиаев Алексей </t>
         </is>
       </c>
       <c r="D140" s="4" t="inlineStr">
@@ -5041,7 +4957,7 @@
       </c>
       <c r="C141" s="4" t="inlineStr">
         <is>
-          <t>Нуридин кызы Айдай</t>
+          <t xml:space="preserve">Нуридин кызы Айдай </t>
         </is>
       </c>
       <c r="D141" s="4" t="inlineStr">
@@ -5073,7 +4989,7 @@
       </c>
       <c r="C142" s="4" t="inlineStr">
         <is>
-          <t>Нуридинов Уултай</t>
+          <t xml:space="preserve">Нуридинов Уултай </t>
         </is>
       </c>
       <c r="D142" s="4" t="inlineStr">
@@ -5105,7 +5021,7 @@
       </c>
       <c r="C143" s="4" t="inlineStr">
         <is>
-          <t>Бантабаев Амирхамза</t>
+          <t xml:space="preserve">Бантабаев Амирхамза </t>
         </is>
       </c>
       <c r="D143" s="4" t="inlineStr">
@@ -5137,7 +5053,7 @@
       </c>
       <c r="C144" s="4" t="inlineStr">
         <is>
-          <t>Иманалиев Хайдарали</t>
+          <t xml:space="preserve">Иманалиев Хайдарали </t>
         </is>
       </c>
       <c r="D144" s="4" t="inlineStr">
@@ -5169,7 +5085,7 @@
       </c>
       <c r="C145" s="4" t="inlineStr">
         <is>
-          <t>Иманалиев Жайлообай</t>
+          <t xml:space="preserve">Иманалиев Жайлообай </t>
         </is>
       </c>
       <c r="D145" s="4" t="inlineStr">
@@ -5201,7 +5117,7 @@
       </c>
       <c r="C146" s="4" t="inlineStr">
         <is>
-          <t>Имоналиев Бактияр</t>
+          <t xml:space="preserve">Имоналиев Бактияр </t>
         </is>
       </c>
       <c r="D146" s="4" t="inlineStr">
@@ -5233,7 +5149,7 @@
       </c>
       <c r="C147" s="4" t="inlineStr">
         <is>
-          <t>Имомалиев Акылбек</t>
+          <t xml:space="preserve">Имомалиев Акылбек </t>
         </is>
       </c>
       <c r="D147" s="4" t="inlineStr">
@@ -5265,7 +5181,7 @@
       </c>
       <c r="C148" s="4" t="inlineStr">
         <is>
-          <t>Жумабеков Азизбек</t>
+          <t xml:space="preserve">Жумабеков Азизбек </t>
         </is>
       </c>
       <c r="D148" s="4" t="inlineStr">
@@ -5297,7 +5213,7 @@
       </c>
       <c r="C149" s="4" t="inlineStr">
         <is>
-          <t>Чокеев Жанболот</t>
+          <t xml:space="preserve">Чокеев Жанболот </t>
         </is>
       </c>
       <c r="D149" s="4" t="inlineStr">
@@ -5329,7 +5245,7 @@
       </c>
       <c r="C150" s="4" t="inlineStr">
         <is>
-          <t>Камбаралы уулу Манасбек</t>
+          <t xml:space="preserve">Камбаралы уулу Манасбек </t>
         </is>
       </c>
       <c r="D150" s="4" t="inlineStr">
@@ -5361,7 +5277,7 @@
       </c>
       <c r="C151" s="4" t="inlineStr">
         <is>
-          <t>Баялиев Манас Нышанбаевич</t>
+          <t xml:space="preserve">Баялиев Манас Нышанбаевич </t>
         </is>
       </c>
       <c r="D151" s="4" t="inlineStr">
@@ -5393,7 +5309,7 @@
       </c>
       <c r="C152" s="4" t="inlineStr">
         <is>
-          <t>Баялиев Урматбек</t>
+          <t xml:space="preserve">Баялиев Урматбек </t>
         </is>
       </c>
       <c r="D152" s="4" t="inlineStr">
@@ -5425,7 +5341,7 @@
       </c>
       <c r="C153" s="4" t="inlineStr">
         <is>
-          <t>Мадиев Кутман</t>
+          <t xml:space="preserve">Мадиев Кутман </t>
         </is>
       </c>
       <c r="D153" s="4" t="inlineStr">
@@ -5457,7 +5373,7 @@
       </c>
       <c r="C154" s="4" t="inlineStr">
         <is>
-          <t>Казаков Талгат</t>
+          <t xml:space="preserve">Казаков Талгат </t>
         </is>
       </c>
       <c r="D154" s="4" t="inlineStr">
@@ -5489,7 +5405,7 @@
       </c>
       <c r="C155" s="4" t="inlineStr">
         <is>
-          <t>Бектуров Ариет</t>
+          <t xml:space="preserve">Бектуров Ариет </t>
         </is>
       </c>
       <c r="D155" s="4" t="inlineStr">
@@ -5521,7 +5437,7 @@
       </c>
       <c r="C156" s="4" t="inlineStr">
         <is>
-          <t>Шарапидинов Сыймык</t>
+          <t xml:space="preserve">Шарапидинов Сыймык </t>
         </is>
       </c>
       <c r="D156" s="4" t="inlineStr">
@@ -5553,7 +5469,7 @@
       </c>
       <c r="C157" s="4" t="inlineStr">
         <is>
-          <t>Ишенбай уулу Жыргалбек</t>
+          <t xml:space="preserve">Ишенбай уулу Жыргалбек </t>
         </is>
       </c>
       <c r="D157" s="4" t="inlineStr">
@@ -5585,7 +5501,7 @@
       </c>
       <c r="C158" s="4" t="inlineStr">
         <is>
-          <t>Акматов Куштарбек</t>
+          <t xml:space="preserve">Акматов Куштарбек </t>
         </is>
       </c>
       <c r="D158" s="4" t="inlineStr">
@@ -5617,7 +5533,7 @@
       </c>
       <c r="C159" s="4" t="inlineStr">
         <is>
-          <t>Болтаев Бактыбек</t>
+          <t xml:space="preserve">Болтаев Бактыбек </t>
         </is>
       </c>
       <c r="D159" s="4" t="inlineStr">
@@ -5649,7 +5565,7 @@
       </c>
       <c r="C160" s="4" t="inlineStr">
         <is>
-          <t>Камаров Сайфардин</t>
+          <t xml:space="preserve">Камаров Сайфардин </t>
         </is>
       </c>
       <c r="D160" s="4" t="inlineStr">
@@ -5681,7 +5597,7 @@
       </c>
       <c r="C161" s="4" t="inlineStr">
         <is>
-          <t>Таникулов Сулайман</t>
+          <t xml:space="preserve">Таникулов Сулайман </t>
         </is>
       </c>
       <c r="D161" s="4" t="inlineStr">
@@ -5713,7 +5629,7 @@
       </c>
       <c r="C162" s="4" t="inlineStr">
         <is>
-          <t>Махмуджанов Жоробек</t>
+          <t xml:space="preserve">Махмуджанов Жоробек </t>
         </is>
       </c>
       <c r="D162" s="4" t="inlineStr">
@@ -5745,7 +5661,7 @@
       </c>
       <c r="C163" s="4" t="inlineStr">
         <is>
-          <t>Насиров Асланбек Муктарович</t>
+          <t xml:space="preserve">Насиров Асланбек Муктарович </t>
         </is>
       </c>
       <c r="D163" s="4" t="inlineStr">
@@ -5777,7 +5693,7 @@
       </c>
       <c r="C164" s="4" t="inlineStr">
         <is>
-          <t>Насиров Ахматбек Муктарович</t>
+          <t xml:space="preserve">Насиров Ахматбек Муктарович </t>
         </is>
       </c>
       <c r="D164" s="4" t="inlineStr">
@@ -5809,7 +5725,7 @@
       </c>
       <c r="C165" s="4" t="inlineStr">
         <is>
-          <t>Махмудов Мехмасола Хашимович</t>
+          <t xml:space="preserve">Махмудов Мехмасола Хашимович </t>
         </is>
       </c>
       <c r="D165" s="4" t="inlineStr">
@@ -5841,7 +5757,7 @@
       </c>
       <c r="C166" s="4" t="inlineStr">
         <is>
-          <t>Махмудов Хамид Хашимович</t>
+          <t xml:space="preserve">Махмудов Хамид Хашимович </t>
         </is>
       </c>
       <c r="D166" s="4" t="inlineStr">
@@ -5873,7 +5789,7 @@
       </c>
       <c r="C167" s="4" t="inlineStr">
         <is>
-          <t>Мурзаев Кайымжок Бакирович</t>
+          <t xml:space="preserve">Мурзаев Кайымжок Бакирович </t>
         </is>
       </c>
       <c r="D167" s="4" t="inlineStr">
@@ -5905,7 +5821,7 @@
       </c>
       <c r="C168" s="4" t="inlineStr">
         <is>
-          <t>Рыскелди уулу Мирлан</t>
+          <t xml:space="preserve">Рыскелди уулу Мирлан </t>
         </is>
       </c>
       <c r="D168" s="4" t="inlineStr">
@@ -5937,7 +5853,7 @@
       </c>
       <c r="C169" s="4" t="inlineStr">
         <is>
-          <t>Момуналиев Бакыт Мыктыбекович</t>
+          <t xml:space="preserve">Момуналиев Бакыт Мыктыбекович </t>
         </is>
       </c>
       <c r="D169" s="4" t="inlineStr">
@@ -5969,7 +5885,7 @@
       </c>
       <c r="C170" s="4" t="inlineStr">
         <is>
-          <t>Мукалиев Бакыт Токторович</t>
+          <t xml:space="preserve">Мукалиев Бакыт Токторович </t>
         </is>
       </c>
       <c r="D170" s="4" t="inlineStr">
@@ -6001,7 +5917,7 @@
       </c>
       <c r="C171" s="4" t="inlineStr">
         <is>
-          <t>Иманкулов Абиджон Умаркулович</t>
+          <t xml:space="preserve">Иманкулов Абиджон Умаркулович </t>
         </is>
       </c>
       <c r="D171" s="4" t="inlineStr">
@@ -6033,7 +5949,7 @@
       </c>
       <c r="C172" s="4" t="inlineStr">
         <is>
-          <t>Абдылдаев Бекзат Акаарович</t>
+          <t xml:space="preserve">Абдылдаев Бекзат Акаарович </t>
         </is>
       </c>
       <c r="D172" s="4" t="inlineStr">
@@ -6065,7 +5981,7 @@
       </c>
       <c r="C173" s="4" t="inlineStr">
         <is>
-          <t>Тентимишов Автандил Тургунович</t>
+          <t xml:space="preserve">Тентимишов Автандил Тургунович </t>
         </is>
       </c>
       <c r="D173" s="4" t="inlineStr">
@@ -6097,7 +6013,7 @@
       </c>
       <c r="C174" s="4" t="inlineStr">
         <is>
-          <t>Таштемиров Дилмурат</t>
+          <t xml:space="preserve">Таштемиров Дилмурат </t>
         </is>
       </c>
       <c r="D174" s="4" t="inlineStr">
@@ -6129,7 +6045,7 @@
       </c>
       <c r="C175" s="4" t="inlineStr">
         <is>
-          <t>Райымжанова Курсанай</t>
+          <t xml:space="preserve">Райымжанова Курсанай </t>
         </is>
       </c>
       <c r="D175" s="4" t="inlineStr">
@@ -6161,7 +6077,7 @@
       </c>
       <c r="C176" s="4" t="inlineStr">
         <is>
-          <t>Юлдашов Омаджан</t>
+          <t xml:space="preserve">Юлдашов Омаджан </t>
         </is>
       </c>
       <c r="D176" s="4" t="inlineStr">
@@ -6193,7 +6109,7 @@
       </c>
       <c r="C177" s="4" t="inlineStr">
         <is>
-          <t>Мундузов Нурадил</t>
+          <t xml:space="preserve">Мундузов Нурадил </t>
         </is>
       </c>
       <c r="D177" s="4" t="inlineStr">
@@ -6225,7 +6141,7 @@
       </c>
       <c r="C178" s="4" t="inlineStr">
         <is>
-          <t>Мамажанов Бекмамат</t>
+          <t xml:space="preserve">Мамажанов Бекмамат </t>
         </is>
       </c>
       <c r="D178" s="4" t="inlineStr">
@@ -6257,7 +6173,7 @@
       </c>
       <c r="C179" s="4" t="inlineStr">
         <is>
-          <t>Кадыров Усон</t>
+          <t xml:space="preserve">Кадыров Усон </t>
         </is>
       </c>
       <c r="D179" s="4" t="inlineStr">
@@ -6289,7 +6205,7 @@
       </c>
       <c r="C180" s="4" t="inlineStr">
         <is>
-          <t>Арыкбаев Бактияр</t>
+          <t xml:space="preserve">Арыкбаев Бактияр </t>
         </is>
       </c>
       <c r="D180" s="4" t="inlineStr">
@@ -6321,7 +6237,7 @@
       </c>
       <c r="C181" s="4" t="inlineStr">
         <is>
-          <t>Бостонов Мирлан</t>
+          <t xml:space="preserve">Бостонов Мирлан </t>
         </is>
       </c>
       <c r="D181" s="4" t="inlineStr">
@@ -6353,7 +6269,7 @@
       </c>
       <c r="C182" s="4" t="inlineStr">
         <is>
-          <t>Турашов Аскар</t>
+          <t xml:space="preserve">Турашов Аскар </t>
         </is>
       </c>
       <c r="D182" s="4" t="inlineStr">
@@ -6385,7 +6301,7 @@
       </c>
       <c r="C183" s="4" t="inlineStr">
         <is>
-          <t>Сыдыкова Бактыгүл</t>
+          <t xml:space="preserve">Сыдыкова Бактыгуль </t>
         </is>
       </c>
       <c r="D183" s="4" t="inlineStr">
@@ -6417,7 +6333,7 @@
       </c>
       <c r="C184" s="4" t="inlineStr">
         <is>
-          <t>Кааров Алманбет</t>
+          <t xml:space="preserve">Кааров Алманбет </t>
         </is>
       </c>
       <c r="D184" s="4" t="inlineStr">
@@ -6449,7 +6365,7 @@
       </c>
       <c r="C185" s="4" t="inlineStr">
         <is>
-          <t>Курбанов Айбек</t>
+          <t xml:space="preserve">Курбанов Айбек </t>
         </is>
       </c>
       <c r="D185" s="4" t="inlineStr">
@@ -6481,7 +6397,7 @@
       </c>
       <c r="C186" s="4" t="inlineStr">
         <is>
-          <t>Абдрасулов Нурсултан</t>
+          <t xml:space="preserve">Абдрасулов Нурсултан </t>
         </is>
       </c>
       <c r="D186" s="4" t="inlineStr">
@@ -6513,7 +6429,7 @@
       </c>
       <c r="C187" s="4" t="inlineStr">
         <is>
-          <t>Ахунжанов Тойчу</t>
+          <t xml:space="preserve">Ахунжанов Тойчу </t>
         </is>
       </c>
       <c r="D187" s="4" t="inlineStr">
@@ -6545,7 +6461,7 @@
       </c>
       <c r="C188" s="4" t="inlineStr">
         <is>
-          <t>Маматкулов Самаган</t>
+          <t xml:space="preserve">Маматкулов Самаган </t>
         </is>
       </c>
       <c r="D188" s="4" t="inlineStr">
@@ -6577,7 +6493,7 @@
       </c>
       <c r="C189" s="4" t="inlineStr">
         <is>
-          <t>Тешебаев Абдулхамид</t>
+          <t xml:space="preserve">Тешебаев Абдулхамид </t>
         </is>
       </c>
       <c r="D189" s="4" t="inlineStr">
@@ -6609,7 +6525,7 @@
       </c>
       <c r="C190" s="4" t="inlineStr">
         <is>
-          <t>Момуналиев Бектурсун</t>
+          <t xml:space="preserve">Момуналиев Бектурсун </t>
         </is>
       </c>
       <c r="D190" s="4" t="inlineStr">
@@ -6641,7 +6557,7 @@
       </c>
       <c r="C191" s="4" t="inlineStr">
         <is>
-          <t>Полотов Умарбек</t>
+          <t xml:space="preserve">Полотов Умарбек </t>
         </is>
       </c>
       <c r="D191" s="4" t="inlineStr">
@@ -6673,7 +6589,7 @@
       </c>
       <c r="C192" s="13" t="inlineStr">
         <is>
-          <t>Ашираев Суймонкул</t>
+          <t xml:space="preserve">Ашираев Суймонкул </t>
         </is>
       </c>
       <c r="D192" s="15" t="inlineStr">
@@ -6705,7 +6621,7 @@
       </c>
       <c r="C193" s="13" t="inlineStr">
         <is>
-          <t>Аттокуров Заур</t>
+          <t xml:space="preserve">Аттокуров Заур </t>
         </is>
       </c>
       <c r="D193" s="15" t="inlineStr">
@@ -6737,7 +6653,7 @@
       </c>
       <c r="C194" s="13" t="inlineStr">
         <is>
-          <t>Баратов Роман</t>
+          <t xml:space="preserve">Баратов Роман </t>
         </is>
       </c>
       <c r="D194" s="15" t="inlineStr">
@@ -6769,7 +6685,7 @@
       </c>
       <c r="C195" s="13" t="inlineStr">
         <is>
-          <t>Быржыбаев Кубанычбек</t>
+          <t xml:space="preserve">Быржыбаев Кубанычбек </t>
         </is>
       </c>
       <c r="D195" s="15" t="inlineStr">
@@ -6801,7 +6717,7 @@
       </c>
       <c r="C196" s="13" t="inlineStr">
         <is>
-          <t>Календеров Нурали</t>
+          <t xml:space="preserve">Календеров Нурали </t>
         </is>
       </c>
       <c r="D196" s="15" t="inlineStr">
@@ -6833,7 +6749,7 @@
       </c>
       <c r="C197" s="13" t="inlineStr">
         <is>
-          <t>Кушуев Беку</t>
+          <t xml:space="preserve">Кушуев Беку </t>
         </is>
       </c>
       <c r="D197" s="15" t="inlineStr">
@@ -6865,7 +6781,7 @@
       </c>
       <c r="C198" s="13" t="inlineStr">
         <is>
-          <t>Курманалиев Алтынбек</t>
+          <t xml:space="preserve">Курманалиев Алтынбек </t>
         </is>
       </c>
       <c r="D198" s="15" t="inlineStr">
@@ -6897,7 +6813,7 @@
       </c>
       <c r="C199" s="13" t="inlineStr">
         <is>
-          <t>Сайназаров Бакыт</t>
+          <t xml:space="preserve">Сайназаров Бакыт </t>
         </is>
       </c>
       <c r="D199" s="15" t="inlineStr">
@@ -6929,7 +6845,7 @@
       </c>
       <c r="C200" s="13" t="inlineStr">
         <is>
-          <t>Токтоматов Ырыскелди</t>
+          <t xml:space="preserve">Токтоматов Ырыскелди </t>
         </is>
       </c>
       <c r="D200" s="15" t="inlineStr">
@@ -6993,7 +6909,7 @@
       </c>
       <c r="C202" s="13" t="inlineStr">
         <is>
-          <t>Шамшиев Белик</t>
+          <t xml:space="preserve">Шамшиев Белик </t>
         </is>
       </c>
       <c r="D202" s="15" t="inlineStr">
@@ -7025,7 +6941,7 @@
       </c>
       <c r="C203" s="13" t="inlineStr">
         <is>
-          <t>Жунусов Кутманали</t>
+          <t xml:space="preserve">Жунусов Кутманали </t>
         </is>
       </c>
       <c r="D203" s="15" t="inlineStr">
@@ -7057,7 +6973,7 @@
       </c>
       <c r="C204" s="13" t="inlineStr">
         <is>
-          <t>Байсалов Орозбек</t>
+          <t xml:space="preserve">Байсалов Орозбек </t>
         </is>
       </c>
       <c r="D204" s="13" t="inlineStr">
@@ -7089,7 +7005,7 @@
       </c>
       <c r="C205" s="13" t="inlineStr">
         <is>
-          <t>Байсалов Тууганбек</t>
+          <t xml:space="preserve">Байсалов Тууганбек </t>
         </is>
       </c>
       <c r="D205" s="13" t="inlineStr">
@@ -7121,7 +7037,7 @@
       </c>
       <c r="C206" s="13" t="inlineStr">
         <is>
-          <t>Кубанычбек уулу Тынарбек</t>
+          <t xml:space="preserve">Кубанычбек уулу Тынарбек </t>
         </is>
       </c>
       <c r="D206" s="13" t="inlineStr">
@@ -7153,7 +7069,7 @@
       </c>
       <c r="C207" s="13" t="inlineStr">
         <is>
-          <t>Нурдинов Данияр</t>
+          <t xml:space="preserve">Нурдинов Данияр </t>
         </is>
       </c>
       <c r="D207" s="13" t="inlineStr">
@@ -7185,7 +7101,7 @@
       </c>
       <c r="C208" s="13" t="inlineStr">
         <is>
-          <t>Дегтяников Евгений</t>
+          <t xml:space="preserve">Дегтяников Евгений </t>
         </is>
       </c>
       <c r="D208" s="13" t="inlineStr">
@@ -7217,7 +7133,7 @@
       </c>
       <c r="C209" s="13" t="inlineStr">
         <is>
-          <t>Абдиев Урмат</t>
+          <t xml:space="preserve">Абдиев Урмат </t>
         </is>
       </c>
       <c r="D209" s="13" t="inlineStr">
@@ -7249,7 +7165,7 @@
       </c>
       <c r="C210" s="13" t="inlineStr">
         <is>
-          <t>Жумак уулу Максат</t>
+          <t xml:space="preserve">Жумак уулу Максат </t>
         </is>
       </c>
       <c r="D210" s="13" t="inlineStr">
@@ -7281,7 +7197,7 @@
       </c>
       <c r="C211" s="13" t="inlineStr">
         <is>
-          <t>Тургумбаев Бакытбек</t>
+          <t xml:space="preserve">Тургумбаев Бакытбек </t>
         </is>
       </c>
       <c r="D211" s="13" t="inlineStr">
@@ -7313,7 +7229,7 @@
       </c>
       <c r="C212" s="4" t="inlineStr">
         <is>
-          <t>Афлетонов Сергей</t>
+          <t xml:space="preserve">Афлетонов Сергей </t>
         </is>
       </c>
       <c r="D212" s="13" t="inlineStr">
@@ -7345,7 +7261,7 @@
       </c>
       <c r="C213" s="4" t="inlineStr">
         <is>
-          <t>Литвиненко Андрей</t>
+          <t xml:space="preserve">Литвиненко Андрей </t>
         </is>
       </c>
       <c r="D213" s="13" t="inlineStr">
@@ -7377,7 +7293,7 @@
       </c>
       <c r="C214" s="4" t="inlineStr">
         <is>
-          <t>Иргашев Шодиер</t>
+          <t xml:space="preserve">Иргашев Шодиер </t>
         </is>
       </c>
       <c r="D214" s="13" t="inlineStr">
@@ -7409,7 +7325,7 @@
       </c>
       <c r="C215" s="4" t="inlineStr">
         <is>
-          <t>Крюков Денис</t>
+          <t xml:space="preserve">Крюков Денис </t>
         </is>
       </c>
       <c r="D215" s="13" t="inlineStr">
@@ -7441,7 +7357,7 @@
       </c>
       <c r="C216" s="4" t="inlineStr">
         <is>
-          <t>Мамбетбаев Бактыбек</t>
+          <t xml:space="preserve">Мамбетбаев Бактыбек </t>
         </is>
       </c>
       <c r="D216" s="13" t="inlineStr">
@@ -7473,7 +7389,7 @@
       </c>
       <c r="C217" s="4" t="inlineStr">
         <is>
-          <t>Матанов Данияр</t>
+          <t xml:space="preserve">Матанов Данияр </t>
         </is>
       </c>
       <c r="D217" s="13" t="inlineStr">
@@ -7505,7 +7421,7 @@
       </c>
       <c r="C218" s="4" t="inlineStr">
         <is>
-          <t>Макеев Канат</t>
+          <t xml:space="preserve">Макеев Канат </t>
         </is>
       </c>
       <c r="D218" s="13" t="inlineStr">
@@ -7537,7 +7453,7 @@
       </c>
       <c r="C219" s="4" t="inlineStr">
         <is>
-          <t>Хорченко Дмитрий</t>
+          <t xml:space="preserve">Хорченко Дмитрий </t>
         </is>
       </c>
       <c r="D219" s="13" t="inlineStr">
@@ -7569,7 +7485,7 @@
       </c>
       <c r="C220" s="4" t="inlineStr">
         <is>
-          <t>Чымырбаев Максат</t>
+          <t xml:space="preserve">Чымырбаев Максат </t>
         </is>
       </c>
       <c r="D220" s="13" t="inlineStr">
@@ -7601,7 +7517,7 @@
       </c>
       <c r="C221" s="4" t="inlineStr">
         <is>
-          <t>Лянахунов Шакир</t>
+          <t xml:space="preserve">Лянахунов Шакир </t>
         </is>
       </c>
       <c r="D221" s="13" t="inlineStr">
@@ -7633,12 +7549,12 @@
       </c>
       <c r="C222" s="4" t="inlineStr">
         <is>
-          <t>Каипова Элмира</t>
+          <t xml:space="preserve">Каипова Элмира </t>
         </is>
       </c>
       <c r="D222" s="4" t="inlineStr">
         <is>
-          <t>Швея с умением кроить 3-4 разряда</t>
+          <t xml:space="preserve">"Портной с умением кроить" 3-4 разряда </t>
         </is>
       </c>
       <c r="E222" s="4" t="inlineStr">
@@ -7665,12 +7581,12 @@
       </c>
       <c r="C223" s="4" t="inlineStr">
         <is>
-          <t>Кадирберди кызы Махиро</t>
+          <t xml:space="preserve">Кадирберди кызы Махиро </t>
         </is>
       </c>
       <c r="D223" s="4" t="inlineStr">
         <is>
-          <t>Швея с умением кроить 3-4 разряда</t>
+          <t xml:space="preserve">"Портной с умением кроить" 3-4 разряда </t>
         </is>
       </c>
       <c r="E223" s="4" t="inlineStr">
@@ -7697,12 +7613,12 @@
       </c>
       <c r="C224" s="4" t="inlineStr">
         <is>
-          <t>Марупова Зарифахан</t>
+          <t xml:space="preserve">Марупова Зарифахан </t>
         </is>
       </c>
       <c r="D224" s="4" t="inlineStr">
         <is>
-          <t>Швея с умением кроить 3-4 разряда</t>
+          <t xml:space="preserve">"Портной с умением кроить" 3-4 разряда </t>
         </is>
       </c>
       <c r="E224" s="4" t="inlineStr">
@@ -7729,12 +7645,12 @@
       </c>
       <c r="C225" s="4" t="inlineStr">
         <is>
-          <t>Хайруллаева Турсунай</t>
+          <t xml:space="preserve">Хайруллаева Турсунай </t>
         </is>
       </c>
       <c r="D225" s="4" t="inlineStr">
         <is>
-          <t>Швея с умением кроить 3-4 разряда</t>
+          <t xml:space="preserve">"Портной с умением кроить" 3-4 разряда </t>
         </is>
       </c>
       <c r="E225" s="4" t="inlineStr">
@@ -7761,12 +7677,12 @@
       </c>
       <c r="C226" s="4" t="inlineStr">
         <is>
-          <t>Абдурамитова Айкол</t>
+          <t xml:space="preserve">Абдурамитова Айкол </t>
         </is>
       </c>
       <c r="D226" s="4" t="inlineStr">
         <is>
-          <t>Швея с умением кроить 3-4 разряда</t>
+          <t xml:space="preserve">"Портной с умением кроить" 3-4 разряда </t>
         </is>
       </c>
       <c r="E226" s="4" t="inlineStr">
@@ -7793,12 +7709,12 @@
       </c>
       <c r="C227" s="4" t="inlineStr">
         <is>
-          <t>Элинжан кызы Айчурок</t>
+          <t xml:space="preserve">Элинжан кызы Айчурок </t>
         </is>
       </c>
       <c r="D227" s="4" t="inlineStr">
         <is>
-          <t>Швея с умением кроить 3-4 разряда</t>
+          <t xml:space="preserve">"Портной с умением кроить" 3-4 разряда </t>
         </is>
       </c>
       <c r="E227" s="4" t="inlineStr">
@@ -7825,12 +7741,12 @@
       </c>
       <c r="C228" s="4" t="inlineStr">
         <is>
-          <t>Эржин кызы Асылкан</t>
+          <t xml:space="preserve">Эржин кызы Асылкан </t>
         </is>
       </c>
       <c r="D228" s="4" t="inlineStr">
         <is>
-          <t>Швея с умением кроить 3-4 разряда</t>
+          <t xml:space="preserve">"Портной с умением кроить" 3-4 разряда </t>
         </is>
       </c>
       <c r="E228" s="4" t="inlineStr">
@@ -7857,12 +7773,12 @@
       </c>
       <c r="C229" s="4" t="inlineStr">
         <is>
-          <t>Дажап кызы Азиза</t>
+          <t xml:space="preserve">Дажап кызы Азиза </t>
         </is>
       </c>
       <c r="D229" s="4" t="inlineStr">
         <is>
-          <t>Швея с умением кроить 3-4 разряда</t>
+          <t xml:space="preserve">"Портной с умением кроить" 3-4 разряда </t>
         </is>
       </c>
       <c r="E229" s="4" t="inlineStr">
@@ -7889,12 +7805,12 @@
       </c>
       <c r="C230" s="4" t="inlineStr">
         <is>
-          <t>Рустамова Кыздархан</t>
+          <t xml:space="preserve">Рустамова Кыздархан </t>
         </is>
       </c>
       <c r="D230" s="4" t="inlineStr">
         <is>
-          <t>Швея с умением кроить 3-4 разряда</t>
+          <t xml:space="preserve">"Портной с умением кроить" 3-4 разряда </t>
         </is>
       </c>
       <c r="E230" s="4" t="inlineStr">
@@ -7921,12 +7837,12 @@
       </c>
       <c r="C231" s="4" t="inlineStr">
         <is>
-          <t>Акматова Назгүл</t>
+          <t xml:space="preserve">Акматова Назгуль </t>
         </is>
       </c>
       <c r="D231" s="4" t="inlineStr">
         <is>
-          <t>Швея с умением кроить 3-4 разряда</t>
+          <t xml:space="preserve">"Портной с умением кроить" 3-4 разряда </t>
         </is>
       </c>
       <c r="E231" s="4" t="inlineStr">
@@ -7953,12 +7869,12 @@
       </c>
       <c r="C232" s="4" t="inlineStr">
         <is>
-          <t>Саламбек кыз Мираида</t>
+          <t xml:space="preserve">Саламбек кыз Мираида </t>
         </is>
       </c>
       <c r="D232" s="4" t="inlineStr">
         <is>
-          <t>Швея с умением кроить 3-4 разряда</t>
+          <t xml:space="preserve">"Портной с умением кроить" 3-4 разряда </t>
         </is>
       </c>
       <c r="E232" s="4" t="inlineStr">
@@ -7985,12 +7901,12 @@
       </c>
       <c r="C233" s="4" t="inlineStr">
         <is>
-          <t>Длавалдиева Нилуфар</t>
+          <t xml:space="preserve">Длавалдиева Нилуфар </t>
         </is>
       </c>
       <c r="D233" s="4" t="inlineStr">
         <is>
-          <t>Швея с умением кроить 3-4 разряда</t>
+          <t xml:space="preserve">"Портной с умением кроить" 3-4 разряда </t>
         </is>
       </c>
       <c r="E233" s="4" t="inlineStr">
@@ -8017,12 +7933,12 @@
       </c>
       <c r="C234" s="4" t="inlineStr">
         <is>
-          <t>Асанова Рахима</t>
+          <t xml:space="preserve">Асанова Рахима </t>
         </is>
       </c>
       <c r="D234" s="4" t="inlineStr">
         <is>
-          <t>Швея с умением кроить 3-4 разряда</t>
+          <t xml:space="preserve">"Портной с умением кроить" 3-4 разряда </t>
         </is>
       </c>
       <c r="E234" s="4" t="inlineStr">
@@ -8049,12 +7965,12 @@
       </c>
       <c r="C235" s="4" t="inlineStr">
         <is>
-          <t>Бегжалова Айнаш</t>
+          <t xml:space="preserve">Бегжалова Айнаш </t>
         </is>
       </c>
       <c r="D235" s="4" t="inlineStr">
         <is>
-          <t>Швея с умением кроить 3-4 разряда</t>
+          <t xml:space="preserve">"Портной с умением кроить" 3-4 разряда </t>
         </is>
       </c>
       <c r="E235" s="4" t="inlineStr">
@@ -8081,12 +7997,12 @@
       </c>
       <c r="C236" s="4" t="inlineStr">
         <is>
-          <t>Ахунжанова Зарифахан</t>
+          <t xml:space="preserve">Ахунжанова Зарифахан </t>
         </is>
       </c>
       <c r="D236" s="4" t="inlineStr">
         <is>
-          <t>Швея с умением кроить 3-4 разряда</t>
+          <t xml:space="preserve">"Портной с умением кроить" 3-4 разряда </t>
         </is>
       </c>
       <c r="E236" s="4" t="inlineStr">
@@ -8113,12 +8029,12 @@
       </c>
       <c r="C237" s="4" t="inlineStr">
         <is>
-          <t>Марупова Замирахон</t>
+          <t xml:space="preserve">Марупова Замирахон </t>
         </is>
       </c>
       <c r="D237" s="4" t="inlineStr">
         <is>
-          <t>Швея с умением кроить 3-4 разряда</t>
+          <t xml:space="preserve">"Портной с умением кроить" 3-4 разряда </t>
         </is>
       </c>
       <c r="E237" s="4" t="inlineStr">
@@ -8145,12 +8061,12 @@
       </c>
       <c r="C238" s="4" t="inlineStr">
         <is>
-          <t>Миркадырова Нилюпар</t>
+          <t xml:space="preserve">Миркадырова Нилюпар </t>
         </is>
       </c>
       <c r="D238" s="4" t="inlineStr">
         <is>
-          <t>Швея с умением кроить 3-4 разряда</t>
+          <t xml:space="preserve">"Портной с умением кроить" 3-4 разряда </t>
         </is>
       </c>
       <c r="E238" s="4" t="inlineStr">
@@ -8182,7 +8098,7 @@
       </c>
       <c r="D239" s="4" t="inlineStr">
         <is>
-          <t>Швея с умением кроить 3-4 разряда</t>
+          <t xml:space="preserve">"Портной с умением кроить" 3-4 разряда </t>
         </is>
       </c>
       <c r="E239" s="4" t="inlineStr">
@@ -8209,12 +8125,12 @@
       </c>
       <c r="C240" s="4" t="inlineStr">
         <is>
-          <t>Абдурахманова Сарвиноз</t>
+          <t xml:space="preserve">Абдурахманова Сарвиноз </t>
         </is>
       </c>
       <c r="D240" s="4" t="inlineStr">
         <is>
-          <t>Швея с умением кроить 3-4 разряда</t>
+          <t xml:space="preserve">"Портной с умением кроить" 3-4 разряда </t>
         </is>
       </c>
       <c r="E240" s="4" t="inlineStr">
@@ -8241,12 +8157,12 @@
       </c>
       <c r="C241" s="4" t="inlineStr">
         <is>
-          <t>Атаева Нурхон</t>
+          <t xml:space="preserve">Атаева Нурхон </t>
         </is>
       </c>
       <c r="D241" s="4" t="inlineStr">
         <is>
-          <t>Швея с умением кроить 3-4 разряда</t>
+          <t xml:space="preserve">"Портной с умением кроить" 3-4 разряда </t>
         </is>
       </c>
       <c r="E241" s="4" t="inlineStr">
@@ -8273,12 +8189,12 @@
       </c>
       <c r="C242" s="4" t="inlineStr">
         <is>
-          <t>Абсатарова Шарифа</t>
+          <t xml:space="preserve">Абсатарова Шарифа </t>
         </is>
       </c>
       <c r="D242" s="4" t="inlineStr">
         <is>
-          <t>Швея с умением кроить 3-4 разряда</t>
+          <t xml:space="preserve">"Портной с умением кроить" 3-4 разряда </t>
         </is>
       </c>
       <c r="E242" s="4" t="inlineStr">
@@ -8305,12 +8221,12 @@
       </c>
       <c r="C243" s="4" t="inlineStr">
         <is>
-          <t>Хожимаматова Ирода</t>
+          <t xml:space="preserve">Хожимаматова Ирода </t>
         </is>
       </c>
       <c r="D243" s="4" t="inlineStr">
         <is>
-          <t>Швея с умением кроить 3-4 разряда</t>
+          <t xml:space="preserve">"Портной с умением кроить" 3-4 разряда </t>
         </is>
       </c>
       <c r="E243" s="4" t="inlineStr">
@@ -8337,12 +8253,12 @@
       </c>
       <c r="C244" s="4" t="inlineStr">
         <is>
-          <t>Райназарова Мафтура</t>
+          <t xml:space="preserve">Райназарова Мафтура </t>
         </is>
       </c>
       <c r="D244" s="4" t="inlineStr">
         <is>
-          <t>Швея с умением кроить 3-4 разряда</t>
+          <t xml:space="preserve">"Портной с умением кроить" 3-4 разряда </t>
         </is>
       </c>
       <c r="E244" s="4" t="inlineStr">
@@ -8369,12 +8285,12 @@
       </c>
       <c r="C245" s="4" t="inlineStr">
         <is>
-          <t>Хакимова Хадичабону</t>
+          <t xml:space="preserve">Хакимова Хадичабону </t>
         </is>
       </c>
       <c r="D245" s="4" t="inlineStr">
         <is>
-          <t>Швея с умением кроить 3-4 разряда</t>
+          <t xml:space="preserve">"Портной с умением кроить" 3-4 разряда </t>
         </is>
       </c>
       <c r="E245" s="4" t="inlineStr">
@@ -8401,12 +8317,12 @@
       </c>
       <c r="C246" s="4" t="inlineStr">
         <is>
-          <t>Мадымарова Муххабат</t>
+          <t xml:space="preserve">Мадымарова Муххабат </t>
         </is>
       </c>
       <c r="D246" s="4" t="inlineStr">
         <is>
-          <t>Швея с умением кроить 3-4 разряда</t>
+          <t xml:space="preserve">"Портной с умением кроить" 3-4 разряда </t>
         </is>
       </c>
       <c r="E246" s="4" t="inlineStr">
@@ -8433,12 +8349,12 @@
       </c>
       <c r="C247" s="4" t="inlineStr">
         <is>
-          <t>Абдыкеримова Нурила</t>
+          <t xml:space="preserve">Абдыкеримова Нурила </t>
         </is>
       </c>
       <c r="D247" s="4" t="inlineStr">
         <is>
-          <t>Швея с умением кроить 3-4 разряда</t>
+          <t xml:space="preserve">"Портной с умением кроить" 3-4 разряда </t>
         </is>
       </c>
       <c r="E247" s="4" t="inlineStr">
@@ -8465,12 +8381,12 @@
       </c>
       <c r="C248" s="4" t="inlineStr">
         <is>
-          <t>Абдимажит кызы Жумагул</t>
+          <t xml:space="preserve">Абдимажит кызы Жумагул </t>
         </is>
       </c>
       <c r="D248" s="4" t="inlineStr">
         <is>
-          <t>Швея с умением кроить 3-4 разряда</t>
+          <t xml:space="preserve">"Портной с умением кроить" 3-4 разряда </t>
         </is>
       </c>
       <c r="E248" s="4" t="inlineStr">
@@ -8497,12 +8413,12 @@
       </c>
       <c r="C249" s="4" t="inlineStr">
         <is>
-          <t>Акылбек кызы Айгерим</t>
+          <t xml:space="preserve">Акылбек кызы Айгерим </t>
         </is>
       </c>
       <c r="D249" s="4" t="inlineStr">
         <is>
-          <t>Швея с умением кроить 3-4 разряда</t>
+          <t xml:space="preserve">"Портной с умением кроить" 3-4 разряда </t>
         </is>
       </c>
       <c r="E249" s="4" t="inlineStr">
@@ -8529,12 +8445,12 @@
       </c>
       <c r="C250" s="4" t="inlineStr">
         <is>
-          <t>Аматова Айбурак</t>
+          <t xml:space="preserve">Аматова Айбурак </t>
         </is>
       </c>
       <c r="D250" s="4" t="inlineStr">
         <is>
-          <t>Швея с умением кроить 3-4 разряда</t>
+          <t xml:space="preserve">"Портной с умением кроить" 3-4 разряда </t>
         </is>
       </c>
       <c r="E250" s="4" t="inlineStr">
@@ -8561,12 +8477,12 @@
       </c>
       <c r="C251" s="4" t="inlineStr">
         <is>
-          <t>Дадашова Элиза</t>
+          <t xml:space="preserve">Дадашова Элиза </t>
         </is>
       </c>
       <c r="D251" s="4" t="inlineStr">
         <is>
-          <t>Швея с умением кроить 3-4 разряда</t>
+          <t xml:space="preserve">"Портной с умением кроить" 3-4 разряда </t>
         </is>
       </c>
       <c r="E251" s="4" t="inlineStr">
@@ -8593,12 +8509,12 @@
       </c>
       <c r="C252" s="4" t="inlineStr">
         <is>
-          <t>Жоробекова Гүлзада</t>
+          <t xml:space="preserve">Жоробекова Гулзада </t>
         </is>
       </c>
       <c r="D252" s="4" t="inlineStr">
         <is>
-          <t>Швея с умением кроить 3-4 разряда</t>
+          <t xml:space="preserve">"Портной с умением кроить" 3-4 разряда </t>
         </is>
       </c>
       <c r="E252" s="4" t="inlineStr">
@@ -8630,7 +8546,7 @@
       </c>
       <c r="D253" s="4" t="inlineStr">
         <is>
-          <t>Швея с умением кроить 3-4 разряда</t>
+          <t xml:space="preserve">"Портной с умением кроить" 3-4 разряда </t>
         </is>
       </c>
       <c r="E253" s="4" t="inlineStr">
@@ -8657,12 +8573,12 @@
       </c>
       <c r="C254" s="4" t="inlineStr">
         <is>
-          <t>Козубаева Айсалкын</t>
+          <t xml:space="preserve">Козубаева Айсалкын </t>
         </is>
       </c>
       <c r="D254" s="4" t="inlineStr">
         <is>
-          <t>Швея с умением кроить 3-4 разряда</t>
+          <t xml:space="preserve">"Портной с умением кроить" 3-4 разряда </t>
         </is>
       </c>
       <c r="E254" s="4" t="inlineStr">
@@ -8689,12 +8605,12 @@
       </c>
       <c r="C255" s="4" t="inlineStr">
         <is>
-          <t>Маматшукур кызы Канышай</t>
+          <t xml:space="preserve">Маматшукур кызы Канышай </t>
         </is>
       </c>
       <c r="D255" s="4" t="inlineStr">
         <is>
-          <t>Швея с умением кроить 3-4 разряда</t>
+          <t xml:space="preserve">"Портной с умением кроить" 3-4 разряда </t>
         </is>
       </c>
       <c r="E255" s="4" t="inlineStr">
@@ -8721,12 +8637,12 @@
       </c>
       <c r="C256" s="4" t="inlineStr">
         <is>
-          <t>Мусакоджаева Махабат</t>
+          <t xml:space="preserve">Мусакоджаева Махабат </t>
         </is>
       </c>
       <c r="D256" s="4" t="inlineStr">
         <is>
-          <t>Швея с умением кроить 3-4 разряда</t>
+          <t xml:space="preserve">"Портной с умением кроить" 3-4 разряда </t>
         </is>
       </c>
       <c r="E256" s="4" t="inlineStr">
@@ -8753,12 +8669,12 @@
       </c>
       <c r="C257" s="4" t="inlineStr">
         <is>
-          <t>Дахманова Венера</t>
+          <t xml:space="preserve">Дахманова Венера </t>
         </is>
       </c>
       <c r="D257" s="4" t="inlineStr">
         <is>
-          <t>Швея с умением кроить 3-4 разряда</t>
+          <t xml:space="preserve">"Портной с умением кроить" 3-4 разряда </t>
         </is>
       </c>
       <c r="E257" s="4" t="inlineStr">
@@ -8790,7 +8706,7 @@
       </c>
       <c r="D258" s="4" t="inlineStr">
         <is>
-          <t>Швея с умением кроить 3-4 разряда</t>
+          <t xml:space="preserve">"Портной с умением кроить" 3-4 разряда </t>
         </is>
       </c>
       <c r="E258" s="4" t="inlineStr">
@@ -8817,12 +8733,12 @@
       </c>
       <c r="C259" s="4" t="inlineStr">
         <is>
-          <t>Эназарова Кутбу</t>
+          <t xml:space="preserve">Эназарова Кутбу </t>
         </is>
       </c>
       <c r="D259" s="4" t="inlineStr">
         <is>
-          <t>Швея с умением кроить 3-4 разряда</t>
+          <t xml:space="preserve">"Портной с умением кроить" 3-4 разряда </t>
         </is>
       </c>
       <c r="E259" s="4" t="inlineStr">
@@ -8849,12 +8765,12 @@
       </c>
       <c r="C260" s="4" t="inlineStr">
         <is>
-          <t>Юлдашова Замира</t>
+          <t xml:space="preserve">Юлдашова Замира </t>
         </is>
       </c>
       <c r="D260" s="4" t="inlineStr">
         <is>
-          <t>Швея с умением кроить 3-4 разряда</t>
+          <t xml:space="preserve">"Портной с умением кроить" 3-4 разряда </t>
         </is>
       </c>
       <c r="E260" s="4" t="inlineStr">
@@ -8881,7 +8797,7 @@
       </c>
       <c r="C261" s="4" t="inlineStr">
         <is>
-          <t>Арыкова Мээрим</t>
+          <t xml:space="preserve">Арыкова Мээрим </t>
         </is>
       </c>
       <c r="D261" s="4" t="inlineStr">
@@ -8913,7 +8829,7 @@
       </c>
       <c r="C262" s="4" t="inlineStr">
         <is>
-          <t>Бекбоева Алина</t>
+          <t xml:space="preserve">Бекбоева Алина </t>
         </is>
       </c>
       <c r="D262" s="4" t="inlineStr">
@@ -8945,7 +8861,7 @@
       </c>
       <c r="C263" s="4" t="inlineStr">
         <is>
-          <t>Дуйшенбиева Нуриза</t>
+          <t xml:space="preserve">Дуйшенбиева Нуриза </t>
         </is>
       </c>
       <c r="D263" s="4" t="inlineStr">
@@ -8977,7 +8893,7 @@
       </c>
       <c r="C264" s="4" t="inlineStr">
         <is>
-          <t>Жумабаева Айзада</t>
+          <t xml:space="preserve">Жумабаева Айзада </t>
         </is>
       </c>
       <c r="D264" s="4" t="inlineStr">
@@ -9009,7 +8925,7 @@
       </c>
       <c r="C265" s="4" t="inlineStr">
         <is>
-          <t>Аманова Назгүл</t>
+          <t>Аманова Назгул</t>
         </is>
       </c>
       <c r="D265" s="4" t="inlineStr">
@@ -9041,7 +8957,7 @@
       </c>
       <c r="C266" s="4" t="inlineStr">
         <is>
-          <t>Кыдырова Назгүл</t>
+          <t xml:space="preserve">Кыдырова Назгуль </t>
         </is>
       </c>
       <c r="D266" s="4" t="inlineStr">
@@ -9073,7 +8989,7 @@
       </c>
       <c r="C267" s="4" t="inlineStr">
         <is>
-          <t>Джыргалбаева Ирина</t>
+          <t xml:space="preserve">Джыргалбаева Ирина </t>
         </is>
       </c>
       <c r="D267" s="4" t="inlineStr">
@@ -9105,7 +9021,7 @@
       </c>
       <c r="C268" s="4" t="inlineStr">
         <is>
-          <t>Айнилчиева Жыпаргүл</t>
+          <t>Айнилчиева Жыпаргул</t>
         </is>
       </c>
       <c r="D268" s="4" t="inlineStr">
@@ -9201,7 +9117,7 @@
       </c>
       <c r="C271" s="4" t="inlineStr">
         <is>
-          <t>Абдыкалыкова Роза</t>
+          <t xml:space="preserve">Абдыкалыкова Роза </t>
         </is>
       </c>
       <c r="D271" s="4" t="inlineStr">
@@ -9233,7 +9149,7 @@
       </c>
       <c r="C272" s="4" t="inlineStr">
         <is>
-          <t>Жанызакова Манзурат</t>
+          <t xml:space="preserve">Жанызакова Манзурат </t>
         </is>
       </c>
       <c r="D272" s="4" t="inlineStr">
@@ -9265,7 +9181,7 @@
       </c>
       <c r="C273" s="4" t="inlineStr">
         <is>
-          <t>Мамбетова Айнура</t>
+          <t xml:space="preserve">Мамбетова Айнура </t>
         </is>
       </c>
       <c r="D273" s="4" t="inlineStr">
@@ -9297,7 +9213,7 @@
       </c>
       <c r="C274" s="4" t="inlineStr">
         <is>
-          <t>Омельченко Елена</t>
+          <t xml:space="preserve">Омельченко Елена </t>
         </is>
       </c>
       <c r="D274" s="4" t="inlineStr">
@@ -9329,7 +9245,7 @@
       </c>
       <c r="C275" s="4" t="inlineStr">
         <is>
-          <t>Жеребцова Надежда</t>
+          <t xml:space="preserve">Жеребцова Надежда </t>
         </is>
       </c>
       <c r="D275" s="4" t="inlineStr">
@@ -9393,7 +9309,7 @@
       </c>
       <c r="C277" s="4" t="inlineStr">
         <is>
-          <t>Азизова Гүлмира</t>
+          <t xml:space="preserve">Азизова Гульмира </t>
         </is>
       </c>
       <c r="D277" s="4" t="inlineStr">
@@ -9425,7 +9341,7 @@
       </c>
       <c r="C278" s="4" t="inlineStr">
         <is>
-          <t>Малькова Наталья</t>
+          <t xml:space="preserve">Малькова Наталья </t>
         </is>
       </c>
       <c r="D278" s="4" t="inlineStr">
@@ -9457,7 +9373,7 @@
       </c>
       <c r="C279" s="4" t="inlineStr">
         <is>
-          <t>Асаналиева Бактыгүл</t>
+          <t xml:space="preserve">Асаналиева Бактыгуль </t>
         </is>
       </c>
       <c r="D279" s="4" t="inlineStr">
@@ -9489,7 +9405,7 @@
       </c>
       <c r="C280" s="4" t="inlineStr">
         <is>
-          <t>Шергазиева Нагима</t>
+          <t xml:space="preserve">Шергазиева Нагима </t>
         </is>
       </c>
       <c r="D280" s="4" t="inlineStr">
@@ -9521,7 +9437,7 @@
       </c>
       <c r="C281" s="4" t="inlineStr">
         <is>
-          <t>Кенжебаева Дамира</t>
+          <t xml:space="preserve">Кенжебаева Дамира </t>
         </is>
       </c>
       <c r="D281" s="4" t="inlineStr">
@@ -9553,7 +9469,7 @@
       </c>
       <c r="C282" s="4" t="inlineStr">
         <is>
-          <t>Улнурбекова Жаныл</t>
+          <t xml:space="preserve">Улнурбекова Жаныл </t>
         </is>
       </c>
       <c r="D282" s="4" t="inlineStr">
@@ -9585,7 +9501,7 @@
       </c>
       <c r="C283" s="4" t="inlineStr">
         <is>
-          <t>Амангельдиева Алиля</t>
+          <t xml:space="preserve">Амангельдиева Алиля </t>
         </is>
       </c>
       <c r="D283" s="4" t="inlineStr">
@@ -9617,7 +9533,7 @@
       </c>
       <c r="C284" s="4" t="inlineStr">
         <is>
-          <t>Налимова Анна</t>
+          <t xml:space="preserve">Налимова Анна </t>
         </is>
       </c>
       <c r="D284" s="4" t="inlineStr">
@@ -9649,7 +9565,7 @@
       </c>
       <c r="C285" s="4" t="inlineStr">
         <is>
-          <t>Абдылдаева Алина</t>
+          <t xml:space="preserve">Абдылдаева Алина </t>
         </is>
       </c>
       <c r="D285" s="4" t="inlineStr">
@@ -9681,7 +9597,7 @@
       </c>
       <c r="C286" s="4" t="inlineStr">
         <is>
-          <t>Абдылдаева Сабина</t>
+          <t xml:space="preserve">Абдылдаева Сабина </t>
         </is>
       </c>
       <c r="D286" s="4" t="inlineStr">
@@ -9713,7 +9629,7 @@
       </c>
       <c r="C287" s="4" t="inlineStr">
         <is>
-          <t>Исакова Айпери</t>
+          <t xml:space="preserve">Исакова Айпери </t>
         </is>
       </c>
       <c r="D287" s="4" t="inlineStr">
@@ -9745,7 +9661,7 @@
       </c>
       <c r="C288" s="4" t="inlineStr">
         <is>
-          <t>Хасанова Амина</t>
+          <t xml:space="preserve">Хасанова Амина </t>
         </is>
       </c>
       <c r="D288" s="4" t="inlineStr">
@@ -9777,7 +9693,7 @@
       </c>
       <c r="C289" s="4" t="inlineStr">
         <is>
-          <t>Мабо Замина</t>
+          <t xml:space="preserve">Мабо Замина </t>
         </is>
       </c>
       <c r="D289" s="4" t="inlineStr">
@@ -9809,7 +9725,7 @@
       </c>
       <c r="C290" s="4" t="inlineStr">
         <is>
-          <t>Сагыналиева Зумурат</t>
+          <t xml:space="preserve">Сагыналиева Зумурат </t>
         </is>
       </c>
       <c r="D290" s="4" t="inlineStr">
@@ -9841,7 +9757,7 @@
       </c>
       <c r="C291" s="4" t="inlineStr">
         <is>
-          <t>Досумбекова Жаркын</t>
+          <t xml:space="preserve">Досумбекова Жаркын </t>
         </is>
       </c>
       <c r="D291" s="4" t="inlineStr">
@@ -9905,7 +9821,7 @@
       </c>
       <c r="C293" s="4" t="inlineStr">
         <is>
-          <t>Шамай Эрика</t>
+          <t xml:space="preserve">Шамай Эрика </t>
         </is>
       </c>
       <c r="D293" s="4" t="inlineStr">
@@ -9937,7 +9853,7 @@
       </c>
       <c r="C294" s="4" t="inlineStr">
         <is>
-          <t>Сиемонов Юрий</t>
+          <t xml:space="preserve">Сиемонов Юрий </t>
         </is>
       </c>
       <c r="D294" s="4" t="inlineStr">
@@ -9969,7 +9885,7 @@
       </c>
       <c r="C295" s="4" t="inlineStr">
         <is>
-          <t>Асыбек кызы Жибек</t>
+          <t xml:space="preserve">Асыбек кызы Жибек </t>
         </is>
       </c>
       <c r="D295" s="4" t="inlineStr">
@@ -10001,7 +9917,7 @@
       </c>
       <c r="C296" s="4" t="inlineStr">
         <is>
-          <t>Бурканова Айпери</t>
+          <t xml:space="preserve">Бурканова Айпери </t>
         </is>
       </c>
       <c r="D296" s="4" t="inlineStr">
@@ -10033,7 +9949,7 @@
       </c>
       <c r="C297" s="4" t="inlineStr">
         <is>
-          <t>Сатиева Назгүл</t>
+          <t xml:space="preserve">Сатиева Назгуль </t>
         </is>
       </c>
       <c r="D297" s="4" t="inlineStr">
@@ -10065,7 +9981,7 @@
       </c>
       <c r="C298" s="4" t="inlineStr">
         <is>
-          <t>Алыкулова Гүлбара</t>
+          <t xml:space="preserve">Алыкулова Гулбара </t>
         </is>
       </c>
       <c r="D298" s="4" t="inlineStr">
@@ -10097,7 +10013,7 @@
       </c>
       <c r="C299" s="4" t="inlineStr">
         <is>
-          <t>Кыдырмышева Назгүл</t>
+          <t>Кыдырмышева Назгул</t>
         </is>
       </c>
       <c r="D299" s="4" t="inlineStr">
@@ -10129,7 +10045,7 @@
       </c>
       <c r="C300" s="13" t="inlineStr">
         <is>
-          <t>Малабекова Эрмек</t>
+          <t xml:space="preserve">Малабекова Эрмек </t>
         </is>
       </c>
       <c r="D300" s="5" t="inlineStr">
@@ -10161,7 +10077,7 @@
       </c>
       <c r="C301" s="13" t="inlineStr">
         <is>
-          <t>Кумусбеков Руслан</t>
+          <t xml:space="preserve">Кумусбеков Руслан </t>
         </is>
       </c>
       <c r="D301" s="5" t="inlineStr">
@@ -10193,7 +10109,7 @@
       </c>
       <c r="C302" s="13" t="inlineStr">
         <is>
-          <t>Койчуманов Мирлан</t>
+          <t xml:space="preserve">Койчуманов Мирлан </t>
         </is>
       </c>
       <c r="D302" s="5" t="inlineStr">
@@ -10225,7 +10141,7 @@
       </c>
       <c r="C303" s="13" t="inlineStr">
         <is>
-          <t>Кендирбаев Кубанычбек</t>
+          <t xml:space="preserve">Кендирбаев Кубанычбек </t>
         </is>
       </c>
       <c r="D303" s="5" t="inlineStr">
@@ -10257,7 +10173,7 @@
       </c>
       <c r="C304" s="13" t="inlineStr">
         <is>
-          <t>Женишбеков Эрбол</t>
+          <t xml:space="preserve">Женишбеков Эрбол </t>
         </is>
       </c>
       <c r="D304" s="5" t="inlineStr">
@@ -10289,7 +10205,7 @@
       </c>
       <c r="C305" s="13" t="inlineStr">
         <is>
-          <t>Кожоналиев Самат</t>
+          <t xml:space="preserve">Кожоналиев Самат </t>
         </is>
       </c>
       <c r="D305" s="5" t="inlineStr">
@@ -10321,7 +10237,7 @@
       </c>
       <c r="C306" s="13" t="inlineStr">
         <is>
-          <t>Адылбеков Актилек</t>
+          <t xml:space="preserve">Адылбеков Актилек </t>
         </is>
       </c>
       <c r="D306" s="5" t="inlineStr">
@@ -10353,7 +10269,7 @@
       </c>
       <c r="C307" s="13" t="inlineStr">
         <is>
-          <t>Абдырасулов Бактыбек</t>
+          <t xml:space="preserve">Абдырасулов Бактыбек </t>
         </is>
       </c>
       <c r="D307" s="5" t="inlineStr">
@@ -10385,7 +10301,7 @@
       </c>
       <c r="C308" s="13" t="inlineStr">
         <is>
-          <t>Бабаканов Нурланбек</t>
+          <t xml:space="preserve">Бабаканов Нурланбек </t>
         </is>
       </c>
       <c r="D308" s="5" t="inlineStr">
@@ -10417,7 +10333,7 @@
       </c>
       <c r="C309" s="4" t="inlineStr">
         <is>
-          <t>Тураев Алтынбек</t>
+          <t xml:space="preserve">Тураев Алтынбек </t>
         </is>
       </c>
       <c r="D309" s="4" t="inlineStr">
@@ -10449,7 +10365,7 @@
       </c>
       <c r="C310" s="4" t="inlineStr">
         <is>
-          <t>Ноокенбай уулу Нурсултан</t>
+          <t xml:space="preserve">Ноокенбай уулу Нурсултан </t>
         </is>
       </c>
       <c r="D310" s="4" t="inlineStr">
@@ -10481,7 +10397,7 @@
       </c>
       <c r="C311" s="4" t="inlineStr">
         <is>
-          <t>Харьковей Павел</t>
+          <t xml:space="preserve">Харьковей Павел </t>
         </is>
       </c>
       <c r="D311" s="4" t="inlineStr">
@@ -10513,7 +10429,7 @@
       </c>
       <c r="C312" s="4" t="inlineStr">
         <is>
-          <t>Мусохранов Андрей</t>
+          <t xml:space="preserve">Мусохранов Андрей </t>
         </is>
       </c>
       <c r="D312" s="4" t="inlineStr">
@@ -10545,7 +10461,7 @@
       </c>
       <c r="C313" s="4" t="inlineStr">
         <is>
-          <t>Рудницкий Владимир</t>
+          <t xml:space="preserve">Рудницкий Владимир </t>
         </is>
       </c>
       <c r="D313" s="4" t="inlineStr">
@@ -10577,7 +10493,7 @@
       </c>
       <c r="C314" s="4" t="inlineStr">
         <is>
-          <t>Дорченко Восилий</t>
+          <t xml:space="preserve">Дорченко Восилий </t>
         </is>
       </c>
       <c r="D314" s="4" t="inlineStr">
@@ -10641,7 +10557,7 @@
       </c>
       <c r="C316" s="4" t="inlineStr">
         <is>
-          <t>Джаилов Бакыт</t>
+          <t xml:space="preserve">Джаилов Бакыт </t>
         </is>
       </c>
       <c r="D316" s="4" t="inlineStr">
@@ -10673,7 +10589,7 @@
       </c>
       <c r="C317" s="4" t="inlineStr">
         <is>
-          <t>Мадылбек уулу Адилет</t>
+          <t xml:space="preserve">Мадылбек уулу Адилет </t>
         </is>
       </c>
       <c r="D317" s="4" t="inlineStr">
@@ -10705,7 +10621,7 @@
       </c>
       <c r="C318" s="4" t="inlineStr">
         <is>
-          <t>Жуматаева Чынар</t>
+          <t xml:space="preserve">Жуматаева Чынар </t>
         </is>
       </c>
       <c r="D318" s="4" t="inlineStr">
@@ -10737,7 +10653,7 @@
       </c>
       <c r="C319" s="4" t="inlineStr">
         <is>
-          <t>Хушанов Махмадрузи</t>
+          <t xml:space="preserve">Хушанов Махмадрузи </t>
         </is>
       </c>
       <c r="D319" s="4" t="inlineStr">
@@ -10769,7 +10685,7 @@
       </c>
       <c r="C320" s="4" t="inlineStr">
         <is>
-          <t>Калилов Акобиру</t>
+          <t xml:space="preserve">Калилов Акобиру </t>
         </is>
       </c>
       <c r="D320" s="4" t="inlineStr">
@@ -10801,7 +10717,7 @@
       </c>
       <c r="C321" s="4" t="inlineStr">
         <is>
-          <t>Хушанов Мирзовали</t>
+          <t xml:space="preserve">Хушанов Мирзовали </t>
         </is>
       </c>
       <c r="D321" s="4" t="inlineStr">
@@ -10833,7 +10749,7 @@
       </c>
       <c r="C322" s="4" t="inlineStr">
         <is>
-          <t>Мухтаров Азизбек</t>
+          <t xml:space="preserve">Мухтаров Азизбек </t>
         </is>
       </c>
       <c r="D322" s="4" t="inlineStr">
@@ -10865,7 +10781,7 @@
       </c>
       <c r="C323" s="4" t="inlineStr">
         <is>
-          <t>Талипов Эрали</t>
+          <t xml:space="preserve">Талипов Эрали </t>
         </is>
       </c>
       <c r="D323" s="4" t="inlineStr">
@@ -10897,7 +10813,7 @@
       </c>
       <c r="C324" s="4" t="inlineStr">
         <is>
-          <t>Осмоналиев Керезбек</t>
+          <t xml:space="preserve">Осмоналиев Керезбек </t>
         </is>
       </c>
       <c r="D324" s="4" t="inlineStr">
@@ -10929,7 +10845,7 @@
       </c>
       <c r="C325" s="4" t="inlineStr">
         <is>
-          <t>Артемов Евгений</t>
+          <t xml:space="preserve">Артемов Евгений </t>
         </is>
       </c>
       <c r="D325" s="4" t="inlineStr">
@@ -10993,7 +10909,7 @@
       </c>
       <c r="C327" s="4" t="inlineStr">
         <is>
-          <t>Голик Вячавлав</t>
+          <t xml:space="preserve">Голик Вячавлав </t>
         </is>
       </c>
       <c r="D327" s="4" t="inlineStr">
@@ -11025,7 +10941,7 @@
       </c>
       <c r="C328" s="4" t="inlineStr">
         <is>
-          <t>Носков Станислав</t>
+          <t xml:space="preserve">Носков Станислав </t>
         </is>
       </c>
       <c r="D328" s="4" t="inlineStr">
@@ -11057,7 +10973,7 @@
       </c>
       <c r="C329" s="4" t="inlineStr">
         <is>
-          <t>Сон Монид</t>
+          <t xml:space="preserve">Сон Монид </t>
         </is>
       </c>
       <c r="D329" s="4" t="inlineStr">
@@ -11089,7 +11005,7 @@
       </c>
       <c r="C330" s="4" t="inlineStr">
         <is>
-          <t>Доминов Виталий</t>
+          <t xml:space="preserve">Доминов Виталий </t>
         </is>
       </c>
       <c r="D330" s="4" t="inlineStr">
@@ -11121,7 +11037,7 @@
       </c>
       <c r="C331" s="4" t="inlineStr">
         <is>
-          <t>Надкин Алексей</t>
+          <t xml:space="preserve">Надкин Алексей </t>
         </is>
       </c>
       <c r="D331" s="4" t="inlineStr">
@@ -11153,7 +11069,7 @@
       </c>
       <c r="C332" s="4" t="inlineStr">
         <is>
-          <t>Абдыкадыр уулу Азамат</t>
+          <t xml:space="preserve">Абдыкадыр уулу Азамат </t>
         </is>
       </c>
       <c r="D332" s="4" t="inlineStr">
@@ -11185,7 +11101,7 @@
       </c>
       <c r="C333" s="4" t="inlineStr">
         <is>
-          <t>Сардалбеков Медербек</t>
+          <t xml:space="preserve">Сардалбеков Медербек </t>
         </is>
       </c>
       <c r="D333" s="4" t="inlineStr">
@@ -11217,7 +11133,7 @@
       </c>
       <c r="C334" s="4" t="inlineStr">
         <is>
-          <t>Акматова Венера</t>
+          <t xml:space="preserve">Акматова Венера </t>
         </is>
       </c>
       <c r="D334" s="4" t="inlineStr">
@@ -11249,7 +11165,7 @@
       </c>
       <c r="C335" s="4" t="inlineStr">
         <is>
-          <t>Оролов Нурисбек</t>
+          <t xml:space="preserve">Оролов Нурисбек </t>
         </is>
       </c>
       <c r="D335" s="4" t="inlineStr">
@@ -11281,7 +11197,7 @@
       </c>
       <c r="C336" s="4" t="inlineStr">
         <is>
-          <t>Алексеев Виталий</t>
+          <t xml:space="preserve">Алексеев Виталий </t>
         </is>
       </c>
       <c r="D336" s="4" t="inlineStr">
@@ -11313,7 +11229,7 @@
       </c>
       <c r="C337" s="4" t="inlineStr">
         <is>
-          <t>Волохов Павл</t>
+          <t xml:space="preserve">Волохов Павл </t>
         </is>
       </c>
       <c r="D337" s="4" t="inlineStr">
@@ -11345,7 +11261,7 @@
       </c>
       <c r="C338" s="4" t="inlineStr">
         <is>
-          <t>Ильин Александр</t>
+          <t xml:space="preserve">Ильин Александр </t>
         </is>
       </c>
       <c r="D338" s="4" t="inlineStr">
@@ -11377,7 +11293,7 @@
       </c>
       <c r="C339" s="4" t="inlineStr">
         <is>
-          <t>Исаков Алексей</t>
+          <t xml:space="preserve">Исаков Алексей </t>
         </is>
       </c>
       <c r="D339" s="4" t="inlineStr">
@@ -11409,7 +11325,7 @@
       </c>
       <c r="C340" s="4" t="inlineStr">
         <is>
-          <t>Кызылтаев Абылай</t>
+          <t xml:space="preserve">Кызылтаев Абылай </t>
         </is>
       </c>
       <c r="D340" s="4" t="inlineStr">
@@ -11441,7 +11357,7 @@
       </c>
       <c r="C341" s="4" t="inlineStr">
         <is>
-          <t>Палывжан уулу Анваржан</t>
+          <t xml:space="preserve">Палывжан уулу Анваржан </t>
         </is>
       </c>
       <c r="D341" s="4" t="inlineStr">
@@ -11473,7 +11389,7 @@
       </c>
       <c r="C342" s="4" t="inlineStr">
         <is>
-          <t>Хлопков Денис</t>
+          <t xml:space="preserve">Хлопков Денис </t>
         </is>
       </c>
       <c r="D342" s="4" t="inlineStr">
@@ -11505,7 +11421,7 @@
       </c>
       <c r="C343" s="4" t="inlineStr">
         <is>
-          <t>Бактыбек уулу Мирбек</t>
+          <t xml:space="preserve">Бактыбек уулу Мирбек </t>
         </is>
       </c>
       <c r="D343" s="4" t="inlineStr">
@@ -11537,7 +11453,7 @@
       </c>
       <c r="C344" s="4" t="inlineStr">
         <is>
-          <t>Абдрасаков Анывар</t>
+          <t xml:space="preserve">Абдрасаков Анывар </t>
         </is>
       </c>
       <c r="D344" s="4" t="inlineStr">
@@ -11569,7 +11485,7 @@
       </c>
       <c r="C345" s="4" t="inlineStr">
         <is>
-          <t>Курманбек уулу Суусарбек</t>
+          <t xml:space="preserve">Курманбек уулу Суусарбек </t>
         </is>
       </c>
       <c r="D345" s="4" t="inlineStr">
@@ -11601,7 +11517,7 @@
       </c>
       <c r="C346" s="4" t="inlineStr">
         <is>
-          <t>Шаминдинова Асель</t>
+          <t xml:space="preserve">Шаминдинова Асель </t>
         </is>
       </c>
       <c r="D346" s="4" t="inlineStr">
@@ -11633,7 +11549,7 @@
       </c>
       <c r="C347" s="4" t="inlineStr">
         <is>
-          <t>Абдраимова Жылдыз</t>
+          <t xml:space="preserve">Абдраимова Жылдыз </t>
         </is>
       </c>
       <c r="D347" s="4" t="inlineStr">
@@ -11665,7 +11581,7 @@
       </c>
       <c r="C348" s="4" t="inlineStr">
         <is>
-          <t>Абылкасымова Нургуль</t>
+          <t xml:space="preserve">Абылкасымова Нургуль </t>
         </is>
       </c>
       <c r="D348" s="4" t="inlineStr">
@@ -11697,7 +11613,7 @@
       </c>
       <c r="C349" s="4" t="inlineStr">
         <is>
-          <t>Акматова Дилбара</t>
+          <t xml:space="preserve">Акматова Дилбара </t>
         </is>
       </c>
       <c r="D349" s="4" t="inlineStr">
@@ -11729,7 +11645,7 @@
       </c>
       <c r="C350" s="4" t="inlineStr">
         <is>
-          <t>Бутубаева Дамира</t>
+          <t xml:space="preserve">Бутубаева Дамира </t>
         </is>
       </c>
       <c r="D350" s="4" t="inlineStr">
@@ -11761,7 +11677,7 @@
       </c>
       <c r="C351" s="4" t="inlineStr">
         <is>
-          <t>Жумалиева Умут</t>
+          <t xml:space="preserve">Жумалиева Умут </t>
         </is>
       </c>
       <c r="D351" s="4" t="inlineStr">
@@ -11793,7 +11709,7 @@
       </c>
       <c r="C352" s="4" t="inlineStr">
         <is>
-          <t>Искендерова Толобубу</t>
+          <t xml:space="preserve">Искендерова Толобубу </t>
         </is>
       </c>
       <c r="D352" s="4" t="inlineStr">
@@ -11825,7 +11741,7 @@
       </c>
       <c r="C353" s="4" t="inlineStr">
         <is>
-          <t>Курманбаева Рыскул</t>
+          <t xml:space="preserve">Курманбаева Рыскул </t>
         </is>
       </c>
       <c r="D353" s="4" t="inlineStr">
@@ -11857,7 +11773,7 @@
       </c>
       <c r="C354" s="4" t="inlineStr">
         <is>
-          <t>Молдобаева Наргиза</t>
+          <t xml:space="preserve">Молдобаева Наргиза </t>
         </is>
       </c>
       <c r="D354" s="4" t="inlineStr">
@@ -11921,7 +11837,7 @@
       </c>
       <c r="C356" s="4" t="inlineStr">
         <is>
-          <t>Раманкулова Айзада</t>
+          <t xml:space="preserve">Раманкулова Айзада </t>
         </is>
       </c>
       <c r="D356" s="4" t="inlineStr">
@@ -11953,7 +11869,7 @@
       </c>
       <c r="C357" s="4" t="inlineStr">
         <is>
-          <t>Сартбаева Динара</t>
+          <t xml:space="preserve">Сартбаева Динара </t>
         </is>
       </c>
       <c r="D357" s="4" t="inlineStr">
@@ -11985,7 +11901,7 @@
       </c>
       <c r="C358" s="4" t="inlineStr">
         <is>
-          <t>Нурланв Нуржигит</t>
+          <t xml:space="preserve">Нурланв Нуржигит </t>
         </is>
       </c>
       <c r="D358" s="4" t="inlineStr">
@@ -12017,7 +11933,7 @@
       </c>
       <c r="C359" s="4" t="inlineStr">
         <is>
-          <t>Камал уулу Улукман</t>
+          <t xml:space="preserve">Камал уулу Улукман </t>
         </is>
       </c>
       <c r="D359" s="4" t="inlineStr">
@@ -12049,7 +11965,7 @@
       </c>
       <c r="C360" s="4" t="inlineStr">
         <is>
-          <t>Дуйшеев Адилет</t>
+          <t xml:space="preserve">Дуйшеев Адилет </t>
         </is>
       </c>
       <c r="D360" s="4" t="inlineStr">
@@ -12081,7 +11997,7 @@
       </c>
       <c r="C361" s="4" t="inlineStr">
         <is>
-          <t>Толонов Баястан</t>
+          <t xml:space="preserve">Толонов Баястан </t>
         </is>
       </c>
       <c r="D361" s="4" t="inlineStr">
@@ -12145,7 +12061,7 @@
       </c>
       <c r="C363" s="4" t="inlineStr">
         <is>
-          <t>Айбашова Гулийпа</t>
+          <t xml:space="preserve">Айбашова Гулийпа </t>
         </is>
       </c>
       <c r="D363" s="4" t="inlineStr">
@@ -12177,7 +12093,7 @@
       </c>
       <c r="C364" s="4" t="inlineStr">
         <is>
-          <t>Акимова Марифаткан</t>
+          <t xml:space="preserve">Акимова Марифаткан </t>
         </is>
       </c>
       <c r="D364" s="4" t="inlineStr">
@@ -12241,7 +12157,7 @@
       </c>
       <c r="C366" s="4" t="inlineStr">
         <is>
-          <t>Садырбек кызы Өмүркан</t>
+          <t xml:space="preserve">Садырбек кызы Омуркан </t>
         </is>
       </c>
       <c r="D366" s="4" t="inlineStr">
@@ -12273,7 +12189,7 @@
       </c>
       <c r="C367" s="4" t="inlineStr">
         <is>
-          <t>Худайбердиева Гулиза</t>
+          <t xml:space="preserve">Худайбердиева Гулиза </t>
         </is>
       </c>
       <c r="D367" s="4" t="inlineStr">
@@ -12305,7 +12221,7 @@
       </c>
       <c r="C368" s="4" t="inlineStr">
         <is>
-          <t>Памизова Бактыгүл</t>
+          <t>Памизова Бактыгул</t>
         </is>
       </c>
       <c r="D368" s="4" t="inlineStr">
@@ -12369,7 +12285,7 @@
       </c>
       <c r="C370" s="4" t="inlineStr">
         <is>
-          <t>Кутубаева Элмира</t>
+          <t xml:space="preserve">Кутубаева Элмира </t>
         </is>
       </c>
       <c r="D370" s="4" t="inlineStr">
@@ -12401,7 +12317,7 @@
       </c>
       <c r="C371" s="4" t="inlineStr">
         <is>
-          <t>Маманова Мухабботжан</t>
+          <t xml:space="preserve">Маманова Мухабботжан </t>
         </is>
       </c>
       <c r="D371" s="4" t="inlineStr">
@@ -12465,7 +12381,7 @@
       </c>
       <c r="C373" s="4" t="inlineStr">
         <is>
-          <t>Турганбаева Назира</t>
+          <t xml:space="preserve">Турганбаева Назира </t>
         </is>
       </c>
       <c r="D373" s="4" t="inlineStr">
@@ -12529,7 +12445,7 @@
       </c>
       <c r="C375" s="4" t="inlineStr">
         <is>
-          <t>Атакулов Элмира</t>
+          <t xml:space="preserve">Атакулов Элмира </t>
         </is>
       </c>
       <c r="D375" s="4" t="inlineStr">
@@ -12561,7 +12477,7 @@
       </c>
       <c r="C376" s="4" t="inlineStr">
         <is>
-          <t>Кадиев Алтынбек</t>
+          <t xml:space="preserve">Кадиев Алтынбек </t>
         </is>
       </c>
       <c r="D376" s="4" t="inlineStr">
@@ -12593,7 +12509,7 @@
       </c>
       <c r="C377" s="4" t="inlineStr">
         <is>
-          <t>Иманов Тагайбек</t>
+          <t xml:space="preserve">Иманов Тагайбек </t>
         </is>
       </c>
       <c r="D377" s="4" t="inlineStr">
@@ -12625,7 +12541,7 @@
       </c>
       <c r="C378" s="4" t="inlineStr">
         <is>
-          <t>Жанторо уулу Тенирберди</t>
+          <t xml:space="preserve">Жанторо уулу Тенирберди </t>
         </is>
       </c>
       <c r="D378" s="4" t="inlineStr">
@@ -12657,7 +12573,7 @@
       </c>
       <c r="C379" s="4" t="inlineStr">
         <is>
-          <t>Шамирзаев Мамирасул</t>
+          <t xml:space="preserve">Шамирзаев Мамирасул </t>
         </is>
       </c>
       <c r="D379" s="4" t="inlineStr">
@@ -12721,7 +12637,7 @@
       </c>
       <c r="C381" s="13" t="inlineStr">
         <is>
-          <t>Салымбеков Урмат</t>
+          <t xml:space="preserve">Салымбеков Урмат </t>
         </is>
       </c>
       <c r="D381" s="5" t="inlineStr">
@@ -12753,7 +12669,7 @@
       </c>
       <c r="C382" s="4" t="inlineStr">
         <is>
-          <t>Таштанбеков Азамат</t>
+          <t xml:space="preserve">Таштанбеков Азамат </t>
         </is>
       </c>
       <c r="D382" s="4" t="inlineStr">
@@ -12785,7 +12701,7 @@
       </c>
       <c r="C383" s="4" t="inlineStr">
         <is>
-          <t>Турчак Сергей</t>
+          <t xml:space="preserve">Турчак Сергей </t>
         </is>
       </c>
       <c r="D383" s="4" t="inlineStr">
@@ -12817,7 +12733,7 @@
       </c>
       <c r="C384" s="4" t="inlineStr">
         <is>
-          <t>Нарындыков Тилек</t>
+          <t xml:space="preserve">Нарындыков Тилек </t>
         </is>
       </c>
       <c r="D384" s="5" t="inlineStr">
@@ -12881,7 +12797,7 @@
       </c>
       <c r="C386" s="4" t="inlineStr">
         <is>
-          <t>Попов Кирил</t>
+          <t xml:space="preserve">Попов Кирил </t>
         </is>
       </c>
       <c r="D386" s="4" t="inlineStr">
@@ -12913,7 +12829,7 @@
       </c>
       <c r="C387" s="4" t="inlineStr">
         <is>
-          <t>Ибраев Сейитказы</t>
+          <t xml:space="preserve">Ибраев Сейитказы </t>
         </is>
       </c>
       <c r="D387" s="4" t="inlineStr">
@@ -12945,7 +12861,7 @@
       </c>
       <c r="C388" s="13" t="inlineStr">
         <is>
-          <t>Арзиев Нарзилла</t>
+          <t xml:space="preserve">Арзиев Нарзилла </t>
         </is>
       </c>
       <c r="D388" s="5" t="inlineStr">
@@ -12977,7 +12893,7 @@
       </c>
       <c r="C389" s="13" t="inlineStr">
         <is>
-          <t>Кувандиков Бексултан</t>
+          <t xml:space="preserve">Кувандиков Бексултан </t>
         </is>
       </c>
       <c r="D389" s="5" t="inlineStr">
@@ -13009,7 +12925,7 @@
       </c>
       <c r="C390" s="13" t="inlineStr">
         <is>
-          <t>Текебаев Бексултан</t>
+          <t xml:space="preserve">Текебаев Бексултан </t>
         </is>
       </c>
       <c r="D390" s="5" t="inlineStr">
@@ -13041,12 +12957,12 @@
       </c>
       <c r="C391" s="4" t="inlineStr">
         <is>
-          <t>Жапанова Лазат</t>
+          <t xml:space="preserve">Жапанова Лазат </t>
         </is>
       </c>
       <c r="D391" s="4" t="inlineStr">
         <is>
-          <t>Швея с умением кроить</t>
+          <t xml:space="preserve">"Швея" "Портной с умением кроить" </t>
         </is>
       </c>
       <c r="E391" s="4" t="inlineStr">
@@ -13073,12 +12989,12 @@
       </c>
       <c r="C392" s="4" t="inlineStr">
         <is>
-          <t>Абдуразакова Потмахан</t>
+          <t xml:space="preserve">Абдуразакова Потмахан </t>
         </is>
       </c>
       <c r="D392" s="4" t="inlineStr">
         <is>
-          <t>Швея с умением кроить</t>
+          <t xml:space="preserve">"Швея" "Портной с умением кроить" </t>
         </is>
       </c>
       <c r="E392" s="4" t="inlineStr">
@@ -13105,12 +13021,12 @@
       </c>
       <c r="C393" s="4" t="inlineStr">
         <is>
-          <t>Алимова Мамакатжан</t>
+          <t xml:space="preserve">Алимова Мамакатжан </t>
         </is>
       </c>
       <c r="D393" s="4" t="inlineStr">
         <is>
-          <t>Швея с умением кроить</t>
+          <t xml:space="preserve">"Швея" "Портной с умением кроить" </t>
         </is>
       </c>
       <c r="E393" s="4" t="inlineStr">
@@ -13137,12 +13053,12 @@
       </c>
       <c r="C394" s="4" t="inlineStr">
         <is>
-          <t>Кебекова Чынара</t>
+          <t xml:space="preserve">Кебекова Чынара </t>
         </is>
       </c>
       <c r="D394" s="4" t="inlineStr">
         <is>
-          <t>Швея с умением кроить</t>
+          <t xml:space="preserve">"Швея" "Портной с умением кроить" </t>
         </is>
       </c>
       <c r="E394" s="4" t="inlineStr">
@@ -13169,12 +13085,12 @@
       </c>
       <c r="C395" s="4" t="inlineStr">
         <is>
-          <t>Касимова Мамакат</t>
+          <t xml:space="preserve">Касимова Мамакат </t>
         </is>
       </c>
       <c r="D395" s="4" t="inlineStr">
         <is>
-          <t>Швея с умением кроить</t>
+          <t xml:space="preserve">"Швея" "Портной с умением кроить" </t>
         </is>
       </c>
       <c r="E395" s="4" t="inlineStr">
@@ -13201,12 +13117,12 @@
       </c>
       <c r="C396" s="4" t="inlineStr">
         <is>
-          <t>Джураева Яркинай</t>
+          <t xml:space="preserve">Джураева Яркинай </t>
         </is>
       </c>
       <c r="D396" s="4" t="inlineStr">
         <is>
-          <t>Швея с умением кроить</t>
+          <t xml:space="preserve">"Швея" "Портной с умением кроить" </t>
         </is>
       </c>
       <c r="E396" s="4" t="inlineStr">
@@ -13233,12 +13149,12 @@
       </c>
       <c r="C397" s="4" t="inlineStr">
         <is>
-          <t>Исакова Махлие</t>
+          <t xml:space="preserve">Исакова Махлие </t>
         </is>
       </c>
       <c r="D397" s="4" t="inlineStr">
         <is>
-          <t>Швея с умением кроить</t>
+          <t xml:space="preserve">"Швея" "Портной с умением кроить" </t>
         </is>
       </c>
       <c r="E397" s="4" t="inlineStr">
@@ -13265,12 +13181,12 @@
       </c>
       <c r="C398" s="4" t="inlineStr">
         <is>
-          <t>Хаитова Умидохан</t>
+          <t xml:space="preserve">Хаитова Умидохан </t>
         </is>
       </c>
       <c r="D398" s="4" t="inlineStr">
         <is>
-          <t>Швея с умением кроить</t>
+          <t xml:space="preserve">"Швея" "Портной с умением кроить" </t>
         </is>
       </c>
       <c r="E398" s="4" t="inlineStr">
@@ -13297,12 +13213,12 @@
       </c>
       <c r="C399" s="4" t="inlineStr">
         <is>
-          <t>Сотвалдиева Шонра</t>
+          <t xml:space="preserve">Сотвалдиева Шонра </t>
         </is>
       </c>
       <c r="D399" s="4" t="inlineStr">
         <is>
-          <t>Швея с умением кроить</t>
+          <t xml:space="preserve">"Швея" "Портной с умением кроить" </t>
         </is>
       </c>
       <c r="E399" s="4" t="inlineStr">
@@ -13329,12 +13245,12 @@
       </c>
       <c r="C400" s="4" t="inlineStr">
         <is>
-          <t>Мирзаева Манзура</t>
+          <t xml:space="preserve">Мирзаева Манзура </t>
         </is>
       </c>
       <c r="D400" s="4" t="inlineStr">
         <is>
-          <t>Швея с умением кроить</t>
+          <t xml:space="preserve">"Швея" "Портной с умением кроить" </t>
         </is>
       </c>
       <c r="E400" s="4" t="inlineStr">
@@ -13361,12 +13277,12 @@
       </c>
       <c r="C401" s="4" t="inlineStr">
         <is>
-          <t>Бектемирова Айжаркын</t>
+          <t xml:space="preserve">Бектемирова Айжаркын </t>
         </is>
       </c>
       <c r="D401" s="4" t="inlineStr">
         <is>
-          <t>Швея с умением кроить</t>
+          <t xml:space="preserve">"Швея" "Портной с умением кроить" </t>
         </is>
       </c>
       <c r="E401" s="4" t="inlineStr">
@@ -13398,7 +13314,7 @@
       </c>
       <c r="D402" s="4" t="inlineStr">
         <is>
-          <t>Швея с умением кроить</t>
+          <t xml:space="preserve">"Швея" "Портной с умением кроить" </t>
         </is>
       </c>
       <c r="E402" s="4" t="inlineStr">
@@ -13425,7 +13341,7 @@
       </c>
       <c r="C403" s="4" t="inlineStr">
         <is>
-          <t>Балбаев Хусан</t>
+          <t xml:space="preserve">Балбаев Хусан </t>
         </is>
       </c>
       <c r="D403" s="4" t="inlineStr">
@@ -13457,7 +13373,7 @@
       </c>
       <c r="C404" s="4" t="inlineStr">
         <is>
-          <t>Сидиков Самандар</t>
+          <t xml:space="preserve">Сидиков Самандар </t>
         </is>
       </c>
       <c r="D404" s="4" t="inlineStr">
@@ -13489,7 +13405,7 @@
       </c>
       <c r="C405" s="4" t="inlineStr">
         <is>
-          <t>Асек уулу Өмүрзак</t>
+          <t xml:space="preserve">Асек уулу Омурзак </t>
         </is>
       </c>
       <c r="D405" s="4" t="inlineStr">
@@ -13521,7 +13437,7 @@
       </c>
       <c r="C406" s="4" t="inlineStr">
         <is>
-          <t>Жумабек уулу Торобек</t>
+          <t xml:space="preserve">Жумабек уулу Торобек </t>
         </is>
       </c>
       <c r="D406" s="4" t="inlineStr">
@@ -13585,7 +13501,7 @@
       </c>
       <c r="C408" s="4" t="inlineStr">
         <is>
-          <t>Курчубекова Венера</t>
+          <t xml:space="preserve">Курчубекова Венера </t>
         </is>
       </c>
       <c r="D408" s="4" t="inlineStr">
@@ -13617,7 +13533,7 @@
       </c>
       <c r="C409" s="4" t="inlineStr">
         <is>
-          <t>Темирбердиева Тажихан</t>
+          <t xml:space="preserve">Темирбердиева Тажихан </t>
         </is>
       </c>
       <c r="D409" s="4" t="inlineStr">
@@ -13649,7 +13565,7 @@
       </c>
       <c r="C410" s="4" t="inlineStr">
         <is>
-          <t>Халдарова Мукая</t>
+          <t xml:space="preserve">Халдарова Мукая </t>
         </is>
       </c>
       <c r="D410" s="4" t="inlineStr">
@@ -13681,7 +13597,7 @@
       </c>
       <c r="C411" s="4" t="inlineStr">
         <is>
-          <t>Абдуллаева Роза</t>
+          <t xml:space="preserve">Абдуллаева Роза </t>
         </is>
       </c>
       <c r="D411" s="4" t="inlineStr">
@@ -13713,7 +13629,7 @@
       </c>
       <c r="C412" s="4" t="inlineStr">
         <is>
-          <t>Таджихожаева Анархан</t>
+          <t xml:space="preserve">Таджихожаева Анархан </t>
         </is>
       </c>
       <c r="D412" s="4" t="inlineStr">
@@ -13745,7 +13661,7 @@
       </c>
       <c r="C413" s="4" t="inlineStr">
         <is>
-          <t>Асылканова Тинатин</t>
+          <t xml:space="preserve">Асылканова Тинатин </t>
         </is>
       </c>
       <c r="D413" s="4" t="inlineStr">
@@ -13777,7 +13693,7 @@
       </c>
       <c r="C414" s="4" t="inlineStr">
         <is>
-          <t>Воингуй Шахида</t>
+          <t xml:space="preserve">Воингуй Шахида </t>
         </is>
       </c>
       <c r="D414" s="4" t="inlineStr">
@@ -13809,7 +13725,7 @@
       </c>
       <c r="C415" s="4" t="inlineStr">
         <is>
-          <t>Кутуева Сымбат</t>
+          <t xml:space="preserve">Кутуева Сымбат </t>
         </is>
       </c>
       <c r="D415" s="4" t="inlineStr">
@@ -13841,7 +13757,7 @@
       </c>
       <c r="C416" s="4" t="inlineStr">
         <is>
-          <t>Мантекова Айзада</t>
+          <t xml:space="preserve">Мантекова Айзада </t>
         </is>
       </c>
       <c r="D416" s="4" t="inlineStr">
@@ -13873,7 +13789,7 @@
       </c>
       <c r="C417" s="4" t="inlineStr">
         <is>
-          <t>Сабаева Зенбе</t>
+          <t xml:space="preserve">Сабаева Зенбе </t>
         </is>
       </c>
       <c r="D417" s="4" t="inlineStr">
@@ -13905,7 +13821,7 @@
       </c>
       <c r="C418" s="4" t="inlineStr">
         <is>
-          <t>Сабаева Рамиля</t>
+          <t xml:space="preserve">Сабаева Рамиля </t>
         </is>
       </c>
       <c r="D418" s="4" t="inlineStr">
@@ -13937,7 +13853,7 @@
       </c>
       <c r="C419" s="4" t="inlineStr">
         <is>
-          <t>Санина Татьяна</t>
+          <t xml:space="preserve">Санина Татьяна </t>
         </is>
       </c>
       <c r="D419" s="4" t="inlineStr">
@@ -13969,7 +13885,7 @@
       </c>
       <c r="C420" s="4" t="inlineStr">
         <is>
-          <t>Хува Хамима</t>
+          <t xml:space="preserve">Хува Хамима </t>
         </is>
       </c>
       <c r="D420" s="4" t="inlineStr">
@@ -14001,7 +13917,7 @@
       </c>
       <c r="C421" s="4" t="inlineStr">
         <is>
-          <t>Чин Зарина</t>
+          <t xml:space="preserve">Чин Зарина </t>
         </is>
       </c>
       <c r="D421" s="4" t="inlineStr">
@@ -14033,7 +13949,7 @@
       </c>
       <c r="C422" s="4" t="inlineStr">
         <is>
-          <t>Абдугулова Рахат</t>
+          <t xml:space="preserve">Абдугулова Рахат </t>
         </is>
       </c>
       <c r="D422" s="4" t="inlineStr">
@@ -14065,7 +13981,7 @@
       </c>
       <c r="C423" s="4" t="inlineStr">
         <is>
-          <t>Джолдошбекова Майрамкуль</t>
+          <t xml:space="preserve">Джолдошбекова Майрамкуль </t>
         </is>
       </c>
       <c r="D423" s="4" t="inlineStr">
@@ -14097,7 +14013,7 @@
       </c>
       <c r="C424" s="4" t="inlineStr">
         <is>
-          <t>Оморова Кульмира</t>
+          <t xml:space="preserve">Оморова Кульмира </t>
         </is>
       </c>
       <c r="D424" s="4" t="inlineStr">
@@ -14129,7 +14045,7 @@
       </c>
       <c r="C425" s="4" t="inlineStr">
         <is>
-          <t>Джолдошбекова Жибек</t>
+          <t xml:space="preserve">Джолдошбекова Жибек </t>
         </is>
       </c>
       <c r="D425" s="4" t="inlineStr">
@@ -14161,7 +14077,7 @@
       </c>
       <c r="C426" s="4" t="inlineStr">
         <is>
-          <t>Исабекова Элмира</t>
+          <t xml:space="preserve">Исабекова Элмира </t>
         </is>
       </c>
       <c r="D426" s="4" t="inlineStr">
@@ -14193,7 +14109,7 @@
       </c>
       <c r="C427" s="4" t="inlineStr">
         <is>
-          <t>Мамытова Гүлмира</t>
+          <t xml:space="preserve">Мамытова Гульмира </t>
         </is>
       </c>
       <c r="D427" s="4" t="inlineStr">
@@ -14225,7 +14141,7 @@
       </c>
       <c r="C428" s="4" t="inlineStr">
         <is>
-          <t>Аскаркулова Айгүл</t>
+          <t xml:space="preserve">Аскаркулова Айгуль </t>
         </is>
       </c>
       <c r="D428" s="4" t="inlineStr">
@@ -14257,7 +14173,7 @@
       </c>
       <c r="C429" s="4" t="inlineStr">
         <is>
-          <t>Сапашова Эленура</t>
+          <t xml:space="preserve">Сапашова Эленура </t>
         </is>
       </c>
       <c r="D429" s="4" t="inlineStr">
@@ -14289,7 +14205,7 @@
       </c>
       <c r="C430" s="4" t="inlineStr">
         <is>
-          <t>Ли Ажар</t>
+          <t xml:space="preserve">Ли Ажар </t>
         </is>
       </c>
       <c r="D430" s="4" t="inlineStr">
@@ -14321,7 +14237,7 @@
       </c>
       <c r="C431" s="13" t="inlineStr">
         <is>
-          <t>Исмаилов Расул</t>
+          <t xml:space="preserve">Исмаилов Расул </t>
         </is>
       </c>
       <c r="D431" s="5" t="inlineStr">
@@ -14353,7 +14269,7 @@
       </c>
       <c r="C432" s="13" t="inlineStr">
         <is>
-          <t>Аманкулов Эмир</t>
+          <t xml:space="preserve">Аманкулов Эмир </t>
         </is>
       </c>
       <c r="D432" s="5" t="inlineStr">
@@ -14385,7 +14301,7 @@
       </c>
       <c r="C433" s="13" t="inlineStr">
         <is>
-          <t>Абдибаев Айбек</t>
+          <t xml:space="preserve">Абдибаев Айбек </t>
         </is>
       </c>
       <c r="D433" s="5" t="inlineStr">
@@ -14417,7 +14333,7 @@
       </c>
       <c r="C434" s="13" t="inlineStr">
         <is>
-          <t>Атабеков Марсбек</t>
+          <t xml:space="preserve">Атабеков Марсбек </t>
         </is>
       </c>
       <c r="D434" s="5" t="inlineStr">
@@ -14449,7 +14365,7 @@
       </c>
       <c r="C435" s="13" t="inlineStr">
         <is>
-          <t>Бактыбек уулу Айтолду</t>
+          <t xml:space="preserve">Бактыбек уулу Айтолду </t>
         </is>
       </c>
       <c r="D435" s="5" t="inlineStr">
@@ -14481,7 +14397,7 @@
       </c>
       <c r="C436" s="13" t="inlineStr">
         <is>
-          <t>Акматов Алымбек</t>
+          <t xml:space="preserve">Акматов Алымбек </t>
         </is>
       </c>
       <c r="D436" s="5" t="inlineStr">
@@ -14513,7 +14429,7 @@
       </c>
       <c r="C437" s="13" t="inlineStr">
         <is>
-          <t>Ажиматов Искендер</t>
+          <t xml:space="preserve">Ажиматов Искендер </t>
         </is>
       </c>
       <c r="D437" s="5" t="inlineStr">
@@ -14545,7 +14461,7 @@
       </c>
       <c r="C438" s="13" t="inlineStr">
         <is>
-          <t>Дорбонов Нурис</t>
+          <t xml:space="preserve">Дорбонов Нурис </t>
         </is>
       </c>
       <c r="D438" s="5" t="inlineStr">
@@ -14577,7 +14493,7 @@
       </c>
       <c r="C439" s="13" t="inlineStr">
         <is>
-          <t>Аскарбеков Адилет</t>
+          <t xml:space="preserve">Аскарбеков Адилет </t>
         </is>
       </c>
       <c r="D439" s="13" t="inlineStr">
@@ -14609,7 +14525,7 @@
       </c>
       <c r="C440" s="13" t="inlineStr">
         <is>
-          <t>Сабержанов Руслан</t>
+          <t xml:space="preserve">Сабержанов Руслан </t>
         </is>
       </c>
       <c r="D440" s="13" t="inlineStr">
@@ -14641,7 +14557,7 @@
       </c>
       <c r="C441" s="13" t="inlineStr">
         <is>
-          <t>Апальков Николай</t>
+          <t xml:space="preserve">Апальков Николай </t>
         </is>
       </c>
       <c r="D441" s="13" t="inlineStr">
@@ -14673,7 +14589,7 @@
       </c>
       <c r="C442" s="13" t="inlineStr">
         <is>
-          <t>Карагулов Элдар</t>
+          <t xml:space="preserve">Карагулов Элдар </t>
         </is>
       </c>
       <c r="D442" s="13" t="inlineStr">
@@ -14705,7 +14621,7 @@
       </c>
       <c r="C443" s="13" t="inlineStr">
         <is>
-          <t>Мусанов Чингиз</t>
+          <t xml:space="preserve">Мусанов Чингиз </t>
         </is>
       </c>
       <c r="D443" s="13" t="inlineStr">
@@ -14737,7 +14653,7 @@
       </c>
       <c r="C444" s="13" t="inlineStr">
         <is>
-          <t>Нурбек уулу Зайырбек</t>
+          <t xml:space="preserve">Нурбек уулу Зайырбек </t>
         </is>
       </c>
       <c r="D444" s="13" t="inlineStr">
@@ -14769,7 +14685,7 @@
       </c>
       <c r="C445" s="13" t="inlineStr">
         <is>
-          <t>Турдалы уулу Арстанбек</t>
+          <t xml:space="preserve">Турдалы уулу Арстанбек </t>
         </is>
       </c>
       <c r="D445" s="13" t="inlineStr">
@@ -14801,7 +14717,7 @@
       </c>
       <c r="C446" s="13" t="inlineStr">
         <is>
-          <t>Чынгыз уулу Кочкунбек</t>
+          <t xml:space="preserve">Чынгыз уулу Кочкунбек </t>
         </is>
       </c>
       <c r="D446" s="13" t="inlineStr">
@@ -14865,7 +14781,7 @@
       </c>
       <c r="C448" s="13" t="inlineStr">
         <is>
-          <t>Жолочиев Өмүрбек</t>
+          <t xml:space="preserve">Жолочиев Омурбек </t>
         </is>
       </c>
       <c r="D448" s="13" t="inlineStr">
@@ -14897,7 +14813,7 @@
       </c>
       <c r="C449" s="13" t="inlineStr">
         <is>
-          <t>Жусупов Таалайбек</t>
+          <t xml:space="preserve">Жусупов Таалайбек </t>
         </is>
       </c>
       <c r="D449" s="13" t="inlineStr">
@@ -14929,7 +14845,7 @@
       </c>
       <c r="C450" s="13" t="inlineStr">
         <is>
-          <t>Ляшенко Иван</t>
+          <t xml:space="preserve">Ляшенко Иван </t>
         </is>
       </c>
       <c r="D450" s="13" t="inlineStr">
@@ -14961,7 +14877,7 @@
       </c>
       <c r="C451" s="13" t="inlineStr">
         <is>
-          <t>Боронбаев Толобек</t>
+          <t xml:space="preserve">Боронбаев Толобек </t>
         </is>
       </c>
       <c r="D451" s="13" t="inlineStr">
@@ -14993,7 +14909,7 @@
       </c>
       <c r="C452" s="13" t="inlineStr">
         <is>
-          <t>Абдылдаев Баатырбек</t>
+          <t xml:space="preserve">Абдылдаев Баатырбек </t>
         </is>
       </c>
       <c r="D452" s="13" t="inlineStr">
@@ -15025,7 +14941,7 @@
       </c>
       <c r="C453" s="13" t="inlineStr">
         <is>
-          <t>Жумагулов Атай</t>
+          <t xml:space="preserve">Жумагулов Атай </t>
         </is>
       </c>
       <c r="D453" s="13" t="inlineStr">
@@ -15057,7 +14973,7 @@
       </c>
       <c r="C454" s="13" t="inlineStr">
         <is>
-          <t>Ливенщев Антон</t>
+          <t xml:space="preserve">Ливенщев Антон </t>
         </is>
       </c>
       <c r="D454" s="13" t="inlineStr">
@@ -15089,7 +15005,7 @@
       </c>
       <c r="C455" s="13" t="inlineStr">
         <is>
-          <t>Медилов Саматбек</t>
+          <t xml:space="preserve">Медилов Саматбек </t>
         </is>
       </c>
       <c r="D455" s="13" t="inlineStr">
@@ -15121,7 +15037,7 @@
       </c>
       <c r="C456" s="13" t="inlineStr">
         <is>
-          <t>Нурбеков Дастан</t>
+          <t xml:space="preserve">Нурбеков Дастан </t>
         </is>
       </c>
       <c r="D456" s="13" t="inlineStr">
@@ -15153,7 +15069,7 @@
       </c>
       <c r="C457" s="13" t="inlineStr">
         <is>
-          <t>Токторбаев Бекболсун</t>
+          <t xml:space="preserve">Токторбаев Бекболсун </t>
         </is>
       </c>
       <c r="D457" s="13" t="inlineStr">
@@ -15185,7 +15101,7 @@
       </c>
       <c r="C458" s="13" t="inlineStr">
         <is>
-          <t>Таалайбеков Эрмек</t>
+          <t xml:space="preserve">Таалайбеков Эрмек </t>
         </is>
       </c>
       <c r="D458" s="13" t="inlineStr">
@@ -15217,7 +15133,7 @@
       </c>
       <c r="C459" s="13" t="inlineStr">
         <is>
-          <t>Эрболов Нурбол</t>
+          <t xml:space="preserve">Эрболов Нурбол </t>
         </is>
       </c>
       <c r="D459" s="13" t="inlineStr">
@@ -15249,7 +15165,7 @@
       </c>
       <c r="C460" s="13" t="inlineStr">
         <is>
-          <t>Твшбаев Туголбай</t>
+          <t xml:space="preserve">Твшбаев Туголбай </t>
         </is>
       </c>
       <c r="D460" s="13" t="inlineStr">
@@ -15281,7 +15197,7 @@
       </c>
       <c r="C461" s="13" t="inlineStr">
         <is>
-          <t>Аалиев Мирбек</t>
+          <t xml:space="preserve">Аалиев Мирбек </t>
         </is>
       </c>
       <c r="D461" s="13" t="inlineStr">
@@ -15313,7 +15229,7 @@
       </c>
       <c r="C462" s="13" t="inlineStr">
         <is>
-          <t>Айтахунов Мухамеджан</t>
+          <t xml:space="preserve">Айтахунов Мухамеджан </t>
         </is>
       </c>
       <c r="D462" s="13" t="inlineStr">
@@ -15377,7 +15293,7 @@
       </c>
       <c r="C464" s="13" t="inlineStr">
         <is>
-          <t>Ким Эдуард</t>
+          <t xml:space="preserve">Ким Эдуард </t>
         </is>
       </c>
       <c r="D464" s="13" t="inlineStr">
@@ -15409,7 +15325,7 @@
       </c>
       <c r="C465" s="13" t="inlineStr">
         <is>
-          <t>Оражанов Ертай</t>
+          <t xml:space="preserve">Оражанов Ертай </t>
         </is>
       </c>
       <c r="D465" s="13" t="inlineStr">
@@ -15441,7 +15357,7 @@
       </c>
       <c r="C466" s="13" t="inlineStr">
         <is>
-          <t>Дуйшеев Кенжебек</t>
+          <t xml:space="preserve">Дуйшеев Кенжебек </t>
         </is>
       </c>
       <c r="D466" s="13" t="inlineStr">
@@ -15473,7 +15389,7 @@
       </c>
       <c r="C467" s="13" t="inlineStr">
         <is>
-          <t>Абаева Татьяна</t>
+          <t xml:space="preserve">Абаева Татьяна </t>
         </is>
       </c>
       <c r="D467" s="13" t="inlineStr">
@@ -15505,7 +15421,7 @@
       </c>
       <c r="C468" s="13" t="inlineStr">
         <is>
-          <t>Ан Лариса</t>
+          <t xml:space="preserve">Ан Лариса </t>
         </is>
       </c>
       <c r="D468" s="13" t="inlineStr">
@@ -15537,7 +15453,7 @@
       </c>
       <c r="C469" s="13" t="inlineStr">
         <is>
-          <t>Женалиева Кундуз</t>
+          <t xml:space="preserve">Женалиева Кундуз </t>
         </is>
       </c>
       <c r="D469" s="13" t="inlineStr">
@@ -15569,7 +15485,7 @@
       </c>
       <c r="C470" s="13" t="inlineStr">
         <is>
-          <t>Казиева Канипа</t>
+          <t xml:space="preserve">Казиева Канипа </t>
         </is>
       </c>
       <c r="D470" s="13" t="inlineStr">
@@ -15601,7 +15517,7 @@
       </c>
       <c r="C471" s="13" t="inlineStr">
         <is>
-          <t>Каримова Гулай</t>
+          <t xml:space="preserve">Каримова Гулай </t>
         </is>
       </c>
       <c r="D471" s="13" t="inlineStr">
@@ -15633,7 +15549,7 @@
       </c>
       <c r="C472" s="13" t="inlineStr">
         <is>
-          <t>Кочербаева Гүлнара</t>
+          <t xml:space="preserve">Кочербаева Гулнара </t>
         </is>
       </c>
       <c r="D472" s="13" t="inlineStr">
@@ -15665,7 +15581,7 @@
       </c>
       <c r="C473" s="13" t="inlineStr">
         <is>
-          <t>Омурова Назира</t>
+          <t xml:space="preserve">Омурова Назира </t>
         </is>
       </c>
       <c r="D473" s="13" t="inlineStr">
@@ -15697,7 +15613,7 @@
       </c>
       <c r="C474" s="13" t="inlineStr">
         <is>
-          <t>Сейитказиева Жыргалбубу</t>
+          <t xml:space="preserve">Сейитказиева Жыргалбубу </t>
         </is>
       </c>
       <c r="D474" s="13" t="inlineStr">
@@ -15729,7 +15645,7 @@
       </c>
       <c r="C475" s="13" t="inlineStr">
         <is>
-          <t>Турдуева Авахан</t>
+          <t xml:space="preserve">Турдуева Авахан </t>
         </is>
       </c>
       <c r="D475" s="13" t="inlineStr">
@@ -15793,7 +15709,7 @@
       </c>
       <c r="C477" s="17" t="inlineStr">
         <is>
-          <t>Эралы кызы Каныкей</t>
+          <t xml:space="preserve">Эралы кызы Каныкей </t>
         </is>
       </c>
       <c r="D477" s="13" t="inlineStr">
@@ -15825,7 +15741,7 @@
       </c>
       <c r="C478" s="13" t="inlineStr">
         <is>
-          <t>Аширалиева Нурила</t>
+          <t xml:space="preserve">Аширалиева Нурила </t>
         </is>
       </c>
       <c r="D478" s="13" t="inlineStr">
@@ -15857,7 +15773,7 @@
       </c>
       <c r="C479" s="13" t="inlineStr">
         <is>
-          <t>Эгембердиева Уулай</t>
+          <t xml:space="preserve">Эгембердиева Уулай </t>
         </is>
       </c>
       <c r="D479" s="13" t="inlineStr">
@@ -15889,7 +15805,7 @@
       </c>
       <c r="C480" s="13" t="inlineStr">
         <is>
-          <t>Орозбекова Назира</t>
+          <t xml:space="preserve">Орозбекова Назира </t>
         </is>
       </c>
       <c r="D480" s="13" t="inlineStr">
@@ -15921,7 +15837,7 @@
       </c>
       <c r="C481" s="13" t="inlineStr">
         <is>
-          <t>Токтогулова Калмира</t>
+          <t xml:space="preserve">Токтогулова Калмира </t>
         </is>
       </c>
       <c r="D481" s="13" t="inlineStr">
@@ -15953,7 +15869,7 @@
       </c>
       <c r="C482" s="13" t="inlineStr">
         <is>
-          <t>Джапекова Мадина</t>
+          <t xml:space="preserve">Джапекова Мадина </t>
         </is>
       </c>
       <c r="D482" s="13" t="inlineStr">
@@ -15985,7 +15901,7 @@
       </c>
       <c r="C483" s="13" t="inlineStr">
         <is>
-          <t>Исаева Куланда</t>
+          <t xml:space="preserve">Исаева Куланда </t>
         </is>
       </c>
       <c r="D483" s="13" t="inlineStr">
@@ -16017,7 +15933,7 @@
       </c>
       <c r="C484" s="13" t="inlineStr">
         <is>
-          <t>Илиязова Нурийла</t>
+          <t xml:space="preserve">Илиязова Нурийла </t>
         </is>
       </c>
       <c r="D484" s="13" t="inlineStr">
@@ -16049,7 +15965,7 @@
       </c>
       <c r="C485" s="13" t="inlineStr">
         <is>
-          <t>Абдылдаева Мира</t>
+          <t xml:space="preserve">Абдылдаева Мира </t>
         </is>
       </c>
       <c r="D485" s="13" t="inlineStr">
@@ -16081,7 +15997,7 @@
       </c>
       <c r="C486" s="13" t="inlineStr">
         <is>
-          <t>Даниярова Гүлнара</t>
+          <t xml:space="preserve">Даниярова Гульнара </t>
         </is>
       </c>
       <c r="D486" s="13" t="inlineStr">
@@ -16113,7 +16029,7 @@
       </c>
       <c r="C487" s="13" t="inlineStr">
         <is>
-          <t>Мырзабекова Азиза</t>
+          <t xml:space="preserve">Мырзабекова Азиза </t>
         </is>
       </c>
       <c r="D487" s="13" t="inlineStr">
@@ -16145,7 +16061,7 @@
       </c>
       <c r="C488" s="13" t="inlineStr">
         <is>
-          <t>Владимерова Валерия</t>
+          <t xml:space="preserve">Владимерова Валерия </t>
         </is>
       </c>
       <c r="D488" s="13" t="inlineStr">
@@ -16177,7 +16093,7 @@
       </c>
       <c r="C489" s="13" t="inlineStr">
         <is>
-          <t>Нурбек кызы Чолпонай</t>
+          <t xml:space="preserve">Нурбек кызы Чолпонай </t>
         </is>
       </c>
       <c r="D489" s="13" t="inlineStr">
@@ -16209,7 +16125,7 @@
       </c>
       <c r="C490" s="13" t="inlineStr">
         <is>
-          <t>Касымкулова Мира</t>
+          <t xml:space="preserve">Касымкулова Мира </t>
         </is>
       </c>
       <c r="D490" s="13" t="inlineStr">
@@ -16241,7 +16157,7 @@
       </c>
       <c r="C491" s="13" t="inlineStr">
         <is>
-          <t>Масынканова Асель</t>
+          <t xml:space="preserve">Масынканова Асель </t>
         </is>
       </c>
       <c r="D491" s="13" t="inlineStr">
@@ -16273,7 +16189,7 @@
       </c>
       <c r="C492" s="13" t="inlineStr">
         <is>
-          <t>Тентимишова Гүлмира</t>
+          <t xml:space="preserve">Тентимишова Гулмира </t>
         </is>
       </c>
       <c r="D492" s="13" t="inlineStr">
@@ -16305,7 +16221,7 @@
       </c>
       <c r="C493" s="13" t="inlineStr">
         <is>
-          <t>Козмиренко Лилия</t>
+          <t xml:space="preserve">Козмиренко Лилия </t>
         </is>
       </c>
       <c r="D493" s="13" t="inlineStr">
@@ -16337,7 +16253,7 @@
       </c>
       <c r="C494" s="13" t="inlineStr">
         <is>
-          <t>Пашкова Светлана</t>
+          <t xml:space="preserve">Пашкова Светлана </t>
         </is>
       </c>
       <c r="D494" s="13" t="inlineStr">
@@ -16369,7 +16285,7 @@
       </c>
       <c r="C495" s="13" t="inlineStr">
         <is>
-          <t>Осмонов Саламат</t>
+          <t xml:space="preserve">Осмонов Саламат </t>
         </is>
       </c>
       <c r="D495" s="13" t="inlineStr">
@@ -16401,7 +16317,7 @@
       </c>
       <c r="C496" s="13" t="inlineStr">
         <is>
-          <t>Жумашов Урматбек</t>
+          <t xml:space="preserve">Жумашов Урматбек </t>
         </is>
       </c>
       <c r="D496" s="5" t="inlineStr">
@@ -16433,7 +16349,7 @@
       </c>
       <c r="C497" s="13" t="inlineStr">
         <is>
-          <t>Токтоболотов Бактыбек</t>
+          <t xml:space="preserve">Токтоболотов Бактыбек </t>
         </is>
       </c>
       <c r="D497" s="5" t="inlineStr">
@@ -16465,7 +16381,7 @@
       </c>
       <c r="C498" s="13" t="inlineStr">
         <is>
-          <t>Шамшиев Адылбек</t>
+          <t xml:space="preserve">Шамшиев Адылбек </t>
         </is>
       </c>
       <c r="D498" s="5" t="inlineStr">
@@ -16497,7 +16413,7 @@
       </c>
       <c r="C499" s="13" t="inlineStr">
         <is>
-          <t>Белеков Алмамбет</t>
+          <t xml:space="preserve">Белеков Алмамбет </t>
         </is>
       </c>
       <c r="D499" s="5" t="inlineStr">
@@ -16529,7 +16445,7 @@
       </c>
       <c r="C500" s="13" t="inlineStr">
         <is>
-          <t>Беловолова Елена</t>
+          <t xml:space="preserve">Беловолова Елена </t>
         </is>
       </c>
       <c r="D500" s="13" t="inlineStr">
@@ -16593,7 +16509,7 @@
       </c>
       <c r="C502" s="13" t="inlineStr">
         <is>
-          <t>Тургуналиева Джылдызгуль</t>
+          <t xml:space="preserve">Тургуналиева Джылдызгуль </t>
         </is>
       </c>
       <c r="D502" s="13" t="inlineStr">
@@ -16625,7 +16541,7 @@
       </c>
       <c r="C503" s="13" t="inlineStr">
         <is>
-          <t>Байзакова Назира</t>
+          <t xml:space="preserve">Байзакова Назира </t>
         </is>
       </c>
       <c r="D503" s="13" t="inlineStr">
@@ -16657,7 +16573,7 @@
       </c>
       <c r="C504" s="13" t="inlineStr">
         <is>
-          <t>Курманова Мария</t>
+          <t xml:space="preserve">Курманова Мария </t>
         </is>
       </c>
       <c r="D504" s="13" t="inlineStr">
@@ -16689,7 +16605,7 @@
       </c>
       <c r="C505" s="13" t="inlineStr">
         <is>
-          <t>Сулайманова Гульмария</t>
+          <t xml:space="preserve">Сулайманова Гульмария </t>
         </is>
       </c>
       <c r="D505" s="13" t="inlineStr">
@@ -16721,7 +16637,7 @@
       </c>
       <c r="C506" s="4" t="inlineStr">
         <is>
-          <t>Аысбаев Азиз</t>
+          <t xml:space="preserve">Аысбаев Азиз </t>
         </is>
       </c>
       <c r="D506" s="4" t="inlineStr">
@@ -16753,7 +16669,7 @@
       </c>
       <c r="C507" s="4" t="inlineStr">
         <is>
-          <t>Ниязов Алымжан</t>
+          <t xml:space="preserve">Ниязов Алымжан </t>
         </is>
       </c>
       <c r="D507" s="4" t="inlineStr">
@@ -16785,7 +16701,7 @@
       </c>
       <c r="C508" s="4" t="inlineStr">
         <is>
-          <t>Шинизар Ибрагим</t>
+          <t xml:space="preserve">Шинизар Ибрагим </t>
         </is>
       </c>
       <c r="D508" s="4" t="inlineStr">
@@ -16817,7 +16733,7 @@
       </c>
       <c r="C509" s="13" t="inlineStr">
         <is>
-          <t>Ахметова Жанара</t>
+          <t xml:space="preserve">Ахметова Жанара </t>
         </is>
       </c>
       <c r="D509" s="13" t="inlineStr">
@@ -16849,7 +16765,7 @@
       </c>
       <c r="C510" s="13" t="inlineStr">
         <is>
-          <t>Куванычбек кызы Айперим</t>
+          <t xml:space="preserve">Куванычбек кызы Айперим </t>
         </is>
       </c>
       <c r="D510" s="13" t="inlineStr">
@@ -16881,7 +16797,7 @@
       </c>
       <c r="C511" s="13" t="inlineStr">
         <is>
-          <t>Маатова Толкун</t>
+          <t xml:space="preserve">Маатова Толкун </t>
         </is>
       </c>
       <c r="D511" s="13" t="inlineStr">
@@ -16913,7 +16829,7 @@
       </c>
       <c r="C512" s="13" t="inlineStr">
         <is>
-          <t>Мукашева Айгүл</t>
+          <t xml:space="preserve">Мукашева Айгуль </t>
         </is>
       </c>
       <c r="D512" s="13" t="inlineStr">
@@ -16945,7 +16861,7 @@
       </c>
       <c r="C513" s="13" t="inlineStr">
         <is>
-          <t>Сулайманова Онолкан</t>
+          <t xml:space="preserve">Сулайманова Онолкан </t>
         </is>
       </c>
       <c r="D513" s="13" t="inlineStr">
@@ -16977,7 +16893,7 @@
       </c>
       <c r="C514" s="13" t="inlineStr">
         <is>
-          <t>Хоменко Галина</t>
+          <t xml:space="preserve">Хоменко Галина </t>
         </is>
       </c>
       <c r="D514" s="13" t="inlineStr">
@@ -17009,7 +16925,7 @@
       </c>
       <c r="C515" s="13" t="inlineStr">
         <is>
-          <t>Озубекова Венера</t>
+          <t xml:space="preserve">Озубекова Венера </t>
         </is>
       </c>
       <c r="D515" s="13" t="inlineStr">
@@ -17041,7 +16957,7 @@
       </c>
       <c r="C516" s="13" t="inlineStr">
         <is>
-          <t>Асанова Элиза</t>
+          <t xml:space="preserve">Асанова Элиза </t>
         </is>
       </c>
       <c r="D516" s="13" t="inlineStr">
@@ -17073,7 +16989,7 @@
       </c>
       <c r="C517" s="13" t="inlineStr">
         <is>
-          <t>Асаналиева Эркингул</t>
+          <t xml:space="preserve">Асаналиева Эркингул </t>
         </is>
       </c>
       <c r="D517" s="13" t="inlineStr">
@@ -17105,7 +17021,7 @@
       </c>
       <c r="C518" s="13" t="inlineStr">
         <is>
-          <t>Мукабаева Рафкат</t>
+          <t xml:space="preserve">Мукабаева Рафкат </t>
         </is>
       </c>
       <c r="D518" s="13" t="inlineStr">
@@ -17137,7 +17053,7 @@
       </c>
       <c r="C519" s="13" t="inlineStr">
         <is>
-          <t>Исагалиева Гүлнара</t>
+          <t xml:space="preserve">Исагалиева Гульнара </t>
         </is>
       </c>
       <c r="D519" s="13" t="inlineStr">
@@ -17169,7 +17085,7 @@
       </c>
       <c r="C520" s="13" t="inlineStr">
         <is>
-          <t>Оморов Тилек</t>
+          <t xml:space="preserve">Оморов Тилек </t>
         </is>
       </c>
       <c r="D520" s="13" t="inlineStr">
@@ -17201,7 +17117,7 @@
       </c>
       <c r="C521" s="13" t="inlineStr">
         <is>
-          <t>Кадыракунов Кожояр</t>
+          <t xml:space="preserve">Кадыракунов Кожояр </t>
         </is>
       </c>
       <c r="D521" s="13" t="inlineStr">
@@ -17233,7 +17149,7 @@
       </c>
       <c r="C522" s="13" t="inlineStr">
         <is>
-          <t>Толомушов Мирлан</t>
+          <t xml:space="preserve">Толомушов Мирлан </t>
         </is>
       </c>
       <c r="D522" s="13" t="inlineStr">
@@ -17265,7 +17181,7 @@
       </c>
       <c r="C523" s="13" t="inlineStr">
         <is>
-          <t>Асылбеков Өмүрбек</t>
+          <t xml:space="preserve">Асылбеков Омурбек </t>
         </is>
       </c>
       <c r="D523" s="13" t="inlineStr">
@@ -17329,7 +17245,7 @@
       </c>
       <c r="C525" s="13" t="inlineStr">
         <is>
-          <t>Абдыкадыров Адилет</t>
+          <t xml:space="preserve">Абдыкадыров Адилет </t>
         </is>
       </c>
       <c r="D525" s="13" t="inlineStr">
@@ -17361,7 +17277,7 @@
       </c>
       <c r="C526" s="13" t="inlineStr">
         <is>
-          <t>Орозалиев Өмүрбек</t>
+          <t xml:space="preserve">Орозалиев Омурбек </t>
         </is>
       </c>
       <c r="D526" s="13" t="inlineStr">
@@ -17393,7 +17309,7 @@
       </c>
       <c r="C527" s="13" t="inlineStr">
         <is>
-          <t>Батырбеков Ислам</t>
+          <t xml:space="preserve">Батырбеков Ислам </t>
         </is>
       </c>
       <c r="D527" s="13" t="inlineStr">
@@ -17425,7 +17341,7 @@
       </c>
       <c r="C528" s="13" t="inlineStr">
         <is>
-          <t>Батыров Хаким</t>
+          <t xml:space="preserve">Батыров Хаким </t>
         </is>
       </c>
       <c r="D528" s="13" t="inlineStr">
@@ -17457,7 +17373,7 @@
       </c>
       <c r="C529" s="13" t="inlineStr">
         <is>
-          <t>Деркембаев Эрмек</t>
+          <t xml:space="preserve">Деркембаев Эрмек </t>
         </is>
       </c>
       <c r="D529" s="13" t="inlineStr">
@@ -17489,7 +17405,7 @@
       </c>
       <c r="C530" s="13" t="inlineStr">
         <is>
-          <t>Осмоналиев Алмазбек</t>
+          <t xml:space="preserve">Осмоналиев Алмазбек </t>
         </is>
       </c>
       <c r="D530" s="13" t="inlineStr">
@@ -17521,7 +17437,7 @@
       </c>
       <c r="C531" s="13" t="inlineStr">
         <is>
-          <t>Озумкулов Жолдошбек</t>
+          <t xml:space="preserve">Озумкулов Жолдошбек </t>
         </is>
       </c>
       <c r="D531" s="13" t="inlineStr">
@@ -17553,7 +17469,7 @@
       </c>
       <c r="C532" s="13" t="inlineStr">
         <is>
-          <t>Азамат уулу Сталбек</t>
+          <t xml:space="preserve">Азамат уулу Сталбек </t>
         </is>
       </c>
       <c r="D532" s="15" t="inlineStr">
@@ -17585,7 +17501,7 @@
       </c>
       <c r="C533" s="4" t="inlineStr">
         <is>
-          <t>Абдыразаков Алмаз</t>
+          <t xml:space="preserve">Абдыразаков Алмаз </t>
         </is>
       </c>
       <c r="D533" s="4" t="inlineStr">
@@ -17617,7 +17533,7 @@
       </c>
       <c r="C534" s="4" t="inlineStr">
         <is>
-          <t>Азимкулов Нургазы</t>
+          <t xml:space="preserve">Азимкулов Нургазы </t>
         </is>
       </c>
       <c r="D534" s="4" t="inlineStr">
@@ -17649,7 +17565,7 @@
       </c>
       <c r="C535" s="4" t="inlineStr">
         <is>
-          <t>Азимкулов Нурсултан</t>
+          <t xml:space="preserve">Азимкулов Нурсултан </t>
         </is>
       </c>
       <c r="D535" s="4" t="inlineStr">
@@ -17681,7 +17597,7 @@
       </c>
       <c r="C536" s="4" t="inlineStr">
         <is>
-          <t>Бараков Мазанбек</t>
+          <t xml:space="preserve">Бараков Мазанбек </t>
         </is>
       </c>
       <c r="D536" s="4" t="inlineStr">
@@ -17713,7 +17629,7 @@
       </c>
       <c r="C537" s="4" t="inlineStr">
         <is>
-          <t>Мырзакулов Маратбек</t>
+          <t xml:space="preserve">Мырзакулов Маратбек </t>
         </is>
       </c>
       <c r="D537" s="4" t="inlineStr">
@@ -17745,7 +17661,7 @@
       </c>
       <c r="C538" s="4" t="inlineStr">
         <is>
-          <t>Дорофеев Михайил</t>
+          <t xml:space="preserve">Дорофеев Михайил </t>
         </is>
       </c>
       <c r="D538" s="4" t="inlineStr">
@@ -17777,7 +17693,7 @@
       </c>
       <c r="C539" s="4" t="inlineStr">
         <is>
-          <t>Лохуза Махмуд</t>
+          <t xml:space="preserve">Лохуза Махмуд </t>
         </is>
       </c>
       <c r="D539" s="4" t="inlineStr">
@@ -17809,7 +17725,7 @@
       </c>
       <c r="C540" s="4" t="inlineStr">
         <is>
-          <t>Шмелевский Дмитрий</t>
+          <t xml:space="preserve">Шмелевский Дмитрий </t>
         </is>
       </c>
       <c r="D540" s="4" t="inlineStr">
@@ -17841,12 +17757,12 @@
       </c>
       <c r="C541" s="4" t="inlineStr">
         <is>
-          <t>Кабаев Бакир</t>
+          <t xml:space="preserve">Кабаев Бакир </t>
         </is>
       </c>
       <c r="D541" s="4" t="inlineStr">
         <is>
-          <t>"Слесарь по ремонту автотранспортных средств"</t>
+          <t xml:space="preserve">"Слесарь по ремонту автотранспортных средств" </t>
         </is>
       </c>
       <c r="E541" s="4" t="inlineStr">
@@ -17873,7 +17789,7 @@
       </c>
       <c r="C542" s="4" t="inlineStr">
         <is>
-          <t>Маргузиев Талайбек</t>
+          <t xml:space="preserve">Маргузиев Талайбек </t>
         </is>
       </c>
       <c r="D542" s="4" t="inlineStr">
@@ -17905,7 +17821,7 @@
       </c>
       <c r="C543" s="4" t="inlineStr">
         <is>
-          <t>Орозбаев Нурсултан</t>
+          <t xml:space="preserve">Орозбаев Нурсултан </t>
         </is>
       </c>
       <c r="D543" s="4" t="inlineStr">
@@ -17937,7 +17853,7 @@
       </c>
       <c r="C544" s="4" t="inlineStr">
         <is>
-          <t>Эсенбаев Ызатбек</t>
+          <t xml:space="preserve">Эсенбаев Ызатбек </t>
         </is>
       </c>
       <c r="D544" s="4" t="inlineStr">
@@ -17969,7 +17885,7 @@
       </c>
       <c r="C545" s="4" t="inlineStr">
         <is>
-          <t>Абдуразаков Эмир</t>
+          <t xml:space="preserve">Абдуразаков Эмир </t>
         </is>
       </c>
       <c r="D545" s="4" t="inlineStr">
@@ -18001,7 +17917,7 @@
       </c>
       <c r="C546" s="4" t="inlineStr">
         <is>
-          <t>Айтбаев Тилек</t>
+          <t xml:space="preserve">Айтбаев Тилек </t>
         </is>
       </c>
       <c r="D546" s="4" t="inlineStr">
@@ -18033,7 +17949,7 @@
       </c>
       <c r="C547" s="4" t="inlineStr">
         <is>
-          <t>Сива Арафат</t>
+          <t xml:space="preserve">Сива Арафат </t>
         </is>
       </c>
       <c r="D547" s="4" t="inlineStr">
@@ -18065,7 +17981,7 @@
       </c>
       <c r="C548" s="4" t="inlineStr">
         <is>
-          <t>Токталиев Азамат</t>
+          <t xml:space="preserve">Токталиев Азамат </t>
         </is>
       </c>
       <c r="D548" s="4" t="inlineStr">
@@ -18097,7 +18013,7 @@
       </c>
       <c r="C549" s="4" t="inlineStr">
         <is>
-          <t>Бакиев Айбек</t>
+          <t xml:space="preserve">Бакиев Айбек </t>
         </is>
       </c>
       <c r="D549" s="4" t="inlineStr">
@@ -18129,7 +18045,7 @@
       </c>
       <c r="C550" s="4" t="inlineStr">
         <is>
-          <t>Садырбаев Сталбек</t>
+          <t xml:space="preserve">Садырбаев Сталбек </t>
         </is>
       </c>
       <c r="D550" s="4" t="inlineStr">
@@ -18193,7 +18109,7 @@
       </c>
       <c r="C552" s="4" t="inlineStr">
         <is>
-          <t>Чин Владислав</t>
+          <t xml:space="preserve">Чин Владислав </t>
         </is>
       </c>
       <c r="D552" s="4" t="inlineStr">
@@ -18225,7 +18141,7 @@
       </c>
       <c r="C553" s="4" t="inlineStr">
         <is>
-          <t>Кошоев Асылбек</t>
+          <t xml:space="preserve">Кошоев Асылбек </t>
         </is>
       </c>
       <c r="D553" s="4" t="inlineStr">
@@ -18257,7 +18173,7 @@
       </c>
       <c r="C554" s="4" t="inlineStr">
         <is>
-          <t>Эркин уулу Аскат</t>
+          <t xml:space="preserve">Эркин уулу Аскат </t>
         </is>
       </c>
       <c r="D554" s="4" t="inlineStr">
@@ -18289,7 +18205,7 @@
       </c>
       <c r="C555" s="13" t="inlineStr">
         <is>
-          <t>Бейшеналиев Насипбек</t>
+          <t xml:space="preserve">Бейшеналиев Насипбек </t>
         </is>
       </c>
       <c r="D555" s="15" t="inlineStr">
@@ -18321,7 +18237,7 @@
       </c>
       <c r="C556" s="4" t="inlineStr">
         <is>
-          <t>Асаналиев Эриндис</t>
+          <t xml:space="preserve">Асаналиев Эриндис </t>
         </is>
       </c>
       <c r="D556" s="4" t="inlineStr">
@@ -18353,7 +18269,7 @@
       </c>
       <c r="C557" s="4" t="inlineStr">
         <is>
-          <t>Буркутбаев Максут</t>
+          <t xml:space="preserve">Буркутбаев Максут </t>
         </is>
       </c>
       <c r="D557" s="4" t="inlineStr">
@@ -18385,7 +18301,7 @@
       </c>
       <c r="C558" s="4" t="inlineStr">
         <is>
-          <t>Кенжебаев Бейшебай</t>
+          <t xml:space="preserve">Кенжебаев Бейшебай </t>
         </is>
       </c>
       <c r="D558" s="4" t="inlineStr">
@@ -18417,7 +18333,7 @@
       </c>
       <c r="C559" s="4" t="inlineStr">
         <is>
-          <t>Миталиев Жаныш</t>
+          <t xml:space="preserve">Миталиев Жаныш </t>
         </is>
       </c>
       <c r="D559" s="4" t="inlineStr">
@@ -18449,7 +18365,7 @@
       </c>
       <c r="C560" s="4" t="inlineStr">
         <is>
-          <t>Нугаева Эркингуль</t>
+          <t xml:space="preserve">Нугаева Эркингуль </t>
         </is>
       </c>
       <c r="D560" s="4" t="inlineStr">
@@ -18513,7 +18429,7 @@
       </c>
       <c r="C562" s="4" t="inlineStr">
         <is>
-          <t>Исаев Бактыбек</t>
+          <t xml:space="preserve">Исаев Бактыбек </t>
         </is>
       </c>
       <c r="D562" s="4" t="inlineStr">
@@ -18545,7 +18461,7 @@
       </c>
       <c r="C563" s="13" t="inlineStr">
         <is>
-          <t>Назаралиев Каныбек</t>
+          <t xml:space="preserve">Назаралиев Каныбек </t>
         </is>
       </c>
       <c r="D563" s="15" t="inlineStr">
@@ -18577,7 +18493,7 @@
       </c>
       <c r="C564" s="4" t="inlineStr">
         <is>
-          <t>Иманалиев Эламан</t>
+          <t xml:space="preserve">Иманалиев Эламан </t>
         </is>
       </c>
       <c r="D564" s="4" t="inlineStr">
@@ -18609,7 +18525,7 @@
       </c>
       <c r="C565" s="4" t="inlineStr">
         <is>
-          <t>Сагынбаева Мадира</t>
+          <t xml:space="preserve">Сагынбаева Мадира </t>
         </is>
       </c>
       <c r="D565" s="4" t="inlineStr">
@@ -18641,7 +18557,7 @@
       </c>
       <c r="C566" s="13" t="inlineStr">
         <is>
-          <t>Азимкулов Бексултан</t>
+          <t xml:space="preserve">Азимкулов Бексултан </t>
         </is>
       </c>
       <c r="D566" s="15" t="inlineStr">
@@ -18705,7 +18621,7 @@
       </c>
       <c r="C568" s="4" t="inlineStr">
         <is>
-          <t>Токтоболотова Назгүл</t>
+          <t>Токтоболотова Назгул</t>
         </is>
       </c>
       <c r="D568" s="4" t="inlineStr">
@@ -18737,7 +18653,7 @@
       </c>
       <c r="C569" s="4" t="inlineStr">
         <is>
-          <t>Бантабаев Медер</t>
+          <t xml:space="preserve">Бантабаев Медер </t>
         </is>
       </c>
       <c r="D569" s="5" t="inlineStr">
@@ -18769,7 +18685,7 @@
       </c>
       <c r="C570" s="4" t="inlineStr">
         <is>
-          <t>Орозбекова Дариха</t>
+          <t xml:space="preserve">Орозбекова Дариха </t>
         </is>
       </c>
       <c r="D570" s="4" t="inlineStr">
@@ -18801,7 +18717,7 @@
       </c>
       <c r="C571" s="4" t="inlineStr">
         <is>
-          <t>Кушубеков Алмазбек</t>
+          <t xml:space="preserve">Кушубеков Алмазбек </t>
         </is>
       </c>
       <c r="D571" s="4" t="inlineStr">
@@ -18833,12 +18749,12 @@
       </c>
       <c r="C572" s="4" t="inlineStr">
         <is>
-          <t>Акимова Кульнара</t>
+          <t xml:space="preserve">Акимова Кульнара </t>
         </is>
       </c>
       <c r="D572" s="4" t="inlineStr">
         <is>
-          <t>Швея, мастер народных промыслов</t>
+          <t xml:space="preserve">портной,мастер народных промыслов </t>
         </is>
       </c>
       <c r="E572" s="4" t="inlineStr">
@@ -18865,12 +18781,12 @@
       </c>
       <c r="C573" s="4" t="inlineStr">
         <is>
-          <t>Анасекнко Павел</t>
+          <t xml:space="preserve">Анасекнко Павел </t>
         </is>
       </c>
       <c r="D573" s="4" t="inlineStr">
         <is>
-          <t>Слесарь по ремонту автотранспортных средств</t>
+          <t xml:space="preserve">Слесарь по ремонту автотранспортных средств </t>
         </is>
       </c>
       <c r="E573" s="4" t="inlineStr">
@@ -18897,12 +18813,12 @@
       </c>
       <c r="C574" s="4" t="inlineStr">
         <is>
-          <t>Булатов Рауф</t>
+          <t xml:space="preserve">Булатов Рауф </t>
         </is>
       </c>
       <c r="D574" s="4" t="inlineStr">
         <is>
-          <t>Слесарь по ремонту автотранспортных средств</t>
+          <t xml:space="preserve">Слесарь по ремонту автотранспортных средств </t>
         </is>
       </c>
       <c r="E574" s="4" t="inlineStr">
@@ -18929,12 +18845,12 @@
       </c>
       <c r="C575" s="4" t="inlineStr">
         <is>
-          <t>Малиновский Александр</t>
+          <t xml:space="preserve">Малиновский Александр </t>
         </is>
       </c>
       <c r="D575" s="4" t="inlineStr">
         <is>
-          <t>Слесарь по ремонту автотранспортных средств</t>
+          <t xml:space="preserve">Слесарь по ремонту автотранспортных средств </t>
         </is>
       </c>
       <c r="E575" s="4" t="inlineStr">
@@ -18961,12 +18877,12 @@
       </c>
       <c r="C576" s="4" t="inlineStr">
         <is>
-          <t>Пыпченко Александр</t>
+          <t xml:space="preserve">Пыпченко Александр </t>
         </is>
       </c>
       <c r="D576" s="4" t="inlineStr">
         <is>
-          <t>Слесарь по ремонту автотранспортных средств</t>
+          <t xml:space="preserve">Слесарь по ремонту автотранспортных средств </t>
         </is>
       </c>
       <c r="E576" s="4" t="inlineStr">
@@ -18993,12 +18909,12 @@
       </c>
       <c r="C577" s="4" t="inlineStr">
         <is>
-          <t>Эрматов Рустам</t>
+          <t xml:space="preserve">Эрматов Рустам </t>
         </is>
       </c>
       <c r="D577" s="4" t="inlineStr">
         <is>
-          <t>Слесарь по ремонту автотранспортных средств</t>
+          <t xml:space="preserve">Слесарь по ремонту автотранспортных средств </t>
         </is>
       </c>
       <c r="E577" s="4" t="inlineStr">
@@ -19025,7 +18941,7 @@
       </c>
       <c r="C578" s="4" t="inlineStr">
         <is>
-          <t>Эсеналиева Айгүл</t>
+          <t xml:space="preserve">Эсеналиева Айгуль </t>
         </is>
       </c>
       <c r="D578" s="4" t="inlineStr">
@@ -19057,7 +18973,7 @@
       </c>
       <c r="C579" s="4" t="inlineStr">
         <is>
-          <t>Джумабаева Зыйнат</t>
+          <t xml:space="preserve">Джумабаева Зыйнат </t>
         </is>
       </c>
       <c r="D579" s="4" t="inlineStr">
@@ -19089,7 +19005,7 @@
       </c>
       <c r="C580" s="4" t="inlineStr">
         <is>
-          <t>Шералиева Айгүл</t>
+          <t xml:space="preserve">Шералиева Айгул </t>
         </is>
       </c>
       <c r="D580" s="4" t="inlineStr">
@@ -19121,7 +19037,7 @@
       </c>
       <c r="C581" s="4" t="inlineStr">
         <is>
-          <t>Джайлообек уулу Эрлан</t>
+          <t xml:space="preserve">Джайлообек уулу Эрлан </t>
         </is>
       </c>
       <c r="D581" s="4" t="inlineStr">
@@ -19153,7 +19069,7 @@
       </c>
       <c r="C582" s="4" t="inlineStr">
         <is>
-          <t>Карабагышов Алтынбек</t>
+          <t xml:space="preserve">Карабагышов Алтынбек </t>
         </is>
       </c>
       <c r="D582" s="4" t="inlineStr">
@@ -19185,7 +19101,7 @@
       </c>
       <c r="C583" s="4" t="inlineStr">
         <is>
-          <t>Тургуналиев Шугурбек</t>
+          <t xml:space="preserve">Тургуналиев Шугурбек </t>
         </is>
       </c>
       <c r="D583" s="4" t="inlineStr">
@@ -19217,7 +19133,7 @@
       </c>
       <c r="C584" s="4" t="inlineStr">
         <is>
-          <t>Шерматов Калкабай</t>
+          <t xml:space="preserve">Шерматов Калкабай </t>
         </is>
       </c>
       <c r="D584" s="4" t="inlineStr">
@@ -19277,7 +19193,7 @@
       </c>
       <c r="C586" s="4" t="inlineStr">
         <is>
-          <t>Абдраимов Чолпонбек</t>
+          <t xml:space="preserve">Абдраимов Чолпонбек </t>
         </is>
       </c>
       <c r="D586" s="4" t="inlineStr">
@@ -19309,7 +19225,7 @@
       </c>
       <c r="C587" s="4" t="inlineStr">
         <is>
-          <t>Маратбек уулу Бексултан</t>
+          <t xml:space="preserve">Маратбек уулу Бексултан </t>
         </is>
       </c>
       <c r="D587" s="4" t="inlineStr">
@@ -19341,12 +19257,12 @@
       </c>
       <c r="C588" s="4" t="inlineStr">
         <is>
-          <t>Шакирова Бурулча</t>
+          <t xml:space="preserve">Шакирова Бурулча </t>
         </is>
       </c>
       <c r="D588" s="4" t="inlineStr">
         <is>
-          <t>Швея с умением кроить</t>
+          <t xml:space="preserve">Портной с умением кроить </t>
         </is>
       </c>
       <c r="E588" s="4" t="inlineStr">
@@ -19405,7 +19321,7 @@
       </c>
       <c r="C590" s="4" t="inlineStr">
         <is>
-          <t>Мажитов Исо</t>
+          <t xml:space="preserve">Мажитов Исо </t>
         </is>
       </c>
       <c r="D590" s="4" t="inlineStr">
@@ -19437,7 +19353,7 @@
       </c>
       <c r="C591" s="4" t="inlineStr">
         <is>
-          <t>Кененбаева Жылдызкан</t>
+          <t xml:space="preserve">Кененбаева Жылдызкан </t>
         </is>
       </c>
       <c r="D591" s="4" t="inlineStr">
@@ -19469,7 +19385,7 @@
       </c>
       <c r="C592" s="4" t="inlineStr">
         <is>
-          <t>Бердибеков Бекболот</t>
+          <t xml:space="preserve">Бердибеков Бекболот </t>
         </is>
       </c>
       <c r="D592" s="4" t="inlineStr">
@@ -19501,7 +19417,7 @@
       </c>
       <c r="C593" s="4" t="inlineStr">
         <is>
-          <t>Джумубаева Асель</t>
+          <t xml:space="preserve">Джумубаева Асель </t>
         </is>
       </c>
       <c r="D593" s="4" t="inlineStr">
@@ -19533,7 +19449,7 @@
       </c>
       <c r="C594" s="4" t="inlineStr">
         <is>
-          <t>Асаналиева Аяна</t>
+          <t xml:space="preserve">Асаналиева Аяна </t>
         </is>
       </c>
       <c r="D594" s="4" t="inlineStr">
@@ -19565,7 +19481,7 @@
       </c>
       <c r="C595" s="4" t="inlineStr">
         <is>
-          <t>Базарбекова Касиет</t>
+          <t xml:space="preserve">Базарбекова Касиет </t>
         </is>
       </c>
       <c r="D595" s="4" t="inlineStr">
@@ -19597,7 +19513,7 @@
       </c>
       <c r="C596" s="4" t="inlineStr">
         <is>
-          <t>Бердикулова Тахмина</t>
+          <t xml:space="preserve">Бердикулова Тахмина </t>
         </is>
       </c>
       <c r="D596" s="4" t="inlineStr">
@@ -19661,7 +19577,7 @@
       </c>
       <c r="C598" s="4" t="inlineStr">
         <is>
-          <t>Жанабаева Алтынай</t>
+          <t xml:space="preserve">Жанабаева Алтынай </t>
         </is>
       </c>
       <c r="D598" s="4" t="inlineStr">
@@ -19693,7 +19609,7 @@
       </c>
       <c r="C599" s="4" t="inlineStr">
         <is>
-          <t>Абдылдаева Гүлзат</t>
+          <t xml:space="preserve">Абдылдаева Гулзат </t>
         </is>
       </c>
       <c r="D599" s="4" t="inlineStr">
@@ -19725,7 +19641,7 @@
       </c>
       <c r="C600" s="4" t="inlineStr">
         <is>
-          <t>Бекболотова Айтурган</t>
+          <t xml:space="preserve">Бекболотова Айтурган </t>
         </is>
       </c>
       <c r="D600" s="4" t="inlineStr">
@@ -19757,7 +19673,7 @@
       </c>
       <c r="C601" s="4" t="inlineStr">
         <is>
-          <t>Жунусова Жылдыз</t>
+          <t xml:space="preserve">Жунусова Жылдыз </t>
         </is>
       </c>
       <c r="D601" s="4" t="inlineStr">
@@ -19789,7 +19705,7 @@
       </c>
       <c r="C602" s="4" t="inlineStr">
         <is>
-          <t>Мойдунбекова Мээрим</t>
+          <t xml:space="preserve">Мойдунбекова Мээрим </t>
         </is>
       </c>
       <c r="D602" s="4" t="inlineStr">
@@ -19821,7 +19737,7 @@
       </c>
       <c r="C603" s="4" t="inlineStr">
         <is>
-          <t>Сагынбек кызы Акылай</t>
+          <t xml:space="preserve">Сагынбек кызы Акылай </t>
         </is>
       </c>
       <c r="D603" s="4" t="inlineStr">
@@ -19853,7 +19769,7 @@
       </c>
       <c r="C604" s="4" t="inlineStr">
         <is>
-          <t>Усенова Кенжегуль</t>
+          <t xml:space="preserve">Усенова Кенжегуль </t>
         </is>
       </c>
       <c r="D604" s="4" t="inlineStr">
@@ -19885,7 +19801,7 @@
       </c>
       <c r="C605" s="4" t="inlineStr">
         <is>
-          <t>Иманалиев Каныбек</t>
+          <t xml:space="preserve">Иманалиев Каныбек </t>
         </is>
       </c>
       <c r="D605" s="4" t="inlineStr">
@@ -19917,7 +19833,7 @@
       </c>
       <c r="C606" s="4" t="inlineStr">
         <is>
-          <t>Байгельдиев Руслан</t>
+          <t xml:space="preserve">Байгельдиев Руслан </t>
         </is>
       </c>
       <c r="D606" s="4" t="inlineStr">
@@ -19949,7 +19865,7 @@
       </c>
       <c r="C607" s="4" t="inlineStr">
         <is>
-          <t>Джумакадыров Канатбек</t>
+          <t xml:space="preserve">Джумакадыров Канатбек </t>
         </is>
       </c>
       <c r="D607" s="4" t="inlineStr">
@@ -19981,7 +19897,7 @@
       </c>
       <c r="C608" s="4" t="inlineStr">
         <is>
-          <t>Абдуллаев Мээримбек</t>
+          <t xml:space="preserve">Абдуллаев Мээримбек </t>
         </is>
       </c>
       <c r="D608" s="4" t="inlineStr">
@@ -20013,7 +19929,7 @@
       </c>
       <c r="C609" s="4" t="inlineStr">
         <is>
-          <t>Солдатенко Сергей</t>
+          <t xml:space="preserve">Солдатенко Сергей </t>
         </is>
       </c>
       <c r="D609" s="4" t="inlineStr">
@@ -20045,7 +19961,7 @@
       </c>
       <c r="C610" s="4" t="inlineStr">
         <is>
-          <t>Кожогулов Нурбек</t>
+          <t xml:space="preserve">Кожогулов Нурбек </t>
         </is>
       </c>
       <c r="D610" s="4" t="inlineStr">
@@ -20077,7 +19993,7 @@
       </c>
       <c r="C611" s="4" t="inlineStr">
         <is>
-          <t>Мокеев Жакшылык</t>
+          <t xml:space="preserve">Мокеев Жакшылык </t>
         </is>
       </c>
       <c r="D611" s="4" t="inlineStr">
@@ -20109,7 +20025,7 @@
       </c>
       <c r="C612" s="4" t="inlineStr">
         <is>
-          <t>Самудин уулу Азис</t>
+          <t xml:space="preserve">Самудин уулу Азис </t>
         </is>
       </c>
       <c r="D612" s="4" t="inlineStr">
@@ -20141,7 +20057,7 @@
       </c>
       <c r="C613" s="4" t="inlineStr">
         <is>
-          <t>Самаганов Бакытбек</t>
+          <t xml:space="preserve">Самаганов Бакытбек </t>
         </is>
       </c>
       <c r="D613" s="4" t="inlineStr">
@@ -20205,7 +20121,7 @@
       </c>
       <c r="C615" s="4" t="inlineStr">
         <is>
-          <t>Сагынбек уулу Азим</t>
+          <t xml:space="preserve">Сагынбек уулу Азим </t>
         </is>
       </c>
       <c r="D615" s="4" t="inlineStr">
@@ -20237,7 +20153,7 @@
       </c>
       <c r="C616" s="4" t="inlineStr">
         <is>
-          <t>Бакаева Жылдыз</t>
+          <t xml:space="preserve">Бакаева Жылдыз </t>
         </is>
       </c>
       <c r="D616" s="4" t="inlineStr">
@@ -20333,7 +20249,7 @@
       </c>
       <c r="C619" s="4" t="inlineStr">
         <is>
-          <t>Кашанова Гүлмира</t>
+          <t xml:space="preserve">Кашанова Гульмира </t>
         </is>
       </c>
       <c r="D619" s="4" t="inlineStr">
@@ -20365,7 +20281,7 @@
       </c>
       <c r="C620" s="4" t="inlineStr">
         <is>
-          <t>Турсуналиева Аида</t>
+          <t xml:space="preserve">Турсуналиева Аида </t>
         </is>
       </c>
       <c r="D620" s="4" t="inlineStr">
@@ -20429,7 +20345,7 @@
       </c>
       <c r="C622" s="4" t="inlineStr">
         <is>
-          <t>Абдылдаева Гүлзат</t>
+          <t xml:space="preserve">Абдылдаева Гулзат </t>
         </is>
       </c>
       <c r="D622" s="4" t="inlineStr">
@@ -20461,7 +20377,7 @@
       </c>
       <c r="C623" s="4" t="inlineStr">
         <is>
-          <t>Закирова Динара</t>
+          <t xml:space="preserve">Закирова Динара </t>
         </is>
       </c>
       <c r="D623" s="4" t="inlineStr">
@@ -20525,7 +20441,7 @@
       </c>
       <c r="C625" s="4" t="inlineStr">
         <is>
-          <t>Сотволдиева Гульнура</t>
+          <t xml:space="preserve">Сотволдиева Гульнура </t>
         </is>
       </c>
       <c r="D625" s="4" t="inlineStr">
@@ -20621,7 +20537,7 @@
       </c>
       <c r="C628" s="4" t="inlineStr">
         <is>
-          <t>Тургунбаева Дилора</t>
+          <t xml:space="preserve">Тургунбаева Дилора </t>
         </is>
       </c>
       <c r="D628" s="4" t="inlineStr">
@@ -20685,7 +20601,7 @@
       </c>
       <c r="C630" s="4" t="inlineStr">
         <is>
-          <t>Айтикулова Камила</t>
+          <t xml:space="preserve">Айтикулова Камила </t>
         </is>
       </c>
       <c r="D630" s="4" t="inlineStr">
@@ -20717,7 +20633,7 @@
       </c>
       <c r="C631" s="4" t="inlineStr">
         <is>
-          <t>Кадирова Набира</t>
+          <t xml:space="preserve">Кадирова Набира </t>
         </is>
       </c>
       <c r="D631" s="4" t="inlineStr">
@@ -20749,7 +20665,7 @@
       </c>
       <c r="C632" s="4" t="inlineStr">
         <is>
-          <t>Сиезбек уулу Эрнас</t>
+          <t xml:space="preserve">Сиезбек уулу Эрнас </t>
         </is>
       </c>
       <c r="D632" s="4" t="inlineStr">
@@ -20877,7 +20793,7 @@
       </c>
       <c r="C636" s="4" t="inlineStr">
         <is>
-          <t>Медербекова Нуриля</t>
+          <t xml:space="preserve">Медербекова Нуриля </t>
         </is>
       </c>
       <c r="D636" s="4" t="inlineStr">
@@ -20941,7 +20857,7 @@
       </c>
       <c r="C638" s="4" t="inlineStr">
         <is>
-          <t>Абдылдаева Алина</t>
+          <t xml:space="preserve">Абдылдаева Алина </t>
         </is>
       </c>
       <c r="D638" s="4" t="inlineStr">
@@ -21133,7 +21049,7 @@
       </c>
       <c r="C644" s="4" t="inlineStr">
         <is>
-          <t>Мирзарахимова Гулбахар</t>
+          <t xml:space="preserve">Мирзарахимова Гулбахар </t>
         </is>
       </c>
       <c r="D644" s="4" t="inlineStr">
@@ -21165,7 +21081,7 @@
       </c>
       <c r="C645" s="4" t="inlineStr">
         <is>
-          <t>Тагаева Нургул</t>
+          <t xml:space="preserve">Тагаева Нургул </t>
         </is>
       </c>
       <c r="D645" s="4" t="inlineStr">
@@ -21197,7 +21113,7 @@
       </c>
       <c r="C646" s="4" t="inlineStr">
         <is>
-          <t>Жарматова Айзада</t>
+          <t xml:space="preserve">Жарматова Айзада </t>
         </is>
       </c>
       <c r="D646" s="4" t="inlineStr">
@@ -21229,7 +21145,7 @@
       </c>
       <c r="C647" s="4" t="inlineStr">
         <is>
-          <t>Сапалова Мунара</t>
+          <t xml:space="preserve">Сапалова Мунара </t>
         </is>
       </c>
       <c r="D647" s="4" t="inlineStr">
@@ -21261,7 +21177,7 @@
       </c>
       <c r="C648" s="4" t="inlineStr">
         <is>
-          <t>Кадырбеков Акимжан</t>
+          <t xml:space="preserve">Кадырбеков Акимжан </t>
         </is>
       </c>
       <c r="D648" s="4" t="inlineStr">
@@ -21293,7 +21209,7 @@
       </c>
       <c r="C649" s="4" t="inlineStr">
         <is>
-          <t>Токтогул кызы Адинай</t>
+          <t xml:space="preserve">Токтогул кызы Адинай </t>
         </is>
       </c>
       <c r="D649" s="4" t="inlineStr">
@@ -21325,7 +21241,7 @@
       </c>
       <c r="C650" s="4" t="inlineStr">
         <is>
-          <t>Иванов Максим</t>
+          <t xml:space="preserve">Иванов Максим </t>
         </is>
       </c>
       <c r="D650" s="4" t="inlineStr">
@@ -21357,7 +21273,7 @@
       </c>
       <c r="C651" s="4" t="inlineStr">
         <is>
-          <t>Зарипов Рафаэль</t>
+          <t xml:space="preserve">Зарипов Рафаэль </t>
         </is>
       </c>
       <c r="D651" s="4" t="inlineStr">
@@ -21389,7 +21305,7 @@
       </c>
       <c r="C652" s="4" t="inlineStr">
         <is>
-          <t>Толобеков Орозобек</t>
+          <t xml:space="preserve">Толобеков Орозобек </t>
         </is>
       </c>
       <c r="D652" s="4" t="inlineStr">
@@ -21421,7 +21337,7 @@
       </c>
       <c r="C653" s="4" t="inlineStr">
         <is>
-          <t>Сарыбаева Бактыгүл</t>
+          <t xml:space="preserve">Сарыбаева Бактыгуль </t>
         </is>
       </c>
       <c r="D653" s="4" t="inlineStr">
@@ -21453,7 +21369,7 @@
       </c>
       <c r="C654" s="4" t="inlineStr">
         <is>
-          <t>Хамраев Жолдош</t>
+          <t xml:space="preserve">Хамраев Жолдош </t>
         </is>
       </c>
       <c r="D654" s="4" t="inlineStr">
@@ -21485,7 +21401,7 @@
       </c>
       <c r="C655" s="4" t="inlineStr">
         <is>
-          <t>Ишен уулу Эдилбек</t>
+          <t xml:space="preserve">Ишен уулу Эдилбек </t>
         </is>
       </c>
       <c r="D655" s="4" t="inlineStr">
@@ -21517,7 +21433,7 @@
       </c>
       <c r="C656" s="4" t="inlineStr">
         <is>
-          <t>Маразыкова Нуржамал</t>
+          <t xml:space="preserve">Маразыкова Нуржамал </t>
         </is>
       </c>
       <c r="D656" s="4" t="inlineStr">
@@ -21549,12 +21465,12 @@
       </c>
       <c r="C657" s="4" t="inlineStr">
         <is>
-          <t>Исаматов Тилек</t>
+          <t xml:space="preserve">Исаматов Тилек </t>
         </is>
       </c>
       <c r="D657" s="4" t="inlineStr">
         <is>
-          <t>Слесерь по ремонту автотранспортных средств</t>
+          <t xml:space="preserve">Слесерь по ремонту автотранспортных средств </t>
         </is>
       </c>
       <c r="E657" s="4" t="inlineStr">
@@ -21581,7 +21497,7 @@
       </c>
       <c r="C658" s="4" t="inlineStr">
         <is>
-          <t>Щвец Дмитрий</t>
+          <t xml:space="preserve">Щвец Дмитрий </t>
         </is>
       </c>
       <c r="D658" s="4" t="inlineStr">
@@ -21613,7 +21529,7 @@
       </c>
       <c r="C659" s="4" t="inlineStr">
         <is>
-          <t>Кашкарбаев Талгат</t>
+          <t xml:space="preserve">Кашкарбаев Талгат </t>
         </is>
       </c>
       <c r="D659" s="4" t="inlineStr">
@@ -21645,7 +21561,7 @@
       </c>
       <c r="C660" s="4" t="inlineStr">
         <is>
-          <t>Батырбек уулу Элеман</t>
+          <t xml:space="preserve">Батырбек уулу Элеман </t>
         </is>
       </c>
       <c r="D660" s="4" t="inlineStr">
@@ -21677,7 +21593,7 @@
       </c>
       <c r="C661" s="4" t="inlineStr">
         <is>
-          <t>Эшенкулова Гулсайра</t>
+          <t xml:space="preserve">Эшенкулова Гулсайра </t>
         </is>
       </c>
       <c r="D661" s="4" t="inlineStr">
@@ -21709,7 +21625,7 @@
       </c>
       <c r="C662" s="4" t="inlineStr">
         <is>
-          <t>Кыдырбаева Динара</t>
+          <t xml:space="preserve">Кыдырбаева Динара </t>
         </is>
       </c>
       <c r="D662" s="4" t="inlineStr">
@@ -21773,7 +21689,7 @@
       </c>
       <c r="C664" s="4" t="inlineStr">
         <is>
-          <t>Атамбеков Шаршенбек</t>
+          <t xml:space="preserve">Атамбеков Шаршенбек </t>
         </is>
       </c>
       <c r="D664" s="4" t="inlineStr">
@@ -21805,7 +21721,7 @@
       </c>
       <c r="C665" s="4" t="inlineStr">
         <is>
-          <t>Майрыков Эрнис</t>
+          <t xml:space="preserve">Майрыков Эрнис </t>
         </is>
       </c>
       <c r="D665" s="4" t="inlineStr">
@@ -21837,7 +21753,7 @@
       </c>
       <c r="C666" s="4" t="inlineStr">
         <is>
-          <t>Тагайбек уулу Бообек</t>
+          <t xml:space="preserve">Тагайбек уулу Бообек </t>
         </is>
       </c>
       <c r="D666" s="4" t="inlineStr">
@@ -21869,7 +21785,7 @@
       </c>
       <c r="C667" s="4" t="inlineStr">
         <is>
-          <t>Жумабай уулу Марсбек</t>
+          <t xml:space="preserve">Жумабай уулу Марсбек </t>
         </is>
       </c>
       <c r="D667" s="4" t="inlineStr">
@@ -21901,7 +21817,7 @@
       </c>
       <c r="C668" s="4" t="inlineStr">
         <is>
-          <t>Алыбаев Алмаз</t>
+          <t xml:space="preserve">Алыбаев Алмаз </t>
         </is>
       </c>
       <c r="D668" s="4" t="inlineStr">
@@ -21933,7 +21849,7 @@
       </c>
       <c r="C669" s="4" t="inlineStr">
         <is>
-          <t>Ишеналы уулу Беккалнур</t>
+          <t xml:space="preserve">Ишеналы уулу Беккалнур </t>
         </is>
       </c>
       <c r="D669" s="4" t="inlineStr">
@@ -21965,7 +21881,7 @@
       </c>
       <c r="C670" s="4" t="inlineStr">
         <is>
-          <t>Ишеналы уулу Беккалнур</t>
+          <t xml:space="preserve">Ишеналы уулу Беккалнур </t>
         </is>
       </c>
       <c r="D670" s="4" t="inlineStr">
@@ -21997,7 +21913,7 @@
       </c>
       <c r="C671" s="4" t="inlineStr">
         <is>
-          <t>Акыш уулу Актилек</t>
+          <t xml:space="preserve">Акыш уулу Актилек </t>
         </is>
       </c>
       <c r="D671" s="4" t="inlineStr">
@@ -22029,7 +21945,7 @@
       </c>
       <c r="C672" s="4" t="inlineStr">
         <is>
-          <t>Кыпчакоы Абдужамил</t>
+          <t xml:space="preserve">Кыпчакоы Абдужамил </t>
         </is>
       </c>
       <c r="D672" s="4" t="inlineStr">
@@ -22063,7 +21979,7 @@
       </c>
       <c r="C673" s="4" t="inlineStr">
         <is>
-          <t>Эргешов Мухамедали</t>
+          <t xml:space="preserve">Эргешов Мухамедали </t>
         </is>
       </c>
       <c r="D673" s="4" t="inlineStr">
@@ -22095,7 +22011,7 @@
       </c>
       <c r="C674" s="4" t="inlineStr">
         <is>
-          <t>Умаров Даиржан</t>
+          <t xml:space="preserve">Умаров Даиржан </t>
         </is>
       </c>
       <c r="D674" s="4" t="inlineStr">
@@ -22127,7 +22043,7 @@
       </c>
       <c r="C675" s="4" t="inlineStr">
         <is>
-          <t>Билалов Алтынбек</t>
+          <t xml:space="preserve">Билалов Алтынбек </t>
         </is>
       </c>
       <c r="D675" s="4" t="inlineStr">
@@ -22159,7 +22075,7 @@
       </c>
       <c r="C676" s="4" t="inlineStr">
         <is>
-          <t>Дуйшенбик Тариэль</t>
+          <t xml:space="preserve">Дуйшенбик Тариэль </t>
         </is>
       </c>
       <c r="D676" s="4" t="inlineStr">
@@ -22191,7 +22107,7 @@
       </c>
       <c r="C677" s="4" t="inlineStr">
         <is>
-          <t>Бектен уулу Мирбек</t>
+          <t xml:space="preserve">Бектен уулу Мирбек </t>
         </is>
       </c>
       <c r="D677" s="4" t="inlineStr">
@@ -22223,7 +22139,7 @@
       </c>
       <c r="C678" s="4" t="inlineStr">
         <is>
-          <t>Султанов Максат</t>
+          <t xml:space="preserve">Султанов Максат </t>
         </is>
       </c>
       <c r="D678" s="4" t="inlineStr">
@@ -22255,7 +22171,7 @@
       </c>
       <c r="C679" s="4" t="inlineStr">
         <is>
-          <t>Абдусаматова Угулай</t>
+          <t xml:space="preserve">Абдусаматова Угулай </t>
         </is>
       </c>
       <c r="D679" s="4" t="inlineStr">
@@ -22287,7 +22203,7 @@
       </c>
       <c r="C680" s="4" t="inlineStr">
         <is>
-          <t>Дадабаева Фатима</t>
+          <t xml:space="preserve">Дадабаева Фатима </t>
         </is>
       </c>
       <c r="D680" s="4" t="inlineStr">
@@ -22319,7 +22235,7 @@
       </c>
       <c r="C681" s="4" t="inlineStr">
         <is>
-          <t>Абдумуталиева Назокат</t>
+          <t xml:space="preserve">Абдумуталиева Назокат </t>
         </is>
       </c>
       <c r="D681" s="4" t="inlineStr">
@@ -22351,7 +22267,7 @@
       </c>
       <c r="C682" s="4" t="inlineStr">
         <is>
-          <t>Калыбекова Жибек</t>
+          <t xml:space="preserve">Калыбекова Жибек </t>
         </is>
       </c>
       <c r="D682" s="4" t="inlineStr">
@@ -22417,7 +22333,7 @@
       </c>
       <c r="C684" s="4" t="inlineStr">
         <is>
-          <t>Жунусова Эльзада</t>
+          <t xml:space="preserve">Жунусова Эльзада </t>
         </is>
       </c>
       <c r="D684" s="4" t="inlineStr">
@@ -22449,7 +22365,7 @@
       </c>
       <c r="C685" s="4" t="inlineStr">
         <is>
-          <t>Карыбаев Намаз</t>
+          <t xml:space="preserve">Карыбаев Намаз </t>
         </is>
       </c>
       <c r="D685" s="4" t="inlineStr">
@@ -22481,7 +22397,7 @@
       </c>
       <c r="C686" s="4" t="inlineStr">
         <is>
-          <t>Авазбек уулу Азамат</t>
+          <t xml:space="preserve">Авазбек уулу Азамат </t>
         </is>
       </c>
       <c r="D686" s="4" t="inlineStr">
@@ -22489,11 +22405,7 @@
           <t xml:space="preserve">Мастер общестроительных работ </t>
         </is>
       </c>
-      <c r="E686" s="4" t="inlineStr">
-        <is>
-          <t>ЦС № 000621</t>
-        </is>
-      </c>
+      <c r="E686" s="4" t="inlineStr"/>
       <c r="F686" s="5" t="inlineStr">
         <is>
           <t xml:space="preserve">Умут-2. Строит.объект. </t>
@@ -22513,7 +22425,7 @@
       </c>
       <c r="C687" s="4" t="inlineStr">
         <is>
-          <t>Борукеев Таалайбек</t>
+          <t xml:space="preserve">Борукеев Таалайбек </t>
         </is>
       </c>
       <c r="D687" s="4" t="inlineStr">
@@ -22545,7 +22457,7 @@
       </c>
       <c r="C688" s="4" t="inlineStr">
         <is>
-          <t>Мамекова Элмира</t>
+          <t xml:space="preserve">Мамекова Элмира </t>
         </is>
       </c>
       <c r="D688" s="4" t="inlineStr">
@@ -22577,7 +22489,7 @@
       </c>
       <c r="C689" s="4" t="inlineStr">
         <is>
-          <t>Оскомбаева Гүлмира</t>
+          <t xml:space="preserve">Оскомбаева Гулмира </t>
         </is>
       </c>
       <c r="D689" s="4" t="inlineStr">
@@ -22737,7 +22649,7 @@
       </c>
       <c r="C694" s="4" t="inlineStr">
         <is>
-          <t>Макешов Уланбек</t>
+          <t xml:space="preserve">Макешов Уланбек </t>
         </is>
       </c>
       <c r="D694" s="4" t="inlineStr">
@@ -22774,7 +22686,7 @@
       </c>
       <c r="D695" s="4" t="inlineStr">
         <is>
-          <t>Слесарь по ремонту автотранспортных средств</t>
+          <t xml:space="preserve">Слесарь по ремонту автотранспортных средств </t>
         </is>
       </c>
       <c r="E695" s="4" t="inlineStr">
@@ -22801,7 +22713,7 @@
       </c>
       <c r="C696" s="4" t="inlineStr">
         <is>
-          <t>Жумалиев Урмат</t>
+          <t xml:space="preserve">Жумалиев Урмат </t>
         </is>
       </c>
       <c r="D696" s="4" t="inlineStr">
@@ -22929,7 +22841,7 @@
       </c>
       <c r="C700" s="4" t="inlineStr">
         <is>
-          <t>Рогожинский Сергей</t>
+          <t xml:space="preserve">Рогожинский Сергей </t>
         </is>
       </c>
       <c r="D700" s="4" t="inlineStr">
@@ -23065,11 +22977,7 @@
           <t xml:space="preserve">Мастер народных промыслов </t>
         </is>
       </c>
-      <c r="E704" s="4" t="inlineStr">
-        <is>
-          <t>ЦС № 000639</t>
-        </is>
-      </c>
+      <c r="E704" s="4" t="inlineStr"/>
       <c r="F704" s="5" t="inlineStr">
         <is>
           <t xml:space="preserve">ЦНСВ </t>
@@ -23089,7 +22997,7 @@
       </c>
       <c r="C705" s="4" t="inlineStr">
         <is>
-          <t>Молотов Бактияр</t>
+          <t xml:space="preserve">Молотов Бактияр </t>
         </is>
       </c>
       <c r="D705" s="4" t="inlineStr">
@@ -23217,7 +23125,7 @@
       </c>
       <c r="C709" s="4" t="inlineStr">
         <is>
-          <t>Кудайбердиев Талант</t>
+          <t xml:space="preserve">Кудайбердиев Талант </t>
         </is>
       </c>
       <c r="D709" s="4" t="inlineStr">
@@ -23249,7 +23157,7 @@
       </c>
       <c r="C710" s="4" t="inlineStr">
         <is>
-          <t>Евтушенко Викентий</t>
+          <t xml:space="preserve">Евтушенко Викентий </t>
         </is>
       </c>
       <c r="D710" s="4" t="inlineStr">
@@ -23281,7 +23189,7 @@
       </c>
       <c r="C711" s="4" t="inlineStr">
         <is>
-          <t>Бактыбеков Нурсултан</t>
+          <t xml:space="preserve">Бактыбеков Нурсултан </t>
         </is>
       </c>
       <c r="D711" s="4" t="inlineStr">
@@ -23318,7 +23226,7 @@
       </c>
       <c r="D712" s="4" t="inlineStr">
         <is>
-          <t>Контролер технического состояния автомототранспортных средств</t>
+          <t xml:space="preserve">Контролер технического состояния автомототранспортных средств </t>
         </is>
       </c>
       <c r="E712" s="4" t="inlineStr">
@@ -23441,7 +23349,7 @@
       </c>
       <c r="C716" s="4" t="inlineStr">
         <is>
-          <t>Молдалиев Шумкарбек</t>
+          <t xml:space="preserve">Молдалиев Шумкарбек </t>
         </is>
       </c>
       <c r="D716" s="4" t="inlineStr">
@@ -23473,7 +23381,7 @@
       </c>
       <c r="C717" s="4" t="inlineStr">
         <is>
-          <t>Усеналиев Тагайбек Бусурманович</t>
+          <t xml:space="preserve">Усеналиев Тагайбек Бусурманович </t>
         </is>
       </c>
       <c r="D717" s="4" t="inlineStr">
@@ -23505,7 +23413,7 @@
       </c>
       <c r="C718" s="4" t="inlineStr">
         <is>
-          <t>Токолов Замирбек Таатканович</t>
+          <t xml:space="preserve">Токолов Замирбек Таатканович </t>
         </is>
       </c>
       <c r="D718" s="4" t="inlineStr">
@@ -23537,7 +23445,7 @@
       </c>
       <c r="C719" s="4" t="inlineStr">
         <is>
-          <t>Нуркулов Токтобек Көкөнович</t>
+          <t xml:space="preserve">Нуркулов Токтобек Көкөнович </t>
         </is>
       </c>
       <c r="D719" s="4" t="inlineStr">
@@ -23569,7 +23477,7 @@
       </c>
       <c r="C720" s="4" t="inlineStr">
         <is>
-          <t>Жаныкулов Айбек Чолпонович</t>
+          <t xml:space="preserve">Жаныкулов Айбек Чолпонович </t>
         </is>
       </c>
       <c r="D720" s="4" t="inlineStr">
@@ -23601,7 +23509,7 @@
       </c>
       <c r="C721" s="4" t="inlineStr">
         <is>
-          <t>Романенко Илья Антонович</t>
+          <t xml:space="preserve">Романенко Илья Антонович </t>
         </is>
       </c>
       <c r="D721" s="4" t="inlineStr">
@@ -23633,7 +23541,7 @@
       </c>
       <c r="C722" s="4" t="inlineStr">
         <is>
-          <t>Баршугуров Эрлан Бейшенбекович</t>
+          <t xml:space="preserve">Баршугуров Эрлан Бейшенбекович </t>
         </is>
       </c>
       <c r="D722" s="4" t="inlineStr">
@@ -23665,7 +23573,7 @@
       </c>
       <c r="C723" s="4" t="inlineStr">
         <is>
-          <t>Тынымбеков Бекулан Тилекович</t>
+          <t xml:space="preserve">Тынымбеков Бекулан Тилекович </t>
         </is>
       </c>
       <c r="D723" s="4" t="inlineStr">
@@ -23697,7 +23605,7 @@
       </c>
       <c r="C724" s="4" t="inlineStr">
         <is>
-          <t>Мамбетказиев Өмүркул</t>
+          <t xml:space="preserve">Мамбетказиев Өмүркул </t>
         </is>
       </c>
       <c r="D724" s="4" t="inlineStr">
@@ -23788,192 +23696,96 @@
       <c r="A727" s="4" t="n">
         <v>725</v>
       </c>
-      <c r="B727" s="6" t="n">
-        <v>46191</v>
-      </c>
-      <c r="C727" s="4" t="inlineStr">
-        <is>
-          <t>Казыбекова Ырыс</t>
-        </is>
-      </c>
-      <c r="D727" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">повар 3 разряда </t>
-        </is>
-      </c>
+      <c r="B727" s="4" t="n"/>
+      <c r="C727" s="4" t="n"/>
+      <c r="D727" s="4" t="n"/>
       <c r="E727" s="4" t="inlineStr">
         <is>
           <t>ЦС № 000662</t>
         </is>
       </c>
-      <c r="F727" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">ЦНСВ </t>
-        </is>
-      </c>
-      <c r="G727" s="6" t="n">
-        <v>46191</v>
-      </c>
+      <c r="F727" s="5" t="n"/>
+      <c r="G727" s="6" t="n"/>
       <c r="H727" s="4" t="n"/>
     </row>
     <row r="728">
       <c r="A728" s="4" t="n">
         <v>726</v>
       </c>
-      <c r="B728" s="6" t="n">
-        <v>46196</v>
-      </c>
-      <c r="C728" s="4" t="inlineStr">
-        <is>
-          <t>Эгембердиев Жоробек</t>
-        </is>
-      </c>
-      <c r="D728" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">слесарь -сантехник 3 разряда </t>
-        </is>
-      </c>
+      <c r="B728" s="4" t="n"/>
+      <c r="C728" s="4" t="n"/>
+      <c r="D728" s="4" t="n"/>
       <c r="E728" s="4" t="inlineStr">
         <is>
           <t>ЦС № 000663</t>
         </is>
       </c>
-      <c r="F728" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Кут Олокон </t>
-        </is>
-      </c>
-      <c r="G728" s="6" t="n">
-        <v>46196</v>
-      </c>
+      <c r="F728" s="5" t="n"/>
+      <c r="G728" s="6" t="n"/>
       <c r="H728" s="4" t="n"/>
     </row>
     <row r="729">
       <c r="A729" s="4" t="n">
         <v>727</v>
       </c>
-      <c r="B729" s="6" t="n">
-        <v>46196</v>
-      </c>
-      <c r="C729" s="4" t="inlineStr">
-        <is>
-          <t>Каримов Кубанычбек</t>
-        </is>
-      </c>
-      <c r="D729" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">слесарь - сантехник 3 разряда </t>
-        </is>
-      </c>
+      <c r="B729" s="4" t="n"/>
+      <c r="C729" s="4" t="n"/>
+      <c r="D729" s="4" t="n"/>
       <c r="E729" s="4" t="inlineStr">
         <is>
           <t>Цс № 000664</t>
         </is>
       </c>
-      <c r="F729" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Кут Олокон </t>
-        </is>
-      </c>
-      <c r="G729" s="6" t="n">
-        <v>46196</v>
-      </c>
+      <c r="F729" s="5" t="n"/>
+      <c r="G729" s="6" t="n"/>
       <c r="H729" s="4" t="n"/>
     </row>
     <row r="730">
       <c r="A730" s="4" t="n">
         <v>728</v>
       </c>
-      <c r="B730" s="6" t="n">
-        <v>46197</v>
-      </c>
-      <c r="C730" s="4" t="inlineStr">
-        <is>
-          <t>Чилмомбетов Тилек</t>
-        </is>
-      </c>
-      <c r="D730" s="4" t="inlineStr">
-        <is>
-          <t>Мастер отделочных строительных работ 4 р</t>
-        </is>
-      </c>
+      <c r="B730" s="4" t="n"/>
+      <c r="C730" s="4" t="n"/>
+      <c r="D730" s="4" t="n"/>
       <c r="E730" s="4" t="inlineStr">
         <is>
           <t>ЦС № 000665</t>
         </is>
       </c>
-      <c r="F730" s="5" t="inlineStr">
-        <is>
-          <t>БКАМС</t>
-        </is>
-      </c>
-      <c r="G730" s="6" t="n">
-        <v>46197</v>
-      </c>
+      <c r="F730" s="5" t="n"/>
+      <c r="G730" s="6" t="n"/>
       <c r="H730" s="4" t="n"/>
     </row>
     <row r="731">
       <c r="A731" s="4" t="n">
         <v>729</v>
       </c>
-      <c r="B731" s="6" t="n">
-        <v>46197</v>
-      </c>
-      <c r="C731" s="4" t="inlineStr">
-        <is>
-          <t>Садыков Чынгыз</t>
-        </is>
-      </c>
-      <c r="D731" s="4" t="inlineStr">
-        <is>
-          <t>Мастер отделочных строительных работ 4р</t>
-        </is>
-      </c>
+      <c r="B731" s="4" t="n"/>
+      <c r="C731" s="4" t="n"/>
+      <c r="D731" s="4" t="n"/>
       <c r="E731" s="4" t="inlineStr">
         <is>
           <t>ЦС № 000666</t>
         </is>
       </c>
-      <c r="F731" s="5" t="inlineStr">
-        <is>
-          <t>БКАМС</t>
-        </is>
-      </c>
-      <c r="G731" s="6" t="n">
-        <v>46197</v>
-      </c>
+      <c r="F731" s="5" t="n"/>
+      <c r="G731" s="6" t="n"/>
       <c r="H731" s="4" t="n"/>
     </row>
     <row r="732">
       <c r="A732" s="4" t="n">
         <v>730</v>
       </c>
-      <c r="B732" s="6" t="n">
-        <v>46197</v>
-      </c>
-      <c r="C732" s="4" t="inlineStr">
-        <is>
-          <t>Молдокеев Нурбек</t>
-        </is>
-      </c>
-      <c r="D732" s="4" t="inlineStr">
-        <is>
-          <t>Мастер отделочных строительных работ 4р</t>
-        </is>
-      </c>
+      <c r="B732" s="4" t="n"/>
+      <c r="C732" s="4" t="n"/>
+      <c r="D732" s="4" t="n"/>
       <c r="E732" s="4" t="inlineStr">
         <is>
           <t>ЦС № 000667</t>
         </is>
       </c>
-      <c r="F732" s="5" t="inlineStr">
-        <is>
-          <t>БКАМС</t>
-        </is>
-      </c>
-      <c r="G732" s="6" t="n">
-        <v>46197</v>
-      </c>
+      <c r="F732" s="5" t="n"/>
+      <c r="G732" s="6" t="n"/>
       <c r="H732" s="4" t="n"/>
     </row>
     <row r="733">
@@ -24017,7 +23829,7 @@
       </c>
       <c r="C734" s="4" t="inlineStr">
         <is>
-          <t>Жайлообек уулу Бектурган</t>
+          <t xml:space="preserve">Жайлообек уулу Бектурган </t>
         </is>
       </c>
       <c r="D734" s="4" t="inlineStr">
@@ -24049,7 +23861,7 @@
       </c>
       <c r="C735" s="4" t="inlineStr">
         <is>
-          <t>Шамурзаев Доктурбек</t>
+          <t xml:space="preserve">Шамурзаев Доктурбек </t>
         </is>
       </c>
       <c r="D735" s="4" t="inlineStr">
@@ -24081,7 +23893,7 @@
       </c>
       <c r="C736" s="4" t="inlineStr">
         <is>
-          <t>Азамат уулу Арген</t>
+          <t xml:space="preserve">Азамат уулу Арген </t>
         </is>
       </c>
       <c r="D736" s="4" t="inlineStr">
@@ -24113,7 +23925,7 @@
       </c>
       <c r="C737" s="4" t="inlineStr">
         <is>
-          <t>Рахматуулаева Умида</t>
+          <t xml:space="preserve">Рахматуулаева Умида </t>
         </is>
       </c>
       <c r="D737" s="4" t="inlineStr">
@@ -24145,7 +23957,7 @@
       </c>
       <c r="C738" s="4" t="inlineStr">
         <is>
-          <t>Мыйманбай кызы Токтаим</t>
+          <t xml:space="preserve">Мыйманбай кызы Токтаим </t>
         </is>
       </c>
       <c r="D738" s="4" t="inlineStr">
@@ -24177,7 +23989,7 @@
       </c>
       <c r="C739" s="4" t="inlineStr">
         <is>
-          <t>Журавлева Алена Сергеевна</t>
+          <t xml:space="preserve">Журавлева Алена Сергеевна </t>
         </is>
       </c>
       <c r="D739" s="4" t="inlineStr">
@@ -24241,7 +24053,7 @@
       </c>
       <c r="C741" s="4" t="inlineStr">
         <is>
-          <t>ТИщенко Олег Викторович</t>
+          <t xml:space="preserve">ТИщенко Олег Викторович </t>
         </is>
       </c>
       <c r="D741" s="4" t="inlineStr">
@@ -24305,7 +24117,7 @@
       </c>
       <c r="C743" s="4" t="inlineStr">
         <is>
-          <t>Таашыбек уулу Кутман</t>
+          <t xml:space="preserve">Таашыбек уулу Кутман </t>
         </is>
       </c>
       <c r="D743" s="4" t="inlineStr">
@@ -24382,11 +24194,7 @@
           <t>ЦС № 000680</t>
         </is>
       </c>
-      <c r="F745" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">ЦНСВ </t>
-        </is>
-      </c>
+      <c r="F745" s="5" t="n"/>
       <c r="G745" s="6" t="n">
         <v>46205</v>
       </c>
@@ -24396,7 +24204,7 @@
       <c r="A746" s="4" t="n">
         <v>784</v>
       </c>
-      <c r="B746" s="6" t="n">
+      <c r="B746" s="22" t="n">
         <v>46206</v>
       </c>
       <c r="C746" s="4" t="inlineStr">
@@ -24406,7 +24214,7 @@
       </c>
       <c r="D746" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Сварщик ручной сварки 3 разряда </t>
+          <t>Сварщик ручной сварки 3 разряда</t>
         </is>
       </c>
       <c r="E746" s="4" t="inlineStr">
@@ -24428,7 +24236,7 @@
       <c r="A747" s="4" t="n">
         <v>785</v>
       </c>
-      <c r="B747" s="6" t="n">
+      <c r="B747" s="22" t="n">
         <v>46206</v>
       </c>
       <c r="C747" s="4" t="inlineStr">
@@ -24438,7 +24246,7 @@
       </c>
       <c r="D747" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Повар </t>
+          <t>Повар</t>
         </is>
       </c>
       <c r="E747" s="4" t="inlineStr">
@@ -24448,7 +24256,7 @@
       </c>
       <c r="F747" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">ЦНСВ </t>
+          <t>ЦНСВ</t>
         </is>
       </c>
       <c r="G747" s="6" t="n">
@@ -24460,7 +24268,7 @@
       <c r="A748" s="4" t="n">
         <v>786</v>
       </c>
-      <c r="B748" s="6" t="n">
+      <c r="B748" s="22" t="n">
         <v>46211</v>
       </c>
       <c r="C748" s="4" t="inlineStr">
@@ -24470,17 +24278,17 @@
       </c>
       <c r="D748" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">слесарь - сантехник </t>
+          <t>слесарь - сантехник</t>
         </is>
       </c>
       <c r="E748" s="4" t="inlineStr">
         <is>
-          <t>ЦС №000683</t>
+          <t>ЦС № 000683</t>
         </is>
       </c>
       <c r="F748" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Парикмахерская </t>
+          <t>Парикмахерская</t>
         </is>
       </c>
       <c r="G748" s="6" t="n">
@@ -24492,7 +24300,7 @@
       <c r="A749" s="4" t="n">
         <v>787</v>
       </c>
-      <c r="B749" s="6" t="n">
+      <c r="B749" s="22" t="n">
         <v>46213</v>
       </c>
       <c r="C749" s="4" t="inlineStr">
@@ -24502,7 +24310,7 @@
       </c>
       <c r="D749" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Электрогазосварщик  5 разряда </t>
+          <t>Электрогазосварщик 5 разряда</t>
         </is>
       </c>
       <c r="E749" s="4" t="inlineStr">
@@ -24524,27 +24332,27 @@
       <c r="A750" s="4" t="n">
         <v>788</v>
       </c>
-      <c r="B750" s="6" t="n">
+      <c r="B750" s="22" t="n">
         <v>46216</v>
       </c>
       <c r="C750" s="4" t="inlineStr">
         <is>
-          <t>Ураимов Өмүрбек</t>
+          <t>Ураимов Омурбек</t>
         </is>
       </c>
       <c r="D750" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">слесарь - сантехник 4 разряда </t>
+          <t>слесарь - сантехник 4 разряда</t>
         </is>
       </c>
       <c r="E750" s="4" t="inlineStr">
         <is>
-          <t>ЦС №000685</t>
+          <t>ЦС № 000685</t>
         </is>
       </c>
       <c r="F750" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Кут </t>
+          <t>Кут</t>
         </is>
       </c>
       <c r="G750" s="6" t="n">
@@ -24556,7 +24364,7 @@
       <c r="A751" s="4" t="n">
         <v>789</v>
       </c>
-      <c r="B751" s="6" t="n">
+      <c r="B751" s="22" t="n">
         <v>46216</v>
       </c>
       <c r="C751" s="4" t="inlineStr">
@@ -24566,17 +24374,17 @@
       </c>
       <c r="D751" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">слесарь - сантехник 3 разряда </t>
+          <t>слесарь - сантехник 3 разряда</t>
         </is>
       </c>
       <c r="E751" s="4" t="inlineStr">
         <is>
-          <t>ЦС №000686</t>
+          <t>ЦС № 000686</t>
         </is>
       </c>
       <c r="F751" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Кут </t>
+          <t>Кут</t>
         </is>
       </c>
       <c r="G751" s="6" t="n">
@@ -24588,7 +24396,7 @@
       <c r="A752" s="4" t="n">
         <v>790</v>
       </c>
-      <c r="B752" s="6" t="n">
+      <c r="B752" s="22" t="n">
         <v>46216</v>
       </c>
       <c r="C752" s="4" t="inlineStr">
@@ -24598,17 +24406,17 @@
       </c>
       <c r="D752" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Электрик по ремонту автомоб-го оборудования </t>
+          <t>Электрик по ремонту автомоб-го оборудования</t>
         </is>
       </c>
       <c r="E752" s="4" t="inlineStr">
         <is>
-          <t>ЦС №000687</t>
+          <t>ЦС № 000687</t>
         </is>
       </c>
       <c r="F752" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">БАДК </t>
+          <t>БАДК</t>
         </is>
       </c>
       <c r="G752" s="6" t="n">
@@ -24620,7 +24428,7 @@
       <c r="A753" s="4" t="n">
         <v>791</v>
       </c>
-      <c r="B753" s="6" t="n">
+      <c r="B753" s="22" t="n">
         <v>46217</v>
       </c>
       <c r="C753" s="4" t="inlineStr">
@@ -24630,17 +24438,17 @@
       </c>
       <c r="D753" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">повар - кондитер 5 разряда </t>
+          <t>повар - кондитер 5 разряда</t>
         </is>
       </c>
       <c r="E753" s="4" t="inlineStr">
         <is>
-          <t>ЦС№ 000688</t>
+          <t>ЦС № 000688</t>
         </is>
       </c>
       <c r="F753" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Кызыл - Кыя </t>
+          <t>Кызыл - Кыя</t>
         </is>
       </c>
       <c r="G753" s="6" t="n">
@@ -24652,7 +24460,7 @@
       <c r="A754" s="4" t="n">
         <v>792</v>
       </c>
-      <c r="B754" s="6" t="n">
+      <c r="B754" s="22" t="n">
         <v>46217</v>
       </c>
       <c r="C754" s="4" t="inlineStr">
@@ -24662,17 +24470,17 @@
       </c>
       <c r="D754" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">повар - кондитер 5 разряда </t>
+          <t>повар - кондитер 5 разряда</t>
         </is>
       </c>
       <c r="E754" s="4" t="inlineStr">
         <is>
-          <t>ЦС№ 000689</t>
+          <t>ЦС № 000689</t>
         </is>
       </c>
       <c r="F754" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Кызыл - Кыя </t>
+          <t>Кызыл - Кыя</t>
         </is>
       </c>
       <c r="G754" s="6" t="n">
@@ -24684,7 +24492,7 @@
       <c r="A755" s="4" t="n">
         <v>793</v>
       </c>
-      <c r="B755" s="6" t="n">
+      <c r="B755" s="22" t="n">
         <v>46217</v>
       </c>
       <c r="C755" s="4" t="inlineStr">
@@ -24694,17 +24502,17 @@
       </c>
       <c r="D755" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">повар - кондитер 5 разряда </t>
+          <t>повар - кондитер 5 разряда</t>
         </is>
       </c>
       <c r="E755" s="4" t="inlineStr">
         <is>
-          <t>ЦС№ 000690</t>
+          <t>ЦС № 000690</t>
         </is>
       </c>
       <c r="F755" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Кызыл - Кыя </t>
+          <t>Кызыл - Кыя</t>
         </is>
       </c>
       <c r="G755" s="6" t="n">
@@ -24716,17 +24524,17 @@
       <c r="A756" s="4" t="n">
         <v>794</v>
       </c>
-      <c r="B756" s="6" t="n">
+      <c r="B756" s="22" t="n">
         <v>46217</v>
       </c>
       <c r="C756" s="4" t="inlineStr">
         <is>
-          <t>Калданова Гүлзат</t>
+          <t>Калданова Гулзат</t>
         </is>
       </c>
       <c r="D756" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">повар - кондитер 5 разряда </t>
+          <t>повар - кондитер 5 разряда</t>
         </is>
       </c>
       <c r="E756" s="4" t="inlineStr">
@@ -24736,7 +24544,7 @@
       </c>
       <c r="F756" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Кызыл - Кыя </t>
+          <t>Кызыл - Кыя</t>
         </is>
       </c>
       <c r="G756" s="6" t="n">
@@ -24748,7 +24556,7 @@
       <c r="A757" s="4" t="n">
         <v>795</v>
       </c>
-      <c r="B757" s="6" t="n">
+      <c r="B757" s="22" t="n">
         <v>46217</v>
       </c>
       <c r="C757" s="4" t="inlineStr">
@@ -24758,17 +24566,17 @@
       </c>
       <c r="D757" s="4" t="inlineStr">
         <is>
-          <t>Швея с умением кроить 5 разряда</t>
+          <t>Портной с умением кроить 5 разряда</t>
         </is>
       </c>
       <c r="E757" s="4" t="inlineStr">
         <is>
-          <t>Цс № 000692</t>
+          <t>ЦС № 000692</t>
         </is>
       </c>
       <c r="F757" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Кызыл - Кыя </t>
+          <t>Кызыл - Кыя</t>
         </is>
       </c>
       <c r="G757" s="6" t="n">
@@ -24780,7 +24588,7 @@
       <c r="A758" s="4" t="n">
         <v>796</v>
       </c>
-      <c r="B758" s="6" t="n">
+      <c r="B758" s="22" t="n">
         <v>46217</v>
       </c>
       <c r="C758" s="4" t="inlineStr">
@@ -24790,17 +24598,17 @@
       </c>
       <c r="D758" s="4" t="inlineStr">
         <is>
-          <t>Швея с умением кроить 5 разряда</t>
+          <t>Портной с умением кроить 5 разряда</t>
         </is>
       </c>
       <c r="E758" s="4" t="inlineStr">
         <is>
-          <t>ЦС №000693</t>
+          <t>ЦС № 000693</t>
         </is>
       </c>
       <c r="F758" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Кызыл - Кыя </t>
+          <t>Кызыл - Кыя</t>
         </is>
       </c>
       <c r="G758" s="6" t="n">
@@ -24812,7 +24620,7 @@
       <c r="A759" s="4" t="n">
         <v>797</v>
       </c>
-      <c r="B759" s="6" t="n">
+      <c r="B759" s="22" t="n">
         <v>46220</v>
       </c>
       <c r="C759" s="4" t="inlineStr">
@@ -24822,12 +24630,12 @@
       </c>
       <c r="D759" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Электрогазосварщик 5 разхряда </t>
+          <t>Электрогазосварщик 5 разряда</t>
         </is>
       </c>
       <c r="E759" s="4" t="inlineStr">
         <is>
-          <t>ЦС №000694</t>
+          <t>ЦС № 000694</t>
         </is>
       </c>
       <c r="F759" s="5" t="inlineStr">
@@ -24844,7 +24652,7 @@
       <c r="A760" s="4" t="n">
         <v>798</v>
       </c>
-      <c r="B760" s="6" t="n">
+      <c r="B760" s="22" t="n">
         <v>46223</v>
       </c>
       <c r="C760" s="4" t="inlineStr">
@@ -24854,17 +24662,17 @@
       </c>
       <c r="D760" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Облицовщик - плиточник </t>
+          <t>Облицовщик - плиточник</t>
         </is>
       </c>
       <c r="E760" s="4" t="inlineStr">
         <is>
-          <t>ЦС №000695</t>
+          <t>ЦС № 000695</t>
         </is>
       </c>
       <c r="F760" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">ЖК Каусар </t>
+          <t>ЖК Каусар</t>
         </is>
       </c>
       <c r="G760" s="6" t="n">
@@ -24876,7 +24684,7 @@
       <c r="A761" s="4" t="n">
         <v>799</v>
       </c>
-      <c r="B761" s="6" t="n">
+      <c r="B761" s="22" t="n">
         <v>46225</v>
       </c>
       <c r="C761" s="4" t="inlineStr">
@@ -24891,7 +24699,7 @@
       </c>
       <c r="E761" s="4" t="inlineStr">
         <is>
-          <t>ЦС №000696</t>
+          <t>ЦС № 000696</t>
         </is>
       </c>
       <c r="F761" s="5" t="inlineStr">
@@ -24908,7 +24716,7 @@
       <c r="A762" s="4" t="n">
         <v>800</v>
       </c>
-      <c r="B762" s="6" t="n">
+      <c r="B762" s="22" t="n">
         <v>46232</v>
       </c>
       <c r="C762" s="4" t="inlineStr">
@@ -24918,7 +24726,7 @@
       </c>
       <c r="D762" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Электросварщик 2 разряда </t>
+          <t>Электросварщик 2 разряда</t>
         </is>
       </c>
       <c r="E762" s="4" t="inlineStr">
@@ -24928,11 +24736,11 @@
       </c>
       <c r="F762" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">ПЛ 27 </t>
+          <t>ПЛ 27</t>
         </is>
       </c>
       <c r="G762" s="6" t="n">
-        <v>46263</v>
+        <v>46232</v>
       </c>
       <c r="H762" s="4" t="n"/>
     </row>
@@ -24940,7 +24748,7 @@
       <c r="A763" s="4" t="n">
         <v>801</v>
       </c>
-      <c r="B763" s="6" t="n">
+      <c r="B763" s="22" t="n">
         <v>46232</v>
       </c>
       <c r="C763" s="4" t="inlineStr">
@@ -24955,12 +24763,12 @@
       </c>
       <c r="E763" s="4" t="inlineStr">
         <is>
-          <t>ЦС №000698</t>
+          <t>ЦС № 000698</t>
         </is>
       </c>
       <c r="F763" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Частное СТО в с. Лебединовка </t>
+          <t>Частное СТО в с. Лебединовка</t>
         </is>
       </c>
       <c r="G763" s="6" t="n">
@@ -24972,27 +24780,27 @@
       <c r="A764" s="4" t="n">
         <v>802</v>
       </c>
-      <c r="B764" s="6" t="n">
+      <c r="B764" s="22" t="n">
         <v>46232</v>
       </c>
       <c r="C764" s="4" t="inlineStr">
         <is>
-          <t>Чеңкилова Алтынбү Базаркуловна</t>
+          <t>Ченкилова Алтынбу Базаркуловна</t>
         </is>
       </c>
       <c r="D764" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Санитар ветеринарный 4 разряда </t>
+          <t>Санитар ветеринарный 4 разряда</t>
         </is>
       </c>
       <c r="E764" s="4" t="inlineStr">
         <is>
-          <t>ЦС №000699</t>
+          <t>ЦС № 000699</t>
         </is>
       </c>
       <c r="F764" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Токтогул </t>
+          <t>Токтогул</t>
         </is>
       </c>
       <c r="G764" s="6" t="n">
@@ -25004,17 +24812,17 @@
       <c r="A765" s="4" t="n">
         <v>803</v>
       </c>
-      <c r="B765" s="6" t="n">
+      <c r="B765" s="22" t="n">
         <v>46232</v>
       </c>
       <c r="C765" s="4" t="inlineStr">
         <is>
-          <t>Сатымкулова Мира  Балтабаевна</t>
+          <t>Сатымкулова Мира Балтабаевна</t>
         </is>
       </c>
       <c r="D765" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Санитар ветеринарный 4 разряда </t>
+          <t>Санитар ветеринарный 4 разряда</t>
         </is>
       </c>
       <c r="E765" s="4" t="inlineStr">
@@ -25024,7 +24832,7 @@
       </c>
       <c r="F765" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Токтогул </t>
+          <t>Токтогул</t>
         </is>
       </c>
       <c r="G765" s="6" t="n">
@@ -25036,17 +24844,17 @@
       <c r="A766" s="4" t="n">
         <v>804</v>
       </c>
-      <c r="B766" s="6" t="n">
+      <c r="B766" s="22" t="n">
         <v>46237</v>
       </c>
       <c r="C766" s="4" t="inlineStr">
         <is>
-          <t>Туратбек уулу Өмүрбек</t>
+          <t>Туратбек у Омурбек</t>
         </is>
       </c>
       <c r="D766" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">слесарь - сантехник 3 разряда </t>
+          <t>слесарь - сантехник 3 разряда</t>
         </is>
       </c>
       <c r="E766" s="4" t="inlineStr">
@@ -25056,7 +24864,7 @@
       </c>
       <c r="F766" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">ЦНСВ </t>
+          <t>ЦНСВ</t>
         </is>
       </c>
       <c r="G766" s="6" t="n">
@@ -25068,27 +24876,27 @@
       <c r="A767" s="4" t="n">
         <v>805</v>
       </c>
-      <c r="B767" s="6" t="n">
+      <c r="B767" s="22" t="n">
         <v>46239</v>
       </c>
       <c r="C767" s="4" t="inlineStr">
         <is>
-          <t>Назаралиева  Сабырбү</t>
+          <t>Назаралиева Сабырб</t>
         </is>
       </c>
       <c r="D767" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">повар 4 разряда </t>
+          <t>повар 4 разряда</t>
         </is>
       </c>
       <c r="E767" s="4" t="inlineStr">
         <is>
-          <t>ЦС №000702</t>
+          <t>ЦС № 000702</t>
         </is>
       </c>
       <c r="F767" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">ЦНСВ </t>
+          <t>ЦНСВ</t>
         </is>
       </c>
       <c r="G767" s="6" t="n">
@@ -25100,7 +24908,7 @@
       <c r="A768" s="4" t="n">
         <v>806</v>
       </c>
-      <c r="B768" s="6" t="n">
+      <c r="B768" s="22" t="n">
         <v>46240</v>
       </c>
       <c r="C768" s="4" t="inlineStr">
@@ -25110,17 +24918,17 @@
       </c>
       <c r="D768" s="4" t="inlineStr">
         <is>
-          <t>Электромонтер по ремонту воздушных линий электропередачи III разряда</t>
+          <t>Электромонтер по ремонту воздушных линий электропередачи</t>
         </is>
       </c>
       <c r="E768" s="4" t="inlineStr">
         <is>
-          <t>ЦС №000703</t>
+          <t>ЦС № 000703</t>
         </is>
       </c>
       <c r="F768" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">ЦНСВ </t>
+          <t>ЦНСВ</t>
         </is>
       </c>
       <c r="G768" s="6" t="n">
@@ -25132,27 +24940,27 @@
       <c r="A769" s="4" t="n">
         <v>807</v>
       </c>
-      <c r="B769" s="6" t="n">
+      <c r="B769" s="22" t="n">
         <v>46241</v>
       </c>
       <c r="C769" s="4" t="inlineStr">
         <is>
-          <t>Аманбаев Нурмухаммбетали Небирбековичке</t>
+          <t>Аманбаев Нурмухаммбетали Небир</t>
         </is>
       </c>
       <c r="D769" s="4" t="inlineStr">
         <is>
-          <t>Мастер жилищно – коммунального  хозяйства III разряда</t>
+          <t>Мастер жилищно – коммунального хозяйства III р</t>
         </is>
       </c>
       <c r="E769" s="4" t="inlineStr">
         <is>
-          <t>ЦС №000704</t>
+          <t>ЦС № 000704</t>
         </is>
       </c>
       <c r="F769" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">КУТ ЖК УМУТ </t>
+          <t>КУТ ЖК УМУТ</t>
         </is>
       </c>
       <c r="G769" s="6" t="n">
@@ -25164,7 +24972,7 @@
       <c r="A770" s="4" t="n">
         <v>808</v>
       </c>
-      <c r="B770" s="6" t="n">
+      <c r="B770" s="22" t="n">
         <v>46232</v>
       </c>
       <c r="C770" s="4" t="inlineStr">
@@ -25174,17 +24982,17 @@
       </c>
       <c r="D770" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Электромонтажник 3 разряда </t>
+          <t>Электромонтажник 3 разряда</t>
         </is>
       </c>
       <c r="E770" s="4" t="inlineStr">
         <is>
-          <t>ЦС №000705</t>
+          <t>ЦС № 000705</t>
         </is>
       </c>
       <c r="F770" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Частное СТО в с. Лебединовка </t>
+          <t>Частное СТО в с. Лебединовка</t>
         </is>
       </c>
       <c r="G770" s="6" t="n">
@@ -25196,7 +25004,7 @@
       <c r="A771" s="4" t="n">
         <v>809</v>
       </c>
-      <c r="B771" s="6" t="n">
+      <c r="B771" s="22" t="n">
         <v>46244</v>
       </c>
       <c r="C771" s="4" t="inlineStr">
@@ -25206,17 +25014,17 @@
       </c>
       <c r="D771" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Слесарь - сантехник 3 разряда </t>
+          <t>Слесарь - сантехник 3 разряда</t>
         </is>
       </c>
       <c r="E771" s="4" t="inlineStr">
         <is>
-          <t>ЦС №000706</t>
+          <t>ЦС № 000706</t>
         </is>
       </c>
       <c r="F771" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">ЦНСВ </t>
+          <t>ЦНСВ</t>
         </is>
       </c>
       <c r="G771" s="6" t="n">
@@ -25228,7 +25036,7 @@
       <c r="A772" s="4" t="n">
         <v>810</v>
       </c>
-      <c r="B772" s="6" t="n">
+      <c r="B772" s="22" t="n">
         <v>46245</v>
       </c>
       <c r="C772" s="4" t="inlineStr">
@@ -25238,7 +25046,7 @@
       </c>
       <c r="D772" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Слеварь - сантехник 3 разряда </t>
+          <t>Слесарь - сантехник 3 разряда</t>
         </is>
       </c>
       <c r="E772" s="4" t="inlineStr">
@@ -25248,7 +25056,7 @@
       </c>
       <c r="F772" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">ЦНСВ </t>
+          <t>ЦНСВ</t>
         </is>
       </c>
       <c r="G772" s="6" t="n">
@@ -25260,7 +25068,7 @@
       <c r="A773" s="4" t="n">
         <v>811</v>
       </c>
-      <c r="B773" s="6" t="n">
+      <c r="B773" s="22" t="n">
         <v>46248</v>
       </c>
       <c r="C773" s="4" t="inlineStr">
@@ -25270,7 +25078,7 @@
       </c>
       <c r="D773" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Оператор швейного оборудования </t>
+          <t>Оператор швейного оборудования</t>
         </is>
       </c>
       <c r="E773" s="4" t="inlineStr">
@@ -25280,7 +25088,7 @@
       </c>
       <c r="F773" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">ЦНСВ </t>
+          <t>ЦНСВ</t>
         </is>
       </c>
       <c r="G773" s="6" t="n">
@@ -25292,7 +25100,7 @@
       <c r="A774" s="4" t="n">
         <v>812</v>
       </c>
-      <c r="B774" s="6" t="n">
+      <c r="B774" s="22" t="n">
         <v>46252</v>
       </c>
       <c r="C774" s="4" t="inlineStr">
@@ -25302,12 +25110,12 @@
       </c>
       <c r="D774" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Электросварщик 4 разряда </t>
+          <t>Электросварщик 4 разряда</t>
         </is>
       </c>
       <c r="E774" s="4" t="inlineStr">
         <is>
-          <t>ЦС №000709</t>
+          <t>ЦС № 000709</t>
         </is>
       </c>
       <c r="F774" s="5" t="inlineStr">
@@ -25324,27 +25132,27 @@
       <c r="A775" s="4" t="n">
         <v>813</v>
       </c>
-      <c r="B775" s="6" t="n">
+      <c r="B775" s="22" t="n">
         <v>46253</v>
       </c>
       <c r="C775" s="4" t="inlineStr">
         <is>
-          <t>Буслаева Валентина Валентиновна</t>
+          <t>Буслаева Валентина Валентинова</t>
         </is>
       </c>
       <c r="D775" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Сыродел 4 разряда </t>
+          <t>Сыродел 4 разряда</t>
         </is>
       </c>
       <c r="E775" s="4" t="inlineStr">
         <is>
-          <t>ЦС №000710</t>
+          <t>ЦС № 000710</t>
         </is>
       </c>
       <c r="F775" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">с. Веловодское Каф кеф </t>
+          <t>с. Беловодское Каф кеф</t>
         </is>
       </c>
       <c r="G775" s="6" t="n">
@@ -25356,27 +25164,27 @@
       <c r="A776" s="4" t="n">
         <v>814</v>
       </c>
-      <c r="B776" s="6" t="n">
+      <c r="B776" s="22" t="n">
         <v>46254</v>
       </c>
       <c r="C776" s="4" t="inlineStr">
         <is>
-          <t>Жапашова Элмира Назирбековна</t>
+          <t>Жапашова Эльмира Назирбековна</t>
         </is>
       </c>
       <c r="D776" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Повар - кондитер 5 разряда </t>
+          <t>Повар - кондитер 5 разряда</t>
         </is>
       </c>
       <c r="E776" s="4" t="inlineStr">
         <is>
-          <t>ЦС №000711</t>
+          <t>ЦС № 000711</t>
         </is>
       </c>
       <c r="F776" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">ЦНСВ </t>
+          <t>ЦНСВ</t>
         </is>
       </c>
       <c r="G776" s="6" t="n">
@@ -25388,7 +25196,7 @@
       <c r="A777" s="4" t="n">
         <v>815</v>
       </c>
-      <c r="B777" s="6" t="n">
+      <c r="B777" s="22" t="n">
         <v>46254</v>
       </c>
       <c r="C777" s="4" t="inlineStr">
@@ -25398,17 +25206,17 @@
       </c>
       <c r="D777" s="4" t="inlineStr">
         <is>
-          <t>Швея с умением кроить 3 разряда</t>
+          <t>Портной с умением кроить 3 разряда</t>
         </is>
       </c>
       <c r="E777" s="4" t="inlineStr">
         <is>
-          <t>ЦС №000712</t>
+          <t>ЦС № 000712</t>
         </is>
       </c>
       <c r="F777" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">ЦНСВ </t>
+          <t>ЦНСВ</t>
         </is>
       </c>
       <c r="G777" s="6" t="n">
@@ -25420,27 +25228,27 @@
       <c r="A778" s="4" t="n">
         <v>816</v>
       </c>
-      <c r="B778" s="6" t="n">
+      <c r="B778" s="22" t="n">
         <v>46258</v>
       </c>
       <c r="C778" s="4" t="inlineStr">
         <is>
-          <t>Орунбекова Назгүл Сонунбековна</t>
+          <t>Орунбекова Назгуль Сонунбековна</t>
         </is>
       </c>
       <c r="D778" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Повар - кондитер 4 разряда </t>
+          <t>Повар - кондитер 4 разряда</t>
         </is>
       </c>
       <c r="E778" s="4" t="inlineStr">
         <is>
-          <t>ЦС №000713</t>
+          <t>ЦС № 000713</t>
         </is>
       </c>
       <c r="F778" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">ЦНСВ </t>
+          <t>ЦНСВ</t>
         </is>
       </c>
       <c r="G778" s="6" t="n">
@@ -25449,89 +25257,57 @@
       <c r="H778" s="4" t="n"/>
     </row>
     <row r="779">
-      <c r="A779" s="4" t="n">
-        <v>817</v>
-      </c>
+      <c r="A779" s="4" t="n"/>
       <c r="B779" s="4" t="n"/>
       <c r="C779" s="4" t="n"/>
       <c r="D779" s="4" t="n"/>
-      <c r="E779" s="4" t="inlineStr">
-        <is>
-          <t>ЦС № 000714</t>
-        </is>
-      </c>
+      <c r="E779" s="4" t="n"/>
       <c r="F779" s="5" t="n"/>
       <c r="G779" s="6" t="n"/>
       <c r="H779" s="4" t="n"/>
     </row>
     <row r="780">
-      <c r="A780" s="4" t="n">
-        <v>818</v>
-      </c>
+      <c r="A780" s="4" t="n"/>
       <c r="B780" s="4" t="n"/>
       <c r="C780" s="4" t="n"/>
       <c r="D780" s="4" t="n"/>
-      <c r="E780" s="4" t="inlineStr">
-        <is>
-          <t>ЦС № 000715</t>
-        </is>
-      </c>
+      <c r="E780" s="4" t="n"/>
       <c r="F780" s="5" t="n"/>
       <c r="G780" s="6" t="n"/>
       <c r="H780" s="4" t="n"/>
     </row>
     <row r="781">
-      <c r="A781" s="4" t="n">
-        <v>819</v>
-      </c>
+      <c r="A781" s="4" t="n"/>
       <c r="B781" s="4" t="n"/>
       <c r="C781" s="4" t="n"/>
       <c r="D781" s="4" t="n"/>
-      <c r="E781" s="4" t="inlineStr">
-        <is>
-          <t>ЦС №000716</t>
-        </is>
-      </c>
+      <c r="E781" s="4" t="n"/>
       <c r="F781" s="5" t="n"/>
       <c r="G781" s="6" t="n"/>
       <c r="H781" s="4" t="n"/>
     </row>
     <row r="782">
-      <c r="A782" s="4" t="n">
-        <v>820</v>
-      </c>
+      <c r="A782" s="4" t="n"/>
       <c r="B782" s="4" t="n"/>
       <c r="C782" s="4" t="n"/>
       <c r="D782" s="4" t="n"/>
-      <c r="E782" s="4" t="inlineStr">
-        <is>
-          <t>ЦС №000717</t>
-        </is>
-      </c>
+      <c r="E782" s="4" t="n"/>
       <c r="F782" s="5" t="n"/>
       <c r="G782" s="6" t="n"/>
       <c r="H782" s="4" t="n"/>
     </row>
     <row r="783">
-      <c r="A783" s="4" t="n">
-        <v>821</v>
-      </c>
+      <c r="A783" s="4" t="n"/>
       <c r="B783" s="4" t="n"/>
       <c r="C783" s="4" t="n"/>
       <c r="D783" s="4" t="n"/>
-      <c r="E783" s="4" t="inlineStr">
-        <is>
-          <t>ЦС №000718</t>
-        </is>
-      </c>
+      <c r="E783" s="4" t="n"/>
       <c r="F783" s="5" t="n"/>
       <c r="G783" s="6" t="n"/>
       <c r="H783" s="4" t="n"/>
     </row>
     <row r="784">
-      <c r="A784" s="4" t="n">
-        <v>822</v>
-      </c>
+      <c r="A784" s="4" t="n"/>
       <c r="B784" s="4" t="n"/>
       <c r="C784" s="4" t="n"/>
       <c r="D784" s="4" t="n"/>
@@ -25541,9 +25317,7 @@
       <c r="H784" s="4" t="n"/>
     </row>
     <row r="785">
-      <c r="A785" s="4" t="n">
-        <v>823</v>
-      </c>
+      <c r="A785" s="4" t="n"/>
       <c r="B785" s="4" t="n"/>
       <c r="C785" s="4" t="n"/>
       <c r="D785" s="4" t="n"/>
@@ -25553,9 +25327,7 @@
       <c r="H785" s="4" t="n"/>
     </row>
     <row r="786">
-      <c r="A786" s="4" t="n">
-        <v>824</v>
-      </c>
+      <c r="A786" s="4" t="n"/>
       <c r="B786" s="4" t="n"/>
       <c r="C786" s="4" t="n"/>
       <c r="D786" s="4" t="n"/>
@@ -25565,9 +25337,7 @@
       <c r="H786" s="4" t="n"/>
     </row>
     <row r="787">
-      <c r="A787" s="4" t="n">
-        <v>825</v>
-      </c>
+      <c r="A787" s="4" t="n"/>
       <c r="B787" s="4" t="n"/>
       <c r="C787" s="4" t="n"/>
       <c r="D787" s="4" t="n"/>
@@ -25577,9 +25347,7 @@
       <c r="H787" s="4" t="n"/>
     </row>
     <row r="788">
-      <c r="A788" s="4" t="n">
-        <v>826</v>
-      </c>
+      <c r="A788" s="4" t="n"/>
       <c r="B788" s="4" t="n"/>
       <c r="C788" s="4" t="n"/>
       <c r="D788" s="4" t="n"/>
@@ -25589,9 +25357,7 @@
       <c r="H788" s="4" t="n"/>
     </row>
     <row r="789">
-      <c r="A789" s="4" t="n">
-        <v>827</v>
-      </c>
+      <c r="A789" s="4" t="n"/>
       <c r="B789" s="4" t="n"/>
       <c r="C789" s="4" t="n"/>
       <c r="D789" s="4" t="n"/>
@@ -25601,9 +25367,7 @@
       <c r="H789" s="4" t="n"/>
     </row>
     <row r="790">
-      <c r="A790" s="4" t="n">
-        <v>828</v>
-      </c>
+      <c r="A790" s="4" t="n"/>
       <c r="B790" s="4" t="n"/>
       <c r="C790" s="4" t="n"/>
       <c r="D790" s="4" t="n"/>
@@ -25613,9 +25377,7 @@
       <c r="H790" s="4" t="n"/>
     </row>
     <row r="791">
-      <c r="A791" s="4" t="n">
-        <v>829</v>
-      </c>
+      <c r="A791" s="4" t="n"/>
       <c r="B791" s="4" t="n"/>
       <c r="C791" s="4" t="n"/>
       <c r="D791" s="4" t="n"/>
@@ -25625,9 +25387,7 @@
       <c r="H791" s="4" t="n"/>
     </row>
     <row r="792">
-      <c r="A792" s="4" t="n">
-        <v>830</v>
-      </c>
+      <c r="A792" s="4" t="n"/>
       <c r="B792" s="4" t="n"/>
       <c r="C792" s="4" t="n"/>
       <c r="D792" s="4" t="n"/>
@@ -25637,9 +25397,7 @@
       <c r="H792" s="4" t="n"/>
     </row>
     <row r="793">
-      <c r="A793" s="4" t="n">
-        <v>831</v>
-      </c>
+      <c r="A793" s="4" t="n"/>
       <c r="B793" s="4" t="n"/>
       <c r="C793" s="4" t="n"/>
       <c r="D793" s="4" t="n"/>
@@ -25649,9 +25407,7 @@
       <c r="H793" s="4" t="n"/>
     </row>
     <row r="794">
-      <c r="A794" s="4" t="n">
-        <v>832</v>
-      </c>
+      <c r="A794" s="4" t="n"/>
       <c r="B794" s="4" t="n"/>
       <c r="C794" s="4" t="n"/>
       <c r="D794" s="4" t="n"/>
@@ -25661,9 +25417,7 @@
       <c r="H794" s="4" t="n"/>
     </row>
     <row r="795">
-      <c r="A795" s="4" t="n">
-        <v>833</v>
-      </c>
+      <c r="A795" s="4" t="n"/>
       <c r="B795" s="4" t="n"/>
       <c r="C795" s="4" t="n"/>
       <c r="D795" s="4" t="n"/>
@@ -25673,9 +25427,7 @@
       <c r="H795" s="4" t="n"/>
     </row>
     <row r="796">
-      <c r="A796" s="4" t="n">
-        <v>834</v>
-      </c>
+      <c r="A796" s="4" t="n"/>
       <c r="B796" s="4" t="n"/>
       <c r="C796" s="4" t="n"/>
       <c r="D796" s="4" t="n"/>
@@ -25685,9 +25437,7 @@
       <c r="H796" s="4" t="n"/>
     </row>
     <row r="797">
-      <c r="A797" s="4" t="n">
-        <v>835</v>
-      </c>
+      <c r="A797" s="4" t="n"/>
       <c r="B797" s="4" t="n"/>
       <c r="C797" s="4" t="n"/>
       <c r="D797" s="4" t="n"/>
@@ -43346,9 +43096,6 @@
       <c r="G2562" s="6" t="n"/>
       <c r="H2562" s="4" t="n"/>
     </row>
-    <row r="2563">
-      <c r="D2563" s="4" t="n"/>
-    </row>
   </sheetData>
   <autoFilter ref="A2:H2"/>
   <mergeCells count="1">
@@ -43356,6 +43103,5 @@
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="landscape" paperSize="9" scale="10"/>
-  <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
 </worksheet>
 </file>